--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="709">
   <si>
     <t>Datum</t>
   </si>
@@ -1842,136 +1842,133 @@
     <t>Počet hodin</t>
   </si>
   <si>
+    <t>Výdaje</t>
+  </si>
+  <si>
+    <t>Benzín</t>
+  </si>
+  <si>
+    <t>Auta</t>
+  </si>
+  <si>
+    <t>Suroviny</t>
+  </si>
+  <si>
+    <t>Ostatní</t>
+  </si>
+  <si>
+    <t>PHM - soukromé</t>
+  </si>
+  <si>
+    <t>Zavíral</t>
+  </si>
+  <si>
+    <t>Zrušené obj. ks</t>
+  </si>
+  <si>
+    <t>Zrušené obj. $</t>
+  </si>
+  <si>
+    <t>Počet zpožděných našich rozvozů +5 min</t>
+  </si>
+  <si>
+    <t>Průměrný make Time</t>
+  </si>
+  <si>
+    <t>Počet rozvozů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vlastní vůz </t>
+  </si>
+  <si>
+    <t>Vyplatit PHM</t>
+  </si>
+  <si>
+    <t>počet výdajových dokadů</t>
+  </si>
+  <si>
+    <t>Počet nezrušených celkem</t>
+  </si>
+  <si>
+    <t>Počet našich rozvozů</t>
+  </si>
+  <si>
+    <t>Počet pozdě přiřazeným WoltDrive 5+</t>
+  </si>
+  <si>
+    <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
+  </si>
+  <si>
+    <t>% zpožděných našich rozvozů +5 min</t>
+  </si>
+  <si>
+    <t>Počet zpožděných Woltdrivem</t>
+  </si>
+  <si>
+    <t>% doručených včas</t>
+  </si>
+  <si>
+    <t>% zpožděných Woltdrivem</t>
+  </si>
+  <si>
+    <t>Wolt drive</t>
+  </si>
+  <si>
+    <t>Vyber datum    &lt;----------&gt;</t>
+  </si>
+  <si>
+    <t>Celkem hodin Instor</t>
+  </si>
+  <si>
+    <t>Celkem hodin Kurýr</t>
+  </si>
+  <si>
+    <t>Počet dní</t>
+  </si>
+  <si>
+    <t>Yarushynskyi Vladyslav</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>29:00</t>
+  </si>
+  <si>
+    <t>Vychivskyi Volodymyr</t>
+  </si>
+  <si>
+    <t>35:00</t>
+  </si>
+  <si>
+    <t>Šebesta Tomáš</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Nováková Adéla</t>
+  </si>
+  <si>
+    <t>26:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
     <t>Putna Jaroslav</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Výdaje</t>
-  </si>
-  <si>
-    <t>Nováková Adéla</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>Benzín</t>
-  </si>
-  <si>
-    <t>Auta</t>
-  </si>
-  <si>
-    <t>Suroviny</t>
-  </si>
-  <si>
-    <t>Ostatní</t>
-  </si>
-  <si>
-    <t>PHM - soukromé</t>
-  </si>
-  <si>
-    <t>Zavíral</t>
-  </si>
-  <si>
-    <t>Zrušené obj. ks</t>
-  </si>
-  <si>
-    <t>Zrušené obj. $</t>
-  </si>
-  <si>
-    <t>Počet zpožděných našich rozvozů +5 min</t>
-  </si>
-  <si>
-    <t>Průměrný make Time</t>
-  </si>
-  <si>
-    <t>Počet rozvozů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vlastní vůz </t>
-  </si>
-  <si>
-    <t>Vyplatit PHM</t>
-  </si>
-  <si>
-    <t>počet výdajových dokadů</t>
-  </si>
-  <si>
-    <t>Počet nezrušených celkem</t>
-  </si>
-  <si>
-    <t>Počet našich rozvozů</t>
-  </si>
-  <si>
-    <t>Počet pozdě přiřazeným WoltDrive 5+</t>
-  </si>
-  <si>
-    <t>Vychivskyi Volodymyr</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
-  </si>
-  <si>
-    <t>% zpožděných našich rozvozů +5 min</t>
-  </si>
-  <si>
-    <t>Počet zpožděných Woltdrivem</t>
-  </si>
-  <si>
-    <t>% doručených včas</t>
-  </si>
-  <si>
-    <t>% zpožděných Woltdrivem</t>
-  </si>
-  <si>
-    <t>Wolt drive</t>
-  </si>
-  <si>
-    <t>Vyber datum    &lt;----------&gt;</t>
-  </si>
-  <si>
-    <t>Celkem hodin Instor</t>
-  </si>
-  <si>
-    <t>Celkem hodin Kurýr</t>
-  </si>
-  <si>
-    <t>Počet dní</t>
-  </si>
-  <si>
-    <t>Yarushynskyi Vladyslav</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>29:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>Šebesta Tomáš</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
+    <t>16:00</t>
   </si>
   <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>10 min 13 s</t>
+    <t>11 min 09 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13250,7 +13247,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46177.0</v>
+        <v>46179.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13299,7 +13296,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Sobota</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -13458,9 +13455,7 @@
       <c r="F11" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="G11" s="45" t="s">
-        <v>607</v>
-      </c>
+      <c r="G11" s="45"/>
       <c r="I11" s="20"/>
       <c r="J11" s="46">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
@@ -13475,28 +13470,22 @@
     <row r="12">
       <c r="A12" s="49">
         <f t="array" ref="A12">IF(ISBLANK(B12), 0, IF(ISNUMBER(MATCH(B12, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B12, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B12, HR!B:B, 0)) * (F12 * 24), 0)))</f>
-        <v>2001.648</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>607</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>608</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>609</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B12" s="50"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="52"/>
       <c r="F12" s="53" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="I12" s="20"/>
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="54" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M12" s="18"/>
     </row>
@@ -13505,19 +13494,13 @@
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B13" s="50" t="s">
-        <v>611</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>609</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>612</v>
-      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="52"/>
       <c r="F13" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>07:00</v>
+        <v>0:00</v>
       </c>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
@@ -13525,7 +13508,7 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="22" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="M13" s="37"/>
     </row>
@@ -13547,7 +13530,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="57" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="M14" s="37"/>
     </row>
@@ -13568,7 +13551,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="57" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M15" s="37"/>
     </row>
@@ -13589,7 +13572,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="57" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="M16" s="37"/>
     </row>
@@ -13612,7 +13595,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="59" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="M17" s="60">
         <f>sum(I25:I31)</f>
@@ -13633,7 +13616,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="18"/>
@@ -13653,9 +13636,7 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="45" t="s">
-        <v>611</v>
-      </c>
+      <c r="G19" s="45"/>
       <c r="I19" s="20"/>
       <c r="M19" s="62"/>
     </row>
@@ -13704,16 +13685,16 @@
       <c r="H22" s="27"/>
       <c r="I22" s="18"/>
       <c r="J22" s="70" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="K22" s="70" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L22" s="71" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="M22" s="71" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23">
@@ -13757,46 +13738,40 @@
         <v>606</v>
       </c>
       <c r="G24" s="75" t="s">
+        <v>618</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>619</v>
+      </c>
+      <c r="I24" s="76" t="s">
+        <v>620</v>
+      </c>
+      <c r="J24" s="77" t="s">
+        <v>621</v>
+      </c>
+      <c r="K24" s="78" t="s">
+        <v>622</v>
+      </c>
+      <c r="L24" s="77" t="s">
         <v>623</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="M24" s="78" t="s">
         <v>624</v>
-      </c>
-      <c r="I24" s="76" t="s">
-        <v>625</v>
-      </c>
-      <c r="J24" s="77" t="s">
-        <v>626</v>
-      </c>
-      <c r="K24" s="78" t="s">
-        <v>627</v>
-      </c>
-      <c r="L24" s="77" t="s">
-        <v>628</v>
-      </c>
-      <c r="M24" s="78" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="49">
         <f t="array" ref="A25">IF(ISBLANK(B25), 0, IF(ISNUMBER(MATCH(B25, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B25, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B25, HR!B:B, 0)) * (F25 * 24), 0)))</f>
-        <v>3502.884</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>630</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>631</v>
-      </c>
-      <c r="D25" s="79" t="s">
-        <v>612</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
       <c r="E25" s="79"/>
       <c r="F25" s="80" t="str">
         <f t="shared" ref="F25:F31" si="2">IF(OR(ISBLANK(B25), ISBLANK(D25), D25=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))+1, TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))) - TIMEVALUE(IF(ISBLANK(C25), "00:00", C25)) - TIMEVALUE(IF(ISBLANK(E25), "00:00", E25))), "hh:mm"))
 </f>
-        <v>14:00</v>
+        <v>0:00</v>
       </c>
       <c r="G25" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B25)</f>
@@ -13880,14 +13855,14 @@
         <v>0</v>
       </c>
       <c r="J27" s="89" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="K27" s="90"/>
       <c r="L27" s="77" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="M27" s="78" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -13984,10 +13959,10 @@
       <c r="J30" s="96"/>
       <c r="K30" s="96"/>
       <c r="L30" s="78" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="M30" s="78" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31">
@@ -14025,7 +14000,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="99" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
@@ -14114,9 +14089,6 @@
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
       <formula1>"Hanibal Filip,Mikuš Pavel,Šmídová Sabina,Kormash Liubov,Vychivskyi Volodymyr,Hřebík Martin,Reischl Jan,Kulinič Michail,Kačena Stanislav"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G11 G19">
-      <formula1>"Putna Jaroslav,Nováková Adéla"</formula1>
-    </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -14149,7 +14121,7 @@
         <v>46174.0</v>
       </c>
       <c r="D1" s="108" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E1" s="109">
         <v>46203.0</v>
@@ -14177,18 +14149,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.3441024629731718</v>
+        <v>0.34931562507951885</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>58728.10999999999</v>
+        <v>124409.9</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>25378.1</v>
+        <v>47534.399999999994</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14210,7 +14182,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>15822.0</v>
+        <v>25868.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14230,20 +14202,20 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>5305.01</v>
+        <v>22021.5</v>
       </c>
       <c r="N4" s="116"/>
     </row>
     <row r="5">
       <c r="A5" s="121"/>
       <c r="B5" s="122" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="10"/>
       <c r="F5" s="123" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
@@ -14254,7 +14226,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>4430.0</v>
+        <v>12202.0</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14274,7 +14246,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>0.0</v>
+        <v>784.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14282,14 +14254,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>42</v>
+        <v>72.5</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14334,7 +14306,7 @@
         <v>602</v>
       </c>
       <c r="C9" s="138" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="D9" s="138" t="s">
         <v>606</v>
@@ -14344,51 +14316,51 @@
         <v>602</v>
       </c>
       <c r="G9" s="138" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="H9" s="138" t="s">
         <v>606</v>
       </c>
       <c r="I9" s="140" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>4.000000000003638</v>
+        <v>4.000000000007276</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>4042.0</v>
+        <v>9759.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="143"/>
       <c r="B10" s="144" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C10" s="145">
         <v>1.0</v>
       </c>
       <c r="D10" s="145" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="E10" s="146" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="F10" s="144" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="G10" s="145">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H10" s="145" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="I10" s="147">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14403,16 +14375,16 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="143"/>
       <c r="B11" s="144" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C11" s="145">
         <v>2.0</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="E11" s="146" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="F11" s="144"/>
       <c r="G11" s="145"/>
@@ -14424,23 +14396,23 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>3575.0</v>
+        <v>5615.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
       <c r="B12" s="144" t="s">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="C12" s="145">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F12" s="144"/>
       <c r="G12" s="145"/>
@@ -14449,18 +14421,24 @@
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="150" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="111"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
-      <c r="B13" s="144"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
+      <c r="B13" s="144" t="s">
+        <v>646</v>
+      </c>
+      <c r="C13" s="145">
+        <v>2.0</v>
+      </c>
+      <c r="D13" s="145" t="s">
+        <v>647</v>
+      </c>
       <c r="E13" s="146" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14469,7 +14447,7 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="142" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="M13" s="120">
         <v>0.0</v>
@@ -14482,7 +14460,7 @@
       <c r="C14" s="145"/>
       <c r="D14" s="145"/>
       <c r="E14" s="146" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14491,7 +14469,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="151" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="M14" s="120">
         <v>0.0</v>
@@ -14504,7 +14482,7 @@
       <c r="C15" s="145"/>
       <c r="D15" s="145"/>
       <c r="E15" s="146" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14513,7 +14491,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="151" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M15" s="120">
         <v>0.0</v>
@@ -14533,7 +14511,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="151" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="M16" s="120">
         <v>0.0</v>
@@ -14553,10 +14531,10 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="153" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>180.0</v>
+        <v>630.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14587,16 +14565,16 @@
       <c r="H19" s="145"/>
       <c r="I19" s="147"/>
       <c r="J19" s="157" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="K19" s="158" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L19" s="159" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="M19" s="160" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="N19" s="161"/>
     </row>
@@ -14627,16 +14605,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
+        <v>4.0</v>
+      </c>
+      <c r="K21" s="165">
+        <v>2868.0</v>
+      </c>
+      <c r="L21" s="166">
         <v>1.0</v>
       </c>
-      <c r="K21" s="165">
-        <v>817.0</v>
-      </c>
-      <c r="L21" s="166">
-        <v>0.0</v>
-      </c>
       <c r="M21" s="167" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14651,16 +14629,16 @@
       <c r="H22" s="145"/>
       <c r="I22" s="147"/>
       <c r="J22" s="168" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="K22" s="169" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="L22" s="170" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="M22" s="171" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="N22" s="156"/>
     </row>
@@ -14691,16 +14669,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K24" s="166">
-        <v>130.0</v>
+        <v>293.0</v>
       </c>
       <c r="L24" s="166">
-        <v>11.0</v>
+        <v>29.0</v>
       </c>
       <c r="M24" s="173">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14715,14 +14693,14 @@
       <c r="H25" s="145"/>
       <c r="I25" s="147"/>
       <c r="J25" s="174" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="K25" s="90"/>
       <c r="L25" s="175" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="M25" s="176" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="N25" s="156"/>
     </row>
@@ -14757,10 +14735,10 @@
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.0</v>
+        <v>0.03125</v>
       </c>
       <c r="M27" s="180">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14776,10 +14754,10 @@
       <c r="I28" s="147"/>
       <c r="J28" s="181"/>
       <c r="L28" s="182" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="M28" s="176" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="N28" s="156"/>
     </row>
@@ -14811,10 +14789,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>1.0</v>
+        <v>0.96875</v>
       </c>
       <c r="M30" s="184">
-        <v>0.0</v>
+        <v>0.03125</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14960,7 +14938,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="186"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="185"/>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -15028,7 +15006,7 @@
       <c r="B5" s="186"/>
       <c r="C5" s="186"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="E5" s="185"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -15062,7 +15040,7 @@
       <c r="B6" s="4"/>
       <c r="C6" s="186"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="185"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -15087,6 +15065,7 @@
       <c r="AA6" s="185"/>
       <c r="AB6" s="185"/>
       <c r="AC6" s="185"/>
+      <c r="AD6" s="185"/>
       <c r="AE6" s="185"/>
       <c r="AF6" s="185"/>
     </row>
@@ -15095,7 +15074,7 @@
       <c r="B7" s="4"/>
       <c r="C7" s="186"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="185"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -15129,7 +15108,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="186"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="185"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -15163,7 +15142,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="186"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="185"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -15231,7 +15210,7 @@
       <c r="B11" s="4"/>
       <c r="C11" s="186"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="185"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -15298,7 +15277,7 @@
       <c r="B13" s="4"/>
       <c r="C13" s="186"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="185"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -15332,7 +15311,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="186"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="185"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -15366,7 +15345,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="186"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="185"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -15400,7 +15379,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="186"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="185"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -15434,13 +15413,13 @@
       <c r="B17" s="186"/>
       <c r="C17" s="186"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="185"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="185"/>
+      <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -15468,7 +15447,7 @@
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="185"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -15502,7 +15481,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="186"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="185"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -15536,7 +15515,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="186"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="185"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -15570,16 +15549,16 @@
       <c r="B21" s="4"/>
       <c r="C21" s="186"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="185"/>
+      <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="185"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="185"/>
+      <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="185"/>
@@ -15740,7 +15719,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="185"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15807,13 +15786,13 @@
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="185"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="185"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
@@ -15875,13 +15854,13 @@
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="185"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="185"/>
+      <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
@@ -15909,7 +15888,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="186"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="185"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -15949,7 +15928,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
+      <c r="K32" s="185"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
@@ -16045,7 +16024,7 @@
       <c r="B35" s="186"/>
       <c r="C35" s="186"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="185"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -16079,7 +16058,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="186"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="185"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -16113,7 +16092,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="186"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="185"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -16153,7 +16132,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
+      <c r="K38" s="185"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
@@ -16181,7 +16160,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="185"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -16283,7 +16262,7 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="185"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -16385,7 +16364,7 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="185"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -16419,13 +16398,13 @@
       <c r="B46" s="4"/>
       <c r="C46" s="186"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="185"/>
+      <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
-      <c r="K46" s="185"/>
+      <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -16487,7 +16466,7 @@
       <c r="B48" s="4"/>
       <c r="C48" s="186"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="185"/>
+      <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -16521,13 +16500,13 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="185"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
+      <c r="K49" s="185"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -16589,13 +16568,13 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="185"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
+      <c r="K51" s="185"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
@@ -16657,13 +16636,13 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="185"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
-      <c r="K53" s="185"/>
+      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
@@ -16691,7 +16670,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="186"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="185"/>
+      <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -16725,13 +16704,13 @@
       <c r="B55" s="4"/>
       <c r="C55" s="186"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
+      <c r="E55" s="185"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
+      <c r="K55" s="185"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
@@ -16827,13 +16806,13 @@
       <c r="B58" s="4"/>
       <c r="C58" s="186"/>
       <c r="D58" s="4"/>
-      <c r="E58" s="185"/>
+      <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
-      <c r="K58" s="185"/>
+      <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
@@ -16929,13 +16908,13 @@
       <c r="B61" s="4"/>
       <c r="C61" s="186"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="185"/>
+      <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-      <c r="K61" s="185"/>
+      <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
@@ -16963,13 +16942,13 @@
       <c r="B62" s="4"/>
       <c r="C62" s="186"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="185"/>
+      <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-      <c r="K62" s="185"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
@@ -17031,7 +17010,7 @@
       <c r="B64" s="4"/>
       <c r="C64" s="186"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="185"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -17090,6 +17069,7 @@
       <c r="AA65" s="185"/>
       <c r="AB65" s="185"/>
       <c r="AC65" s="185"/>
+      <c r="AD65" s="185"/>
       <c r="AE65" s="185"/>
       <c r="AF65" s="185"/>
     </row>
@@ -17098,7 +17078,7 @@
       <c r="B66" s="4"/>
       <c r="C66" s="186"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
+      <c r="E66" s="185"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -17132,7 +17112,7 @@
       <c r="B67" s="4"/>
       <c r="C67" s="186"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="185"/>
+      <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -17199,13 +17179,13 @@
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="185"/>
+      <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-      <c r="K69" s="185"/>
+      <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -17233,7 +17213,7 @@
       <c r="B70" s="4"/>
       <c r="C70" s="186"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="185"/>
+      <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -17339,7 +17319,7 @@
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-      <c r="K73" s="185"/>
+      <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
@@ -17373,7 +17353,7 @@
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-      <c r="K74" s="185"/>
+      <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -17509,7 +17489,7 @@
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
+      <c r="K78" s="185"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
@@ -17537,7 +17517,7 @@
       <c r="B79" s="4"/>
       <c r="C79" s="186"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
+      <c r="E79" s="185"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -17571,7 +17551,7 @@
       <c r="B80" s="4"/>
       <c r="C80" s="186"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="185"/>
+      <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
@@ -17605,13 +17585,13 @@
       <c r="B81" s="4"/>
       <c r="C81" s="186"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
+      <c r="E81" s="185"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
+      <c r="K81" s="185"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
@@ -17635,22 +17615,22 @@
       <c r="AF81" s="185"/>
     </row>
     <row r="82">
-      <c r="A82" s="185"/>
-      <c r="B82" s="185"/>
-      <c r="C82" s="185"/>
-      <c r="D82" s="185"/>
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
       <c r="E82" s="185"/>
-      <c r="F82" s="185"/>
-      <c r="G82" s="185"/>
-      <c r="H82" s="185"/>
-      <c r="I82" s="185"/>
-      <c r="J82" s="185"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
       <c r="K82" s="185"/>
-      <c r="L82" s="185"/>
-      <c r="M82" s="185"/>
-      <c r="N82" s="185"/>
-      <c r="O82" s="185"/>
-      <c r="P82" s="185"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
       <c r="Q82" s="185"/>
       <c r="R82" s="185"/>
       <c r="S82" s="185"/>
@@ -17669,22 +17649,22 @@
       <c r="AF82" s="185"/>
     </row>
     <row r="83">
-      <c r="A83" s="185"/>
-      <c r="B83" s="185"/>
-      <c r="C83" s="185"/>
-      <c r="D83" s="185"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
       <c r="E83" s="185"/>
-      <c r="F83" s="185"/>
-      <c r="G83" s="185"/>
-      <c r="H83" s="185"/>
-      <c r="I83" s="185"/>
-      <c r="J83" s="185"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
       <c r="K83" s="185"/>
-      <c r="L83" s="185"/>
-      <c r="M83" s="185"/>
-      <c r="N83" s="185"/>
-      <c r="O83" s="185"/>
-      <c r="P83" s="185"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
       <c r="Q83" s="185"/>
       <c r="R83" s="185"/>
       <c r="S83" s="185"/>
@@ -17703,22 +17683,22 @@
       <c r="AF83" s="185"/>
     </row>
     <row r="84">
-      <c r="A84" s="185"/>
-      <c r="B84" s="185"/>
-      <c r="C84" s="187"/>
-      <c r="D84" s="185"/>
-      <c r="E84" s="185"/>
-      <c r="F84" s="185"/>
-      <c r="G84" s="185"/>
-      <c r="H84" s="185"/>
-      <c r="I84" s="185"/>
-      <c r="J84" s="185"/>
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="186"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
       <c r="K84" s="185"/>
-      <c r="L84" s="185"/>
-      <c r="M84" s="185"/>
-      <c r="N84" s="185"/>
-      <c r="O84" s="185"/>
-      <c r="P84" s="185"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
       <c r="Q84" s="185"/>
       <c r="R84" s="185"/>
       <c r="S84" s="185"/>
@@ -17737,22 +17717,22 @@
       <c r="AF84" s="185"/>
     </row>
     <row r="85">
-      <c r="A85" s="185"/>
-      <c r="B85" s="185"/>
-      <c r="C85" s="187"/>
-      <c r="D85" s="185"/>
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="186"/>
+      <c r="D85" s="4"/>
       <c r="E85" s="185"/>
-      <c r="F85" s="185"/>
-      <c r="G85" s="185"/>
-      <c r="H85" s="185"/>
-      <c r="I85" s="185"/>
-      <c r="J85" s="185"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
       <c r="K85" s="185"/>
-      <c r="L85" s="185"/>
-      <c r="M85" s="185"/>
-      <c r="N85" s="185"/>
-      <c r="O85" s="185"/>
-      <c r="P85" s="185"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
       <c r="Q85" s="185"/>
       <c r="R85" s="185"/>
       <c r="S85" s="185"/>
@@ -17766,26 +17746,27 @@
       <c r="AA85" s="185"/>
       <c r="AB85" s="185"/>
       <c r="AC85" s="185"/>
+      <c r="AD85" s="185"/>
       <c r="AE85" s="185"/>
       <c r="AF85" s="185"/>
     </row>
     <row r="86">
-      <c r="A86" s="185"/>
-      <c r="B86" s="185"/>
-      <c r="C86" s="187"/>
-      <c r="D86" s="185"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="186"/>
+      <c r="D86" s="4"/>
       <c r="E86" s="185"/>
-      <c r="F86" s="185"/>
-      <c r="G86" s="185"/>
-      <c r="H86" s="185"/>
-      <c r="I86" s="185"/>
-      <c r="J86" s="185"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
       <c r="K86" s="185"/>
-      <c r="L86" s="185"/>
-      <c r="M86" s="185"/>
-      <c r="N86" s="185"/>
-      <c r="O86" s="185"/>
-      <c r="P86" s="185"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
       <c r="Q86" s="185"/>
       <c r="R86" s="185"/>
       <c r="S86" s="185"/>
@@ -17804,22 +17785,22 @@
       <c r="AF86" s="185"/>
     </row>
     <row r="87">
-      <c r="A87" s="185"/>
-      <c r="B87" s="185"/>
-      <c r="C87" s="187"/>
-      <c r="D87" s="185"/>
-      <c r="E87" s="185"/>
-      <c r="F87" s="185"/>
-      <c r="G87" s="185"/>
-      <c r="H87" s="185"/>
-      <c r="I87" s="185"/>
-      <c r="J87" s="185"/>
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="186"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
       <c r="K87" s="185"/>
-      <c r="L87" s="185"/>
-      <c r="M87" s="185"/>
-      <c r="N87" s="185"/>
-      <c r="O87" s="185"/>
-      <c r="P87" s="185"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
       <c r="Q87" s="185"/>
       <c r="R87" s="185"/>
       <c r="S87" s="185"/>
@@ -17838,22 +17819,22 @@
       <c r="AF87" s="185"/>
     </row>
     <row r="88">
-      <c r="A88" s="185"/>
-      <c r="B88" s="185"/>
-      <c r="C88" s="187"/>
-      <c r="D88" s="185"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="186"/>
+      <c r="D88" s="4"/>
       <c r="E88" s="185"/>
-      <c r="F88" s="185"/>
-      <c r="G88" s="185"/>
-      <c r="H88" s="185"/>
-      <c r="I88" s="185"/>
-      <c r="J88" s="185"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
       <c r="K88" s="185"/>
-      <c r="L88" s="185"/>
-      <c r="M88" s="185"/>
-      <c r="N88" s="185"/>
-      <c r="O88" s="185"/>
-      <c r="P88" s="185"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
       <c r="Q88" s="185"/>
       <c r="R88" s="185"/>
       <c r="S88" s="185"/>
@@ -17871,22 +17852,22 @@
       <c r="AF88" s="185"/>
     </row>
     <row r="89">
-      <c r="A89" s="185"/>
-      <c r="B89" s="185"/>
-      <c r="C89" s="187"/>
-      <c r="D89" s="185"/>
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="186"/>
+      <c r="D89" s="4"/>
       <c r="E89" s="185"/>
-      <c r="F89" s="185"/>
-      <c r="G89" s="185"/>
-      <c r="H89" s="185"/>
-      <c r="I89" s="185"/>
-      <c r="J89" s="185"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
       <c r="K89" s="185"/>
-      <c r="L89" s="185"/>
-      <c r="M89" s="185"/>
-      <c r="N89" s="185"/>
-      <c r="O89" s="185"/>
-      <c r="P89" s="185"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4"/>
       <c r="Q89" s="185"/>
       <c r="R89" s="185"/>
       <c r="S89" s="185"/>
@@ -17904,22 +17885,22 @@
       <c r="AF89" s="185"/>
     </row>
     <row r="90">
-      <c r="A90" s="185"/>
-      <c r="B90" s="185"/>
-      <c r="C90" s="187"/>
-      <c r="D90" s="185"/>
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="186"/>
+      <c r="D90" s="4"/>
       <c r="E90" s="185"/>
-      <c r="F90" s="185"/>
-      <c r="G90" s="185"/>
-      <c r="H90" s="185"/>
-      <c r="I90" s="185"/>
-      <c r="J90" s="185"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
       <c r="K90" s="185"/>
-      <c r="L90" s="185"/>
-      <c r="M90" s="185"/>
-      <c r="N90" s="185"/>
-      <c r="O90" s="185"/>
-      <c r="P90" s="185"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
       <c r="Q90" s="185"/>
       <c r="R90" s="185"/>
       <c r="S90" s="185"/>
@@ -17937,22 +17918,22 @@
       <c r="AF90" s="185"/>
     </row>
     <row r="91">
-      <c r="A91" s="185"/>
-      <c r="B91" s="185"/>
-      <c r="C91" s="185"/>
-      <c r="D91" s="185"/>
-      <c r="E91" s="185"/>
-      <c r="F91" s="185"/>
-      <c r="G91" s="185"/>
-      <c r="H91" s="185"/>
-      <c r="I91" s="185"/>
-      <c r="J91" s="185"/>
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
       <c r="K91" s="185"/>
-      <c r="L91" s="185"/>
-      <c r="M91" s="185"/>
-      <c r="N91" s="185"/>
-      <c r="O91" s="185"/>
-      <c r="P91" s="185"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
       <c r="Q91" s="185"/>
       <c r="R91" s="185"/>
       <c r="S91" s="185"/>
@@ -17970,22 +17951,22 @@
       <c r="AF91" s="185"/>
     </row>
     <row r="92">
-      <c r="A92" s="185"/>
-      <c r="B92" s="185"/>
-      <c r="C92" s="185"/>
-      <c r="D92" s="185"/>
-      <c r="E92" s="185"/>
-      <c r="F92" s="185"/>
-      <c r="G92" s="185"/>
-      <c r="H92" s="185"/>
-      <c r="I92" s="185"/>
-      <c r="J92" s="185"/>
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
       <c r="K92" s="185"/>
-      <c r="L92" s="185"/>
-      <c r="M92" s="185"/>
-      <c r="N92" s="185"/>
-      <c r="O92" s="185"/>
-      <c r="P92" s="185"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
       <c r="Q92" s="185"/>
       <c r="R92" s="185"/>
       <c r="S92" s="185"/>
@@ -18003,22 +17984,22 @@
       <c r="AF92" s="185"/>
     </row>
     <row r="93">
-      <c r="A93" s="185"/>
-      <c r="B93" s="185"/>
-      <c r="C93" s="185"/>
-      <c r="D93" s="185"/>
-      <c r="E93" s="185"/>
-      <c r="F93" s="185"/>
-      <c r="G93" s="185"/>
-      <c r="H93" s="185"/>
-      <c r="I93" s="185"/>
-      <c r="J93" s="185"/>
-      <c r="K93" s="185"/>
-      <c r="L93" s="185"/>
-      <c r="M93" s="185"/>
-      <c r="N93" s="185"/>
-      <c r="O93" s="185"/>
-      <c r="P93" s="185"/>
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
       <c r="Q93" s="185"/>
       <c r="R93" s="185"/>
       <c r="S93" s="185"/>
@@ -18037,22 +18018,22 @@
       <c r="AF93" s="185"/>
     </row>
     <row r="94">
-      <c r="A94" s="185"/>
-      <c r="B94" s="185"/>
-      <c r="C94" s="185"/>
-      <c r="D94" s="185"/>
-      <c r="E94" s="185"/>
-      <c r="F94" s="185"/>
-      <c r="G94" s="185"/>
-      <c r="H94" s="185"/>
-      <c r="I94" s="185"/>
-      <c r="J94" s="185"/>
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
       <c r="K94" s="185"/>
-      <c r="L94" s="185"/>
-      <c r="M94" s="185"/>
-      <c r="N94" s="185"/>
-      <c r="O94" s="185"/>
-      <c r="P94" s="185"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
       <c r="Q94" s="185"/>
       <c r="R94" s="185"/>
       <c r="S94" s="185"/>
@@ -18070,22 +18051,22 @@
       <c r="AF94" s="185"/>
     </row>
     <row r="95">
-      <c r="A95" s="185"/>
-      <c r="B95" s="185"/>
-      <c r="C95" s="185"/>
-      <c r="D95" s="185"/>
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
       <c r="E95" s="185"/>
-      <c r="F95" s="185"/>
-      <c r="G95" s="185"/>
-      <c r="H95" s="185"/>
-      <c r="I95" s="185"/>
-      <c r="J95" s="185"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
       <c r="K95" s="185"/>
-      <c r="L95" s="185"/>
-      <c r="M95" s="185"/>
-      <c r="N95" s="185"/>
-      <c r="O95" s="185"/>
-      <c r="P95" s="185"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
       <c r="Q95" s="185"/>
       <c r="R95" s="185"/>
       <c r="S95" s="185"/>
@@ -18103,22 +18084,22 @@
       <c r="AF95" s="185"/>
     </row>
     <row r="96">
-      <c r="A96" s="185"/>
-      <c r="B96" s="185"/>
-      <c r="C96" s="185"/>
-      <c r="D96" s="185"/>
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
       <c r="E96" s="185"/>
-      <c r="F96" s="185"/>
-      <c r="G96" s="185"/>
-      <c r="H96" s="185"/>
-      <c r="I96" s="185"/>
-      <c r="J96" s="185"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
       <c r="K96" s="185"/>
-      <c r="L96" s="185"/>
-      <c r="M96" s="185"/>
-      <c r="N96" s="185"/>
-      <c r="O96" s="185"/>
-      <c r="P96" s="185"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
       <c r="Q96" s="185"/>
       <c r="R96" s="185"/>
       <c r="S96" s="185"/>
@@ -18136,22 +18117,22 @@
       <c r="AF96" s="185"/>
     </row>
     <row r="97">
-      <c r="A97" s="185"/>
-      <c r="B97" s="185"/>
-      <c r="C97" s="185"/>
-      <c r="D97" s="185"/>
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
       <c r="E97" s="185"/>
-      <c r="F97" s="185"/>
-      <c r="G97" s="185"/>
-      <c r="H97" s="185"/>
-      <c r="I97" s="185"/>
-      <c r="J97" s="185"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
       <c r="K97" s="185"/>
-      <c r="L97" s="185"/>
-      <c r="M97" s="185"/>
-      <c r="N97" s="185"/>
-      <c r="O97" s="185"/>
-      <c r="P97" s="185"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
       <c r="Q97" s="185"/>
       <c r="R97" s="185"/>
       <c r="S97" s="185"/>
@@ -18170,22 +18151,22 @@
       <c r="AF97" s="185"/>
     </row>
     <row r="98">
-      <c r="A98" s="185"/>
-      <c r="B98" s="185"/>
-      <c r="C98" s="185"/>
-      <c r="D98" s="185"/>
-      <c r="E98" s="185"/>
-      <c r="F98" s="185"/>
-      <c r="G98" s="185"/>
-      <c r="H98" s="185"/>
-      <c r="I98" s="185"/>
-      <c r="J98" s="185"/>
-      <c r="K98" s="185"/>
-      <c r="L98" s="185"/>
-      <c r="M98" s="185"/>
-      <c r="N98" s="185"/>
-      <c r="O98" s="185"/>
-      <c r="P98" s="185"/>
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
       <c r="Q98" s="185"/>
       <c r="R98" s="185"/>
       <c r="S98" s="185"/>
@@ -18203,22 +18184,22 @@
       <c r="AF98" s="185"/>
     </row>
     <row r="99">
-      <c r="A99" s="185"/>
-      <c r="B99" s="185"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="185"/>
-      <c r="E99" s="185"/>
-      <c r="F99" s="185"/>
-      <c r="G99" s="185"/>
-      <c r="H99" s="185"/>
-      <c r="I99" s="185"/>
-      <c r="J99" s="185"/>
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="186"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
       <c r="K99" s="185"/>
-      <c r="L99" s="185"/>
-      <c r="M99" s="185"/>
-      <c r="N99" s="185"/>
-      <c r="O99" s="185"/>
-      <c r="P99" s="185"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
       <c r="Q99" s="185"/>
       <c r="R99" s="185"/>
       <c r="S99" s="185"/>
@@ -18237,22 +18218,22 @@
       <c r="AF99" s="185"/>
     </row>
     <row r="100">
-      <c r="A100" s="185"/>
-      <c r="B100" s="185"/>
-      <c r="C100" s="187"/>
-      <c r="D100" s="185"/>
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="186"/>
+      <c r="D100" s="4"/>
       <c r="E100" s="185"/>
-      <c r="F100" s="185"/>
-      <c r="G100" s="185"/>
-      <c r="H100" s="185"/>
-      <c r="I100" s="185"/>
-      <c r="J100" s="185"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
       <c r="K100" s="185"/>
-      <c r="L100" s="185"/>
-      <c r="M100" s="185"/>
-      <c r="N100" s="185"/>
-      <c r="O100" s="185"/>
-      <c r="P100" s="185"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
       <c r="Q100" s="185"/>
       <c r="R100" s="185"/>
       <c r="S100" s="185"/>
@@ -18270,22 +18251,22 @@
       <c r="AF100" s="185"/>
     </row>
     <row r="101">
-      <c r="A101" s="185"/>
-      <c r="B101" s="185"/>
-      <c r="C101" s="185"/>
-      <c r="D101" s="185"/>
-      <c r="E101" s="185"/>
-      <c r="F101" s="185"/>
-      <c r="G101" s="185"/>
-      <c r="H101" s="185"/>
-      <c r="I101" s="185"/>
-      <c r="J101" s="185"/>
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
       <c r="K101" s="185"/>
-      <c r="L101" s="185"/>
-      <c r="M101" s="185"/>
-      <c r="N101" s="185"/>
-      <c r="O101" s="185"/>
-      <c r="P101" s="185"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
       <c r="Q101" s="185"/>
       <c r="R101" s="185"/>
       <c r="S101" s="185"/>
@@ -18303,22 +18284,22 @@
       <c r="AF101" s="185"/>
     </row>
     <row r="102">
-      <c r="A102" s="185"/>
-      <c r="B102" s="185"/>
-      <c r="C102" s="187"/>
-      <c r="D102" s="185"/>
-      <c r="E102" s="185"/>
-      <c r="F102" s="185"/>
-      <c r="G102" s="185"/>
-      <c r="H102" s="185"/>
-      <c r="I102" s="185"/>
-      <c r="J102" s="185"/>
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="186"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
       <c r="K102" s="185"/>
-      <c r="L102" s="185"/>
-      <c r="M102" s="185"/>
-      <c r="N102" s="185"/>
-      <c r="O102" s="185"/>
-      <c r="P102" s="185"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
       <c r="Q102" s="185"/>
       <c r="S102" s="185"/>
       <c r="T102" s="185"/>
@@ -18334,22 +18315,22 @@
       <c r="AF102" s="185"/>
     </row>
     <row r="103">
-      <c r="A103" s="185"/>
-      <c r="B103" s="185"/>
-      <c r="C103" s="187"/>
-      <c r="D103" s="185"/>
-      <c r="E103" s="185"/>
-      <c r="F103" s="185"/>
-      <c r="G103" s="185"/>
-      <c r="H103" s="185"/>
-      <c r="I103" s="185"/>
-      <c r="J103" s="185"/>
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="186"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
       <c r="K103" s="185"/>
-      <c r="L103" s="185"/>
-      <c r="M103" s="185"/>
-      <c r="N103" s="185"/>
-      <c r="O103" s="185"/>
-      <c r="P103" s="185"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
       <c r="Q103" s="185"/>
       <c r="R103" s="185"/>
       <c r="S103" s="185"/>
@@ -18368,22 +18349,22 @@
       <c r="AF103" s="185"/>
     </row>
     <row r="104">
-      <c r="A104" s="185"/>
-      <c r="B104" s="185"/>
-      <c r="C104" s="185"/>
-      <c r="D104" s="185"/>
-      <c r="E104" s="185"/>
-      <c r="F104" s="185"/>
-      <c r="G104" s="185"/>
-      <c r="H104" s="185"/>
-      <c r="I104" s="185"/>
-      <c r="J104" s="185"/>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
       <c r="K104" s="185"/>
-      <c r="L104" s="185"/>
-      <c r="M104" s="185"/>
-      <c r="N104" s="185"/>
-      <c r="O104" s="185"/>
-      <c r="P104" s="185"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
       <c r="Q104" s="185"/>
       <c r="R104" s="185"/>
       <c r="S104" s="185"/>
@@ -18401,22 +18382,22 @@
       <c r="AF104" s="185"/>
     </row>
     <row r="105">
-      <c r="A105" s="185"/>
-      <c r="B105" s="185"/>
-      <c r="C105" s="187"/>
-      <c r="D105" s="185"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="186"/>
+      <c r="D105" s="4"/>
       <c r="E105" s="185"/>
-      <c r="F105" s="185"/>
-      <c r="G105" s="185"/>
-      <c r="H105" s="185"/>
-      <c r="I105" s="185"/>
-      <c r="J105" s="185"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
       <c r="K105" s="185"/>
-      <c r="L105" s="185"/>
-      <c r="M105" s="185"/>
-      <c r="N105" s="185"/>
-      <c r="O105" s="185"/>
-      <c r="P105" s="185"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
       <c r="Q105" s="185"/>
       <c r="R105" s="185"/>
       <c r="S105" s="185"/>
@@ -18435,22 +18416,22 @@
       <c r="AF105" s="185"/>
     </row>
     <row r="106">
-      <c r="A106" s="185"/>
-      <c r="B106" s="185"/>
-      <c r="C106" s="185"/>
-      <c r="D106" s="185"/>
-      <c r="E106" s="185"/>
-      <c r="F106" s="185"/>
-      <c r="G106" s="185"/>
-      <c r="H106" s="185"/>
-      <c r="I106" s="185"/>
-      <c r="J106" s="185"/>
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
       <c r="K106" s="185"/>
-      <c r="L106" s="185"/>
-      <c r="M106" s="185"/>
-      <c r="N106" s="185"/>
-      <c r="O106" s="185"/>
-      <c r="P106" s="185"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
       <c r="Q106" s="185"/>
       <c r="R106" s="185"/>
       <c r="S106" s="185"/>
@@ -18469,22 +18450,22 @@
       <c r="AF106" s="185"/>
     </row>
     <row r="107">
-      <c r="A107" s="185"/>
-      <c r="B107" s="185"/>
-      <c r="C107" s="185"/>
-      <c r="D107" s="185"/>
-      <c r="E107" s="185"/>
-      <c r="F107" s="185"/>
-      <c r="G107" s="185"/>
-      <c r="H107" s="185"/>
-      <c r="I107" s="185"/>
-      <c r="J107" s="185"/>
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
       <c r="K107" s="185"/>
-      <c r="L107" s="185"/>
-      <c r="M107" s="185"/>
-      <c r="N107" s="185"/>
-      <c r="O107" s="185"/>
-      <c r="P107" s="185"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
       <c r="Q107" s="185"/>
       <c r="R107" s="185"/>
       <c r="S107" s="185"/>
@@ -18502,22 +18483,22 @@
       <c r="AF107" s="185"/>
     </row>
     <row r="108">
-      <c r="A108" s="185"/>
-      <c r="B108" s="185"/>
-      <c r="C108" s="185"/>
-      <c r="D108" s="185"/>
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="186"/>
+      <c r="D108" s="4"/>
       <c r="E108" s="185"/>
-      <c r="F108" s="185"/>
-      <c r="G108" s="185"/>
-      <c r="H108" s="185"/>
-      <c r="I108" s="185"/>
-      <c r="J108" s="185"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
       <c r="K108" s="185"/>
-      <c r="L108" s="185"/>
-      <c r="M108" s="185"/>
-      <c r="N108" s="185"/>
-      <c r="O108" s="185"/>
-      <c r="P108" s="185"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
       <c r="Q108" s="185"/>
       <c r="R108" s="185"/>
       <c r="S108" s="185"/>
@@ -18536,22 +18517,22 @@
       <c r="AF108" s="185"/>
     </row>
     <row r="109">
-      <c r="A109" s="185"/>
-      <c r="B109" s="185"/>
-      <c r="C109" s="185"/>
-      <c r="D109" s="185"/>
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
       <c r="E109" s="185"/>
-      <c r="F109" s="185"/>
-      <c r="G109" s="185"/>
-      <c r="H109" s="185"/>
-      <c r="I109" s="185"/>
-      <c r="J109" s="185"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
       <c r="K109" s="185"/>
-      <c r="L109" s="185"/>
-      <c r="M109" s="185"/>
-      <c r="N109" s="185"/>
-      <c r="O109" s="185"/>
-      <c r="P109" s="185"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
       <c r="Q109" s="185"/>
       <c r="R109" s="185"/>
       <c r="S109" s="185"/>
@@ -18569,22 +18550,22 @@
       <c r="AF109" s="185"/>
     </row>
     <row r="110">
-      <c r="A110" s="185"/>
-      <c r="B110" s="185"/>
-      <c r="C110" s="187"/>
-      <c r="D110" s="185"/>
-      <c r="E110" s="185"/>
-      <c r="F110" s="185"/>
-      <c r="G110" s="185"/>
-      <c r="H110" s="185"/>
-      <c r="I110" s="185"/>
-      <c r="J110" s="185"/>
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="186"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
       <c r="K110" s="185"/>
-      <c r="L110" s="185"/>
-      <c r="M110" s="185"/>
-      <c r="N110" s="185"/>
-      <c r="O110" s="185"/>
-      <c r="P110" s="185"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
       <c r="Q110" s="185"/>
       <c r="S110" s="185"/>
       <c r="T110" s="185"/>
@@ -18600,22 +18581,22 @@
       <c r="AF110" s="185"/>
     </row>
     <row r="111">
-      <c r="A111" s="185"/>
-      <c r="B111" s="185"/>
-      <c r="C111" s="185"/>
-      <c r="D111" s="185"/>
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
       <c r="E111" s="185"/>
-      <c r="F111" s="185"/>
-      <c r="G111" s="185"/>
-      <c r="H111" s="185"/>
-      <c r="I111" s="185"/>
-      <c r="J111" s="185"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
       <c r="K111" s="185"/>
-      <c r="L111" s="185"/>
-      <c r="M111" s="185"/>
-      <c r="N111" s="185"/>
-      <c r="O111" s="185"/>
-      <c r="P111" s="185"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
       <c r="Q111" s="185"/>
       <c r="S111" s="185"/>
       <c r="T111" s="185"/>
@@ -18631,22 +18612,22 @@
       <c r="AF111" s="185"/>
     </row>
     <row r="112">
-      <c r="A112" s="185"/>
-      <c r="B112" s="185"/>
-      <c r="C112" s="185"/>
-      <c r="D112" s="185"/>
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
       <c r="E112" s="185"/>
-      <c r="F112" s="185"/>
-      <c r="G112" s="185"/>
-      <c r="H112" s="185"/>
-      <c r="I112" s="185"/>
-      <c r="J112" s="185"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
       <c r="K112" s="185"/>
-      <c r="L112" s="185"/>
-      <c r="M112" s="185"/>
-      <c r="N112" s="185"/>
-      <c r="O112" s="185"/>
-      <c r="P112" s="185"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
       <c r="Q112" s="185"/>
       <c r="S112" s="185"/>
       <c r="T112" s="185"/>
@@ -18662,22 +18643,22 @@
       <c r="AF112" s="185"/>
     </row>
     <row r="113">
-      <c r="A113" s="185"/>
-      <c r="B113" s="185"/>
-      <c r="C113" s="187"/>
-      <c r="D113" s="185"/>
-      <c r="E113" s="185"/>
-      <c r="F113" s="185"/>
-      <c r="G113" s="185"/>
-      <c r="H113" s="185"/>
-      <c r="I113" s="185"/>
-      <c r="J113" s="185"/>
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="186"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
       <c r="K113" s="185"/>
-      <c r="L113" s="185"/>
-      <c r="M113" s="185"/>
-      <c r="N113" s="185"/>
-      <c r="O113" s="185"/>
-      <c r="P113" s="185"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
       <c r="Q113" s="185"/>
       <c r="S113" s="185"/>
       <c r="T113" s="185"/>
@@ -18693,22 +18674,22 @@
       <c r="AF113" s="185"/>
     </row>
     <row r="114">
-      <c r="A114" s="185"/>
-      <c r="B114" s="185"/>
-      <c r="C114" s="185"/>
-      <c r="D114" s="185"/>
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
       <c r="E114" s="185"/>
-      <c r="F114" s="185"/>
-      <c r="G114" s="185"/>
-      <c r="H114" s="185"/>
-      <c r="I114" s="185"/>
-      <c r="J114" s="185"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
       <c r="K114" s="185"/>
-      <c r="L114" s="185"/>
-      <c r="M114" s="185"/>
-      <c r="N114" s="185"/>
-      <c r="O114" s="185"/>
-      <c r="P114" s="185"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
       <c r="Q114" s="185"/>
       <c r="R114" s="185"/>
       <c r="S114" s="185"/>
@@ -19115,8 +19096,8 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="189">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),31.0)</f>
-        <v>31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),30.0)</f>
+        <v>30</v>
       </c>
       <c r="W1" s="190" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"dní")</f>
@@ -19217,10 +19198,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
+        <v>650</v>
+      </c>
+      <c r="B4" s="191" t="s">
         <v>651</v>
-      </c>
-      <c r="B4" s="191" t="s">
-        <v>652</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -19321,8 +19302,8 @@
         <v>432.3078</v>
       </c>
       <c r="W5" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
@@ -19387,8 +19368,8 @@
         <v>432.3078</v>
       </c>
       <c r="W6" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
@@ -19447,8 +19428,8 @@
         <v>341.19</v>
       </c>
       <c r="W7" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
@@ -19516,8 +19497,8 @@
         <v>432.3078</v>
       </c>
       <c r="W8" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
@@ -19579,8 +19560,8 @@
         <v>341.19</v>
       </c>
       <c r="W9" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
@@ -19648,8 +19629,8 @@
         <v>432.3078</v>
       </c>
       <c r="W10" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
@@ -19828,8 +19809,8 @@
         <v>341.19</v>
       </c>
       <c r="W13" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
@@ -19957,8 +19938,8 @@
         <v>341.19</v>
       </c>
       <c r="W15" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
@@ -20020,8 +20001,8 @@
         <v>341.19</v>
       </c>
       <c r="W16" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
@@ -20329,8 +20310,8 @@
         <v>432.3078</v>
       </c>
       <c r="W21" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
@@ -20389,8 +20370,8 @@
         <v>432.3078</v>
       </c>
       <c r="W22" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
@@ -24415,8 +24396,8 @@
         <v>386.682</v>
       </c>
       <c r="W96" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2494.722580645161)</f>
-        <v>2494.722581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2577.8799999999997)</f>
+        <v>2577.88</v>
       </c>
       <c r="X96" s="2"/>
       <c r="Y96" s="2"/>
@@ -25888,8 +25869,8 @@
         <v>49506</v>
       </c>
       <c r="W122" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1596.967741935484)</f>
-        <v>1596.967742</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1650.2)</f>
+        <v>1650.2</v>
       </c>
       <c r="X122" s="2"/>
       <c r="Y122" s="2"/>
@@ -26271,8 +26252,8 @@
       <c r="T129" s="2"/>
       <c r="U129" s="2"/>
       <c r="V129" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
-        <v>170</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),200.0)</f>
+        <v>200</v>
       </c>
       <c r="W129" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -61034,7 +61015,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -61066,28 +61047,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>660</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>661</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -61116,22 +61097,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>663</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>664</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>665</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -61153,20 +61134,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>667</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>668</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>669</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -61190,18 +61171,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -61228,15 +61209,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -61263,14 +61244,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -61294,14 +61275,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>675</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -61326,17 +61307,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -61361,14 +61342,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>679</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>680</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61581,7 +61562,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61906,7 +61887,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -62027,7 +62008,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62146,7 +62127,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62180,7 +62161,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62272,7 +62253,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62451,7 +62432,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62572,7 +62553,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62780,7 +62761,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62901,7 +62882,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63109,7 +63090,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63578,7 +63559,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63612,7 +63593,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63646,7 +63627,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63680,7 +63661,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63773,7 +63754,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -64039,7 +64020,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -64073,7 +64054,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64165,7 +64146,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64228,7 +64209,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64320,7 +64301,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64354,7 +64335,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64388,7 +64369,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64451,7 +64432,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64543,7 +64524,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64606,7 +64587,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64727,7 +64708,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64878,7 +64859,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65263,7 +65244,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>

--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -1938,13 +1938,13 @@
     <t>Vychivskyi Volodymyr</t>
   </si>
   <si>
-    <t>35:00</t>
+    <t>66:00</t>
   </si>
   <si>
     <t>Šebesta Tomáš</t>
   </si>
   <si>
-    <t>18:00</t>
+    <t>44:30</t>
   </si>
   <si>
     <t>23:00</t>
@@ -1953,7 +1953,7 @@
     <t>Nováková Adéla</t>
   </si>
   <si>
-    <t>26:30</t>
+    <t>31:30</t>
   </si>
   <si>
     <t>13:00</t>
@@ -1962,13 +1962,13 @@
     <t>Putna Jaroslav</t>
   </si>
   <si>
-    <t>16:00</t>
+    <t>45:00</t>
   </si>
   <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>11 min 09 s</t>
+    <t>11 min 53 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13247,7 +13247,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46179.0</v>
+        <v>46183.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13296,7 +13296,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Sobota</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -14124,7 +14124,7 @@
         <v>631</v>
       </c>
       <c r="E1" s="109">
-        <v>46203.0</v>
+        <v>46180.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14149,18 +14149,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.34931562507951885</v>
+        <v>0.3215457224867853</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>124409.9</v>
+        <v>257293.25</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>47534.399999999994</v>
+        <v>97149.7</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14173,7 +14173,7 @@
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Neděle</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14182,7 +14182,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>25868.0</v>
+        <v>48591.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14202,7 +14202,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>22021.5</v>
+        <v>46077.65</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14226,7 +14226,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>12202.0</v>
+        <v>29465.0</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14246,7 +14246,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>784.0</v>
+        <v>1090.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14254,14 +14254,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>72.5</v>
+        <v>133</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14325,14 +14325,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="141">
-        <v>4.000000000007276</v>
+        <v>6.100000000013097</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>9759.0</v>
+        <v>19814.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14354,13 +14354,13 @@
         <v>638</v>
       </c>
       <c r="G10" s="145">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="145" t="s">
         <v>639</v>
       </c>
       <c r="I10" s="147">
-        <v>14.0</v>
+        <v>30.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14368,7 +14368,7 @@
         <v>601</v>
       </c>
       <c r="M10" s="120">
-        <v>0.0</v>
+        <v>1075.0</v>
       </c>
       <c r="N10" s="116"/>
     </row>
@@ -14378,7 +14378,7 @@
         <v>640</v>
       </c>
       <c r="C11" s="145">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D11" s="145" t="s">
         <v>641</v>
@@ -14396,7 +14396,7 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>5615.0</v>
+        <v>11687.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
@@ -14406,7 +14406,7 @@
         <v>643</v>
       </c>
       <c r="C12" s="145">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D12" s="145" t="s">
         <v>644</v>
@@ -14432,7 +14432,7 @@
         <v>646</v>
       </c>
       <c r="C13" s="145">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D13" s="145" t="s">
         <v>647</v>
@@ -14450,7 +14450,7 @@
         <v>608</v>
       </c>
       <c r="M13" s="120">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
@@ -14534,7 +14534,7 @@
         <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>630.0</v>
+        <v>1350.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14611,7 +14611,7 @@
         <v>2868.0</v>
       </c>
       <c r="L21" s="166">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="M21" s="167" t="s">
         <v>649</v>
@@ -14669,16 +14669,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="K24" s="166">
-        <v>293.0</v>
+        <v>621.0</v>
       </c>
       <c r="L24" s="166">
-        <v>29.0</v>
+        <v>63.0</v>
       </c>
       <c r="M24" s="173">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14731,14 +14731,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.03125</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="M27" s="180">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14789,10 +14789,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.96875</v>
+        <v>0.9107142857142857</v>
       </c>
       <c r="M30" s="184">
-        <v>0.03125</v>
+        <v>0.03373015873015873</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14904,7 +14904,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="186"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="185"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -15046,7 +15046,7 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="185"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -15074,7 +15074,7 @@
       <c r="B7" s="4"/>
       <c r="C7" s="186"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="185"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -15142,7 +15142,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="186"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="185"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -15216,7 +15216,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="185"/>
+      <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -15243,7 +15243,7 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="185"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -15283,7 +15283,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="185"/>
+      <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -15311,7 +15311,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="186"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="185"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -15345,7 +15345,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="186"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="185"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -15419,7 +15419,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="K17" s="185"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -15617,7 +15617,7 @@
       <c r="B23" s="186"/>
       <c r="C23" s="186"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="185"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -15651,7 +15651,7 @@
       <c r="B24" s="186"/>
       <c r="C24" s="186"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="185"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -15685,7 +15685,7 @@
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="185"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -15719,7 +15719,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="185"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15786,7 +15786,7 @@
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="185"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -15820,7 +15820,7 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="185"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -15860,7 +15860,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
+      <c r="K30" s="185"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
@@ -15922,7 +15922,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="186"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="185"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -15956,7 +15956,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="185"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -15990,7 +15990,7 @@
       <c r="B34" s="4"/>
       <c r="C34" s="186"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="E34" s="185"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -16024,7 +16024,7 @@
       <c r="B35" s="186"/>
       <c r="C35" s="186"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="185"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -16058,7 +16058,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="186"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="185"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -16160,13 +16160,13 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="185"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-      <c r="K39" s="185"/>
+      <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
@@ -16200,7 +16200,7 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="185"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -16262,7 +16262,7 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="185"/>
+      <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -16302,7 +16302,7 @@
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="185"/>
+      <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
@@ -16364,13 +16364,13 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="185"/>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="K45" s="185"/>
+      <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -16404,7 +16404,7 @@
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
+      <c r="K46" s="185"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -16432,7 +16432,7 @@
       <c r="B47" s="4"/>
       <c r="C47" s="186"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
+      <c r="E47" s="185"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -16500,13 +16500,13 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="185"/>
+      <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-      <c r="K49" s="185"/>
+      <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -16534,7 +16534,7 @@
       <c r="B50" s="4"/>
       <c r="C50" s="186"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="185"/>
+      <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -16568,7 +16568,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="185"/>
+      <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16636,13 +16636,13 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
+      <c r="E53" s="185"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
+      <c r="K53" s="185"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
@@ -16670,7 +16670,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="186"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="185"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -16772,13 +16772,13 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="185"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-      <c r="K57" s="185"/>
+      <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
@@ -16812,7 +16812,7 @@
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
+      <c r="K58" s="185"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
@@ -16874,7 +16874,7 @@
       <c r="B60" s="4"/>
       <c r="C60" s="186"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="185"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -16914,7 +16914,7 @@
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
+      <c r="K61" s="185"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
@@ -16948,7 +16948,7 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
+      <c r="K62" s="185"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
@@ -17010,7 +17010,7 @@
       <c r="B64" s="4"/>
       <c r="C64" s="186"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="185"/>
+      <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -17044,7 +17044,7 @@
       <c r="B65" s="4"/>
       <c r="C65" s="186"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="185"/>
+      <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -17145,7 +17145,7 @@
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="185"/>
+      <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
@@ -17185,7 +17185,7 @@
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+      <c r="K69" s="185"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -17247,7 +17247,7 @@
       <c r="B71" s="4"/>
       <c r="C71" s="186"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="185"/>
+      <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -17319,7 +17319,7 @@
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
+      <c r="K73" s="185"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
@@ -17381,7 +17381,7 @@
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="185"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
@@ -17415,7 +17415,7 @@
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="185"/>
+      <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -17449,7 +17449,7 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="185"/>
+      <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -17517,7 +17517,7 @@
       <c r="B79" s="4"/>
       <c r="C79" s="186"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="185"/>
+      <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -17619,7 +17619,7 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="185"/>
+      <c r="E82" s="4"/>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -17653,7 +17653,7 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="185"/>
+      <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -17721,7 +17721,7 @@
       <c r="B85" s="4"/>
       <c r="C85" s="186"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="185"/>
+      <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -17823,7 +17823,7 @@
       <c r="B88" s="4"/>
       <c r="C88" s="186"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="185"/>
+      <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -17881,26 +17881,27 @@
       <c r="AA89" s="185"/>
       <c r="AB89" s="185"/>
       <c r="AC89" s="185"/>
+      <c r="AD89" s="185"/>
       <c r="AE89" s="185"/>
       <c r="AF89" s="185"/>
     </row>
     <row r="90">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="186"/>
-      <c r="D90" s="4"/>
+      <c r="A90" s="185"/>
+      <c r="B90" s="185"/>
+      <c r="C90" s="187"/>
+      <c r="D90" s="185"/>
       <c r="E90" s="185"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
+      <c r="F90" s="185"/>
+      <c r="G90" s="185"/>
+      <c r="H90" s="185"/>
+      <c r="I90" s="185"/>
+      <c r="J90" s="185"/>
       <c r="K90" s="185"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
+      <c r="L90" s="185"/>
+      <c r="M90" s="185"/>
+      <c r="N90" s="185"/>
+      <c r="O90" s="185"/>
+      <c r="P90" s="185"/>
       <c r="Q90" s="185"/>
       <c r="R90" s="185"/>
       <c r="S90" s="185"/>
@@ -17918,22 +17919,22 @@
       <c r="AF90" s="185"/>
     </row>
     <row r="91">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
+      <c r="A91" s="185"/>
+      <c r="B91" s="185"/>
+      <c r="C91" s="185"/>
+      <c r="D91" s="185"/>
+      <c r="E91" s="185"/>
+      <c r="F91" s="185"/>
+      <c r="G91" s="185"/>
+      <c r="H91" s="185"/>
+      <c r="I91" s="185"/>
+      <c r="J91" s="185"/>
       <c r="K91" s="185"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
+      <c r="L91" s="185"/>
+      <c r="M91" s="185"/>
+      <c r="N91" s="185"/>
+      <c r="O91" s="185"/>
+      <c r="P91" s="185"/>
       <c r="Q91" s="185"/>
       <c r="R91" s="185"/>
       <c r="S91" s="185"/>
@@ -17951,22 +17952,22 @@
       <c r="AF91" s="185"/>
     </row>
     <row r="92">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
+      <c r="A92" s="185"/>
+      <c r="B92" s="185"/>
+      <c r="C92" s="185"/>
+      <c r="D92" s="185"/>
+      <c r="E92" s="185"/>
+      <c r="F92" s="185"/>
+      <c r="G92" s="185"/>
+      <c r="H92" s="185"/>
+      <c r="I92" s="185"/>
+      <c r="J92" s="185"/>
       <c r="K92" s="185"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
+      <c r="L92" s="185"/>
+      <c r="M92" s="185"/>
+      <c r="N92" s="185"/>
+      <c r="O92" s="185"/>
+      <c r="P92" s="185"/>
       <c r="Q92" s="185"/>
       <c r="R92" s="185"/>
       <c r="S92" s="185"/>
@@ -17984,22 +17985,22 @@
       <c r="AF92" s="185"/>
     </row>
     <row r="93">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
+      <c r="A93" s="185"/>
+      <c r="B93" s="185"/>
+      <c r="C93" s="185"/>
+      <c r="D93" s="185"/>
+      <c r="E93" s="185"/>
+      <c r="F93" s="185"/>
+      <c r="G93" s="185"/>
+      <c r="H93" s="185"/>
+      <c r="I93" s="185"/>
+      <c r="J93" s="185"/>
+      <c r="K93" s="185"/>
+      <c r="L93" s="185"/>
+      <c r="M93" s="185"/>
+      <c r="N93" s="185"/>
+      <c r="O93" s="185"/>
+      <c r="P93" s="185"/>
       <c r="Q93" s="185"/>
       <c r="R93" s="185"/>
       <c r="S93" s="185"/>
@@ -18018,22 +18019,22 @@
       <c r="AF93" s="185"/>
     </row>
     <row r="94">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
+      <c r="A94" s="185"/>
+      <c r="B94" s="185"/>
+      <c r="C94" s="185"/>
+      <c r="D94" s="185"/>
+      <c r="E94" s="185"/>
+      <c r="F94" s="185"/>
+      <c r="G94" s="185"/>
+      <c r="H94" s="185"/>
+      <c r="I94" s="185"/>
+      <c r="J94" s="185"/>
       <c r="K94" s="185"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
+      <c r="L94" s="185"/>
+      <c r="M94" s="185"/>
+      <c r="N94" s="185"/>
+      <c r="O94" s="185"/>
+      <c r="P94" s="185"/>
       <c r="Q94" s="185"/>
       <c r="R94" s="185"/>
       <c r="S94" s="185"/>
@@ -18051,22 +18052,22 @@
       <c r="AF94" s="185"/>
     </row>
     <row r="95">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
+      <c r="A95" s="185"/>
+      <c r="B95" s="185"/>
+      <c r="C95" s="185"/>
+      <c r="D95" s="185"/>
       <c r="E95" s="185"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
+      <c r="F95" s="185"/>
+      <c r="G95" s="185"/>
+      <c r="H95" s="185"/>
+      <c r="I95" s="185"/>
+      <c r="J95" s="185"/>
       <c r="K95" s="185"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
+      <c r="L95" s="185"/>
+      <c r="M95" s="185"/>
+      <c r="N95" s="185"/>
+      <c r="O95" s="185"/>
+      <c r="P95" s="185"/>
       <c r="Q95" s="185"/>
       <c r="R95" s="185"/>
       <c r="S95" s="185"/>
@@ -18084,22 +18085,22 @@
       <c r="AF95" s="185"/>
     </row>
     <row r="96">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
+      <c r="A96" s="185"/>
+      <c r="B96" s="185"/>
+      <c r="C96" s="185"/>
+      <c r="D96" s="185"/>
       <c r="E96" s="185"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
+      <c r="F96" s="185"/>
+      <c r="G96" s="185"/>
+      <c r="H96" s="185"/>
+      <c r="I96" s="185"/>
+      <c r="J96" s="185"/>
       <c r="K96" s="185"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
+      <c r="L96" s="185"/>
+      <c r="M96" s="185"/>
+      <c r="N96" s="185"/>
+      <c r="O96" s="185"/>
+      <c r="P96" s="185"/>
       <c r="Q96" s="185"/>
       <c r="R96" s="185"/>
       <c r="S96" s="185"/>
@@ -18117,22 +18118,22 @@
       <c r="AF96" s="185"/>
     </row>
     <row r="97">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
+      <c r="A97" s="185"/>
+      <c r="B97" s="185"/>
+      <c r="C97" s="185"/>
+      <c r="D97" s="185"/>
       <c r="E97" s="185"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
+      <c r="F97" s="185"/>
+      <c r="G97" s="185"/>
+      <c r="H97" s="185"/>
+      <c r="I97" s="185"/>
+      <c r="J97" s="185"/>
       <c r="K97" s="185"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
+      <c r="L97" s="185"/>
+      <c r="M97" s="185"/>
+      <c r="N97" s="185"/>
+      <c r="O97" s="185"/>
+      <c r="P97" s="185"/>
       <c r="Q97" s="185"/>
       <c r="R97" s="185"/>
       <c r="S97" s="185"/>
@@ -18151,22 +18152,22 @@
       <c r="AF97" s="185"/>
     </row>
     <row r="98">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
+      <c r="A98" s="185"/>
+      <c r="B98" s="185"/>
+      <c r="C98" s="185"/>
+      <c r="D98" s="185"/>
+      <c r="E98" s="185"/>
+      <c r="F98" s="185"/>
+      <c r="G98" s="185"/>
+      <c r="H98" s="185"/>
+      <c r="I98" s="185"/>
+      <c r="J98" s="185"/>
+      <c r="K98" s="185"/>
+      <c r="L98" s="185"/>
+      <c r="M98" s="185"/>
+      <c r="N98" s="185"/>
+      <c r="O98" s="185"/>
+      <c r="P98" s="185"/>
       <c r="Q98" s="185"/>
       <c r="R98" s="185"/>
       <c r="S98" s="185"/>
@@ -18184,22 +18185,22 @@
       <c r="AF98" s="185"/>
     </row>
     <row r="99">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="186"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
+      <c r="A99" s="185"/>
+      <c r="B99" s="185"/>
+      <c r="C99" s="187"/>
+      <c r="D99" s="185"/>
+      <c r="E99" s="185"/>
+      <c r="F99" s="185"/>
+      <c r="G99" s="185"/>
+      <c r="H99" s="185"/>
+      <c r="I99" s="185"/>
+      <c r="J99" s="185"/>
       <c r="K99" s="185"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
+      <c r="L99" s="185"/>
+      <c r="M99" s="185"/>
+      <c r="N99" s="185"/>
+      <c r="O99" s="185"/>
+      <c r="P99" s="185"/>
       <c r="Q99" s="185"/>
       <c r="R99" s="185"/>
       <c r="S99" s="185"/>
@@ -18218,22 +18219,22 @@
       <c r="AF99" s="185"/>
     </row>
     <row r="100">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="186"/>
-      <c r="D100" s="4"/>
+      <c r="A100" s="185"/>
+      <c r="B100" s="185"/>
+      <c r="C100" s="187"/>
+      <c r="D100" s="185"/>
       <c r="E100" s="185"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
+      <c r="F100" s="185"/>
+      <c r="G100" s="185"/>
+      <c r="H100" s="185"/>
+      <c r="I100" s="185"/>
+      <c r="J100" s="185"/>
       <c r="K100" s="185"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
+      <c r="L100" s="185"/>
+      <c r="M100" s="185"/>
+      <c r="N100" s="185"/>
+      <c r="O100" s="185"/>
+      <c r="P100" s="185"/>
       <c r="Q100" s="185"/>
       <c r="R100" s="185"/>
       <c r="S100" s="185"/>
@@ -18251,22 +18252,22 @@
       <c r="AF100" s="185"/>
     </row>
     <row r="101">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
+      <c r="A101" s="185"/>
+      <c r="B101" s="185"/>
+      <c r="C101" s="185"/>
+      <c r="D101" s="185"/>
+      <c r="E101" s="185"/>
+      <c r="F101" s="185"/>
+      <c r="G101" s="185"/>
+      <c r="H101" s="185"/>
+      <c r="I101" s="185"/>
+      <c r="J101" s="185"/>
       <c r="K101" s="185"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
+      <c r="L101" s="185"/>
+      <c r="M101" s="185"/>
+      <c r="N101" s="185"/>
+      <c r="O101" s="185"/>
+      <c r="P101" s="185"/>
       <c r="Q101" s="185"/>
       <c r="R101" s="185"/>
       <c r="S101" s="185"/>
@@ -18284,22 +18285,22 @@
       <c r="AF101" s="185"/>
     </row>
     <row r="102">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="186"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
+      <c r="A102" s="185"/>
+      <c r="B102" s="185"/>
+      <c r="C102" s="187"/>
+      <c r="D102" s="185"/>
+      <c r="E102" s="185"/>
+      <c r="F102" s="185"/>
+      <c r="G102" s="185"/>
+      <c r="H102" s="185"/>
+      <c r="I102" s="185"/>
+      <c r="J102" s="185"/>
       <c r="K102" s="185"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
+      <c r="L102" s="185"/>
+      <c r="M102" s="185"/>
+      <c r="N102" s="185"/>
+      <c r="O102" s="185"/>
+      <c r="P102" s="185"/>
       <c r="Q102" s="185"/>
       <c r="S102" s="185"/>
       <c r="T102" s="185"/>
@@ -18315,22 +18316,22 @@
       <c r="AF102" s="185"/>
     </row>
     <row r="103">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="186"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
+      <c r="A103" s="185"/>
+      <c r="B103" s="185"/>
+      <c r="C103" s="187"/>
+      <c r="D103" s="185"/>
+      <c r="E103" s="185"/>
+      <c r="F103" s="185"/>
+      <c r="G103" s="185"/>
+      <c r="H103" s="185"/>
+      <c r="I103" s="185"/>
+      <c r="J103" s="185"/>
       <c r="K103" s="185"/>
-      <c r="L103" s="4"/>
-      <c r="M103" s="4"/>
-      <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
+      <c r="L103" s="185"/>
+      <c r="M103" s="185"/>
+      <c r="N103" s="185"/>
+      <c r="O103" s="185"/>
+      <c r="P103" s="185"/>
       <c r="Q103" s="185"/>
       <c r="R103" s="185"/>
       <c r="S103" s="185"/>
@@ -18349,22 +18350,22 @@
       <c r="AF103" s="185"/>
     </row>
     <row r="104">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
+      <c r="A104" s="185"/>
+      <c r="B104" s="185"/>
+      <c r="C104" s="185"/>
+      <c r="D104" s="185"/>
+      <c r="E104" s="185"/>
+      <c r="F104" s="185"/>
+      <c r="G104" s="185"/>
+      <c r="H104" s="185"/>
+      <c r="I104" s="185"/>
+      <c r="J104" s="185"/>
       <c r="K104" s="185"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
+      <c r="L104" s="185"/>
+      <c r="M104" s="185"/>
+      <c r="N104" s="185"/>
+      <c r="O104" s="185"/>
+      <c r="P104" s="185"/>
       <c r="Q104" s="185"/>
       <c r="R104" s="185"/>
       <c r="S104" s="185"/>
@@ -18382,22 +18383,22 @@
       <c r="AF104" s="185"/>
     </row>
     <row r="105">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="186"/>
-      <c r="D105" s="4"/>
+      <c r="A105" s="185"/>
+      <c r="B105" s="185"/>
+      <c r="C105" s="187"/>
+      <c r="D105" s="185"/>
       <c r="E105" s="185"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
+      <c r="F105" s="185"/>
+      <c r="G105" s="185"/>
+      <c r="H105" s="185"/>
+      <c r="I105" s="185"/>
+      <c r="J105" s="185"/>
       <c r="K105" s="185"/>
-      <c r="L105" s="4"/>
-      <c r="M105" s="4"/>
-      <c r="N105" s="4"/>
-      <c r="O105" s="4"/>
-      <c r="P105" s="4"/>
+      <c r="L105" s="185"/>
+      <c r="M105" s="185"/>
+      <c r="N105" s="185"/>
+      <c r="O105" s="185"/>
+      <c r="P105" s="185"/>
       <c r="Q105" s="185"/>
       <c r="R105" s="185"/>
       <c r="S105" s="185"/>
@@ -18416,22 +18417,22 @@
       <c r="AF105" s="185"/>
     </row>
     <row r="106">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
+      <c r="A106" s="185"/>
+      <c r="B106" s="185"/>
+      <c r="C106" s="185"/>
+      <c r="D106" s="185"/>
+      <c r="E106" s="185"/>
+      <c r="F106" s="185"/>
+      <c r="G106" s="185"/>
+      <c r="H106" s="185"/>
+      <c r="I106" s="185"/>
+      <c r="J106" s="185"/>
       <c r="K106" s="185"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
+      <c r="L106" s="185"/>
+      <c r="M106" s="185"/>
+      <c r="N106" s="185"/>
+      <c r="O106" s="185"/>
+      <c r="P106" s="185"/>
       <c r="Q106" s="185"/>
       <c r="R106" s="185"/>
       <c r="S106" s="185"/>
@@ -18450,22 +18451,22 @@
       <c r="AF106" s="185"/>
     </row>
     <row r="107">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
+      <c r="A107" s="185"/>
+      <c r="B107" s="185"/>
+      <c r="C107" s="185"/>
+      <c r="D107" s="185"/>
+      <c r="E107" s="185"/>
+      <c r="F107" s="185"/>
+      <c r="G107" s="185"/>
+      <c r="H107" s="185"/>
+      <c r="I107" s="185"/>
+      <c r="J107" s="185"/>
       <c r="K107" s="185"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
+      <c r="L107" s="185"/>
+      <c r="M107" s="185"/>
+      <c r="N107" s="185"/>
+      <c r="O107" s="185"/>
+      <c r="P107" s="185"/>
       <c r="Q107" s="185"/>
       <c r="R107" s="185"/>
       <c r="S107" s="185"/>
@@ -18483,22 +18484,22 @@
       <c r="AF107" s="185"/>
     </row>
     <row r="108">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="186"/>
-      <c r="D108" s="4"/>
+      <c r="A108" s="185"/>
+      <c r="B108" s="185"/>
+      <c r="C108" s="187"/>
+      <c r="D108" s="185"/>
       <c r="E108" s="185"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
+      <c r="F108" s="185"/>
+      <c r="G108" s="185"/>
+      <c r="H108" s="185"/>
+      <c r="I108" s="185"/>
+      <c r="J108" s="185"/>
       <c r="K108" s="185"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
+      <c r="L108" s="185"/>
+      <c r="M108" s="185"/>
+      <c r="N108" s="185"/>
+      <c r="O108" s="185"/>
+      <c r="P108" s="185"/>
       <c r="Q108" s="185"/>
       <c r="R108" s="185"/>
       <c r="S108" s="185"/>
@@ -18517,22 +18518,22 @@
       <c r="AF108" s="185"/>
     </row>
     <row r="109">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
+      <c r="A109" s="185"/>
+      <c r="B109" s="185"/>
+      <c r="C109" s="185"/>
+      <c r="D109" s="185"/>
       <c r="E109" s="185"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
+      <c r="F109" s="185"/>
+      <c r="G109" s="185"/>
+      <c r="H109" s="185"/>
+      <c r="I109" s="185"/>
+      <c r="J109" s="185"/>
       <c r="K109" s="185"/>
-      <c r="L109" s="4"/>
-      <c r="M109" s="4"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
+      <c r="L109" s="185"/>
+      <c r="M109" s="185"/>
+      <c r="N109" s="185"/>
+      <c r="O109" s="185"/>
+      <c r="P109" s="185"/>
       <c r="Q109" s="185"/>
       <c r="R109" s="185"/>
       <c r="S109" s="185"/>
@@ -18550,22 +18551,22 @@
       <c r="AF109" s="185"/>
     </row>
     <row r="110">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="186"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
+      <c r="A110" s="185"/>
+      <c r="B110" s="185"/>
+      <c r="C110" s="187"/>
+      <c r="D110" s="185"/>
+      <c r="E110" s="185"/>
+      <c r="F110" s="185"/>
+      <c r="G110" s="185"/>
+      <c r="H110" s="185"/>
+      <c r="I110" s="185"/>
+      <c r="J110" s="185"/>
       <c r="K110" s="185"/>
-      <c r="L110" s="4"/>
-      <c r="M110" s="4"/>
-      <c r="N110" s="4"/>
-      <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
+      <c r="L110" s="185"/>
+      <c r="M110" s="185"/>
+      <c r="N110" s="185"/>
+      <c r="O110" s="185"/>
+      <c r="P110" s="185"/>
       <c r="Q110" s="185"/>
       <c r="S110" s="185"/>
       <c r="T110" s="185"/>
@@ -18581,22 +18582,22 @@
       <c r="AF110" s="185"/>
     </row>
     <row r="111">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
+      <c r="A111" s="185"/>
+      <c r="B111" s="185"/>
+      <c r="C111" s="185"/>
+      <c r="D111" s="185"/>
       <c r="E111" s="185"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
+      <c r="F111" s="185"/>
+      <c r="G111" s="185"/>
+      <c r="H111" s="185"/>
+      <c r="I111" s="185"/>
+      <c r="J111" s="185"/>
       <c r="K111" s="185"/>
-      <c r="L111" s="4"/>
-      <c r="M111" s="4"/>
-      <c r="N111" s="4"/>
-      <c r="O111" s="4"/>
-      <c r="P111" s="4"/>
+      <c r="L111" s="185"/>
+      <c r="M111" s="185"/>
+      <c r="N111" s="185"/>
+      <c r="O111" s="185"/>
+      <c r="P111" s="185"/>
       <c r="Q111" s="185"/>
       <c r="S111" s="185"/>
       <c r="T111" s="185"/>
@@ -18612,22 +18613,22 @@
       <c r="AF111" s="185"/>
     </row>
     <row r="112">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
+      <c r="A112" s="185"/>
+      <c r="B112" s="185"/>
+      <c r="C112" s="185"/>
+      <c r="D112" s="185"/>
       <c r="E112" s="185"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
+      <c r="F112" s="185"/>
+      <c r="G112" s="185"/>
+      <c r="H112" s="185"/>
+      <c r="I112" s="185"/>
+      <c r="J112" s="185"/>
       <c r="K112" s="185"/>
-      <c r="L112" s="4"/>
-      <c r="M112" s="4"/>
-      <c r="N112" s="4"/>
-      <c r="O112" s="4"/>
-      <c r="P112" s="4"/>
+      <c r="L112" s="185"/>
+      <c r="M112" s="185"/>
+      <c r="N112" s="185"/>
+      <c r="O112" s="185"/>
+      <c r="P112" s="185"/>
       <c r="Q112" s="185"/>
       <c r="S112" s="185"/>
       <c r="T112" s="185"/>
@@ -18643,22 +18644,22 @@
       <c r="AF112" s="185"/>
     </row>
     <row r="113">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="186"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
+      <c r="A113" s="185"/>
+      <c r="B113" s="185"/>
+      <c r="C113" s="187"/>
+      <c r="D113" s="185"/>
+      <c r="E113" s="185"/>
+      <c r="F113" s="185"/>
+      <c r="G113" s="185"/>
+      <c r="H113" s="185"/>
+      <c r="I113" s="185"/>
+      <c r="J113" s="185"/>
       <c r="K113" s="185"/>
-      <c r="L113" s="4"/>
-      <c r="M113" s="4"/>
-      <c r="N113" s="4"/>
-      <c r="O113" s="4"/>
-      <c r="P113" s="4"/>
+      <c r="L113" s="185"/>
+      <c r="M113" s="185"/>
+      <c r="N113" s="185"/>
+      <c r="O113" s="185"/>
+      <c r="P113" s="185"/>
       <c r="Q113" s="185"/>
       <c r="S113" s="185"/>
       <c r="T113" s="185"/>
@@ -18674,22 +18675,22 @@
       <c r="AF113" s="185"/>
     </row>
     <row r="114">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
+      <c r="A114" s="185"/>
+      <c r="B114" s="185"/>
+      <c r="C114" s="185"/>
+      <c r="D114" s="185"/>
       <c r="E114" s="185"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
+      <c r="F114" s="185"/>
+      <c r="G114" s="185"/>
+      <c r="H114" s="185"/>
+      <c r="I114" s="185"/>
+      <c r="J114" s="185"/>
       <c r="K114" s="185"/>
-      <c r="L114" s="4"/>
-      <c r="M114" s="4"/>
-      <c r="N114" s="4"/>
-      <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
+      <c r="L114" s="185"/>
+      <c r="M114" s="185"/>
+      <c r="N114" s="185"/>
+      <c r="O114" s="185"/>
+      <c r="P114" s="185"/>
       <c r="Q114" s="185"/>
       <c r="R114" s="185"/>
       <c r="S114" s="185"/>
@@ -18855,6 +18856,7 @@
       <c r="O119" s="185"/>
       <c r="P119" s="185"/>
       <c r="Q119" s="185"/>
+      <c r="R119" s="185"/>
       <c r="S119" s="185"/>
       <c r="T119" s="185"/>
       <c r="U119" s="185"/>
@@ -18863,6 +18865,7 @@
       <c r="X119" s="185"/>
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
+      <c r="AA119" s="185"/>
       <c r="AB119" s="185"/>
       <c r="AC119" s="185"/>
       <c r="AE119" s="185"/>
@@ -23613,7 +23616,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F83" s="2"/>
+      <c r="F83" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>

--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="710">
   <si>
     <t>Datum</t>
   </si>
@@ -1842,9 +1842,24 @@
     <t>Počet hodin</t>
   </si>
   <si>
+    <t>Nováková Adéla</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
     <t>Výdaje</t>
   </si>
   <si>
+    <t>Putna Jaroslav</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
     <t>Benzín</t>
   </si>
   <si>
@@ -1917,6 +1932,9 @@
     <t>Vyber datum    &lt;----------&gt;</t>
   </si>
   <si>
+    <t>0#ERROR!</t>
+  </si>
+  <si>
     <t>Celkem hodin Instor</t>
   </si>
   <si>
@@ -1926,49 +1944,34 @@
     <t>Počet dní</t>
   </si>
   <si>
-    <t>Yarushynskyi Vladyslav</t>
-  </si>
-  <si>
-    <t>12:00</t>
+    <t>Šebesta Tomáš</t>
+  </si>
+  <si>
+    <t>3:00</t>
   </si>
   <si>
     <t>29:00</t>
   </si>
   <si>
-    <t>Vychivskyi Volodymyr</t>
-  </si>
-  <si>
-    <t>66:00</t>
-  </si>
-  <si>
-    <t>Šebesta Tomáš</t>
-  </si>
-  <si>
-    <t>44:30</t>
+    <t>15:00</t>
   </si>
   <si>
     <t>23:00</t>
   </si>
   <si>
-    <t>Nováková Adéla</t>
-  </si>
-  <si>
-    <t>31:30</t>
+    <t>Fáberová Kateřina</t>
+  </si>
+  <si>
+    <t>8:00</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
-    <t>Putna Jaroslav</t>
-  </si>
-  <si>
-    <t>45:00</t>
-  </si>
-  <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>11 min 53 s</t>
+    <t>11 min 03 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -3683,7 +3686,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:colOff>1038225</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -13247,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46183.0</v>
+        <v>46189.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13280,7 +13283,7 @@
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="21">
-        <f>SUM(RestiaCSV!C:C) - SUMIFS(RestiaCSV!C:C, RestiaCSV!B:B, "canceled")</f>
+        <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!B:B, "&lt;&gt;canceled", RestiaCSV!B:B, "&lt;&gt;expired")</f>
         <v>0</v>
       </c>
       <c r="K2" s="20"/>
@@ -13288,7 +13291,7 @@
         <v>589</v>
       </c>
       <c r="M2" s="23">
-        <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, Report!L2, RestiaCSV!B:B, "&lt;&gt;canceled")</f>
+        <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, Report!L2, RestiaCSV!B:B, "&lt;&gt;canceled", RestiaCSV!B:B, "&lt;&gt;expired")</f>
         <v>0</v>
       </c>
     </row>
@@ -13296,7 +13299,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Středa</v>
+        <v>Úterý</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -13455,7 +13458,9 @@
       <c r="F11" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="G11" s="45"/>
+      <c r="G11" s="45" t="s">
+        <v>607</v>
+      </c>
       <c r="I11" s="20"/>
       <c r="J11" s="46">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
@@ -13472,35 +13477,47 @@
         <f t="array" ref="A12">IF(ISBLANK(B12), 0, IF(ISNUMBER(MATCH(B12, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B12, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B12, HR!B:B, 0)) * (F12 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
+      <c r="B12" s="50" t="s">
+        <v>607</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>608</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>609</v>
+      </c>
       <c r="E12" s="52"/>
       <c r="F12" s="53" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>0:00</v>
+        <v>15:00</v>
       </c>
       <c r="I12" s="20"/>
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="54" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M12" s="18"/>
     </row>
     <row r="13">
       <c r="A13" s="49">
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
+        <v>1751.442</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>611</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>612</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>609</v>
+      </c>
       <c r="E13" s="52"/>
       <c r="F13" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>07:00</v>
       </c>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
@@ -13508,7 +13525,7 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="22" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="M13" s="37"/>
     </row>
@@ -13530,7 +13547,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="57" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="M14" s="37"/>
     </row>
@@ -13551,7 +13568,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="57" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="M15" s="37"/>
     </row>
@@ -13572,7 +13589,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="57" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M16" s="37"/>
     </row>
@@ -13595,7 +13612,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="59" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="M17" s="60">
         <f>sum(I25:I31)</f>
@@ -13616,7 +13633,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="18"/>
@@ -13636,7 +13653,9 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="45"/>
+      <c r="G19" s="45" t="s">
+        <v>607</v>
+      </c>
       <c r="I19" s="20"/>
       <c r="M19" s="62"/>
     </row>
@@ -13685,16 +13704,16 @@
       <c r="H22" s="27"/>
       <c r="I22" s="18"/>
       <c r="J22" s="70" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="K22" s="70" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="L22" s="71" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="M22" s="71" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="23">
@@ -13738,25 +13757,25 @@
         <v>606</v>
       </c>
       <c r="G24" s="75" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="H24" s="75" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="J24" s="77" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K24" s="78" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L24" s="77" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="M24" s="78" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="25">
@@ -13855,14 +13874,14 @@
         <v>0</v>
       </c>
       <c r="J27" s="89" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="K27" s="90"/>
       <c r="L27" s="77" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M27" s="78" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -13959,10 +13978,10 @@
       <c r="J30" s="96"/>
       <c r="K30" s="96"/>
       <c r="L30" s="78" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="M30" s="78" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="31">
@@ -14000,7 +14019,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="99" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
@@ -14083,6 +14102,9 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" sqref="G11 G19">
+      <formula1>"Nováková Adéla,Putna Jaroslav"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
       <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
     </dataValidation>
@@ -14118,13 +14140,13 @@
         <v>Prosek</v>
       </c>
       <c r="C1" s="107">
-        <v>46174.0</v>
+        <v>46188.0</v>
       </c>
       <c r="D1" s="108" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E1" s="109">
-        <v>46180.0</v>
+        <v>46188.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14149,18 +14171,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.3215457224867853</v>
+        <v>0.0</v>
       </c>
       <c r="H2" s="20"/>
-      <c r="I2" s="113">
-        <v>257293.25</v>
+      <c r="I2" s="113" t="s">
+        <v>637</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>97149.7</v>
+        <v>14580.200000000008</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14173,7 +14195,7 @@
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Pondělí</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14182,7 +14204,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>48591.0</v>
+        <v>1903.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14202,20 +14224,20 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>46077.65</v>
+        <v>7583.0</v>
       </c>
       <c r="N4" s="116"/>
     </row>
     <row r="5">
       <c r="A5" s="121"/>
       <c r="B5" s="122" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="10"/>
       <c r="F5" s="123" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
@@ -14226,7 +14248,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>29465.0</v>
+        <v>3557.0</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14246,7 +14268,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>1090.0</v>
+        <v>927.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14254,14 +14276,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14306,7 +14328,7 @@
         <v>602</v>
       </c>
       <c r="C9" s="138" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D9" s="138" t="s">
         <v>606</v>
@@ -14316,75 +14338,67 @@
         <v>602</v>
       </c>
       <c r="G9" s="138" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="H9" s="138" t="s">
         <v>606</v>
       </c>
       <c r="I9" s="140" t="s">
-        <v>618</v>
-      </c>
-      <c r="J9" s="141">
-        <v>6.100000000013097</v>
+        <v>623</v>
+      </c>
+      <c r="J9" s="141" t="s">
+        <v>637</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>19814.0</v>
+        <v>3956.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="143"/>
       <c r="B10" s="144" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C10" s="145">
         <v>1.0</v>
       </c>
       <c r="D10" s="145" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E10" s="146" t="s">
-        <v>637</v>
-      </c>
-      <c r="F10" s="144" t="s">
-        <v>638</v>
-      </c>
-      <c r="G10" s="145">
-        <v>6.0</v>
-      </c>
-      <c r="H10" s="145" t="s">
-        <v>639</v>
-      </c>
-      <c r="I10" s="147">
-        <v>30.0</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="F10" s="144"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="147"/>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
       <c r="L10" s="142" t="s">
         <v>601</v>
       </c>
       <c r="M10" s="120">
-        <v>1075.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="116"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="143"/>
       <c r="B11" s="144" t="s">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="C11" s="145">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E11" s="146" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F11" s="144"/>
       <c r="G11" s="145"/>
@@ -14396,23 +14410,23 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>11687.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
       <c r="B12" s="144" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C12" s="145">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F12" s="144"/>
       <c r="G12" s="145"/>
@@ -14421,24 +14435,18 @@
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="150" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="111"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
-      <c r="B13" s="144" t="s">
-        <v>646</v>
-      </c>
-      <c r="C13" s="145">
-        <v>5.0</v>
-      </c>
-      <c r="D13" s="145" t="s">
-        <v>647</v>
-      </c>
+      <c r="B13" s="144"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
       <c r="E13" s="146" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14447,10 +14455,10 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="142" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="M13" s="120">
-        <v>1000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
@@ -14460,7 +14468,7 @@
       <c r="C14" s="145"/>
       <c r="D14" s="145"/>
       <c r="E14" s="146" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14469,7 +14477,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="151" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="M14" s="120">
         <v>0.0</v>
@@ -14482,7 +14490,7 @@
       <c r="C15" s="145"/>
       <c r="D15" s="145"/>
       <c r="E15" s="146" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14491,7 +14499,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="151" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="M15" s="120">
         <v>0.0</v>
@@ -14511,10 +14519,10 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="151" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M16" s="120">
-        <v>0.0</v>
+        <v>1165.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
@@ -14531,10 +14539,10 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="153" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="M17" s="154">
-        <v>1350.0</v>
+        <v>0.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14565,16 +14573,16 @@
       <c r="H19" s="145"/>
       <c r="I19" s="147"/>
       <c r="J19" s="157" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="K19" s="158" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="L19" s="159" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="M19" s="160" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="N19" s="161"/>
     </row>
@@ -14605,16 +14613,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="K21" s="165">
-        <v>2868.0</v>
+        <v>0.0</v>
       </c>
       <c r="L21" s="166">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="M21" s="167" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14629,16 +14637,16 @@
       <c r="H22" s="145"/>
       <c r="I22" s="147"/>
       <c r="J22" s="168" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K22" s="169" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L22" s="170" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="M22" s="171" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="N22" s="156"/>
     </row>
@@ -14669,16 +14677,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="166">
-        <v>621.0</v>
+        <v>89.0</v>
       </c>
       <c r="L24" s="166">
-        <v>63.0</v>
+        <v>6.0</v>
       </c>
       <c r="M24" s="173">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14693,14 +14701,14 @@
       <c r="H25" s="145"/>
       <c r="I25" s="147"/>
       <c r="J25" s="174" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="K25" s="90"/>
       <c r="L25" s="175" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M25" s="176" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="N25" s="156"/>
     </row>
@@ -14731,14 +14739,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.08928571428571429</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="M27" s="180">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14754,10 +14762,10 @@
       <c r="I28" s="147"/>
       <c r="J28" s="181"/>
       <c r="L28" s="182" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="M28" s="176" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="N28" s="156"/>
     </row>
@@ -14789,10 +14797,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.9107142857142857</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M30" s="184">
-        <v>0.03373015873015873</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14904,7 +14912,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="186"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="185"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -14938,7 +14946,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="186"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="185"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -14972,7 +14980,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="186"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="185"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -15040,13 +15048,13 @@
       <c r="B6" s="4"/>
       <c r="C6" s="186"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="185"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="K6" s="185"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -15176,7 +15184,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="186"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="185"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -15216,7 +15224,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="K11" s="185"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -15283,7 +15291,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="K13" s="185"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -15453,7 +15461,7 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="185"/>
+      <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -15583,7 +15591,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="185"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -15651,7 +15659,7 @@
       <c r="B24" s="186"/>
       <c r="C24" s="186"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="185"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -15719,7 +15727,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="185"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15820,7 +15828,7 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="185"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -15860,7 +15868,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="185"/>
+      <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
@@ -15922,7 +15930,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="186"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="185"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -15956,7 +15964,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="185"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -15990,7 +15998,7 @@
       <c r="B34" s="4"/>
       <c r="C34" s="186"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="185"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -16024,7 +16032,7 @@
       <c r="B35" s="186"/>
       <c r="C35" s="186"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="185"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -16058,7 +16066,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="186"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="185"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -16166,7 +16174,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
+      <c r="K39" s="185"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
@@ -16194,13 +16202,13 @@
       <c r="B40" s="4"/>
       <c r="C40" s="186"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="185"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
+      <c r="K40" s="185"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -16228,7 +16236,7 @@
       <c r="B41" s="4"/>
       <c r="C41" s="186"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="185"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -16262,7 +16270,7 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="185"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -16296,13 +16304,13 @@
       <c r="B43" s="4"/>
       <c r="C43" s="186"/>
       <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="185"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="185"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
@@ -16336,7 +16344,7 @@
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="185"/>
+      <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
@@ -16364,13 +16372,13 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="185"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
+      <c r="K45" s="185"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -16398,7 +16406,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="186"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="E46" s="185"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -16472,7 +16480,7 @@
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-      <c r="K48" s="185"/>
+      <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -16500,13 +16508,13 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="185"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
+      <c r="K49" s="185"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -16534,7 +16542,7 @@
       <c r="B50" s="4"/>
       <c r="C50" s="186"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="185"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -16568,7 +16576,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="185"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16636,7 +16644,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="185"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16670,7 +16678,7 @@
       <c r="B54" s="4"/>
       <c r="C54" s="186"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="185"/>
+      <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -16704,7 +16712,7 @@
       <c r="B55" s="4"/>
       <c r="C55" s="186"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="185"/>
+      <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -16772,13 +16780,13 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="185"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
+      <c r="K57" s="185"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
@@ -16908,7 +16916,7 @@
       <c r="B61" s="4"/>
       <c r="C61" s="186"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
+      <c r="E61" s="185"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -16942,7 +16950,7 @@
       <c r="B62" s="4"/>
       <c r="C62" s="186"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
+      <c r="E62" s="185"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -17016,7 +17024,7 @@
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
-      <c r="K64" s="185"/>
+      <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
@@ -17112,7 +17120,7 @@
       <c r="B67" s="4"/>
       <c r="C67" s="186"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
+      <c r="E67" s="185"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -17213,7 +17221,7 @@
       <c r="B70" s="4"/>
       <c r="C70" s="186"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="E70" s="185"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -17253,7 +17261,7 @@
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
-      <c r="K71" s="185"/>
+      <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
@@ -17272,6 +17280,7 @@
       <c r="AA71" s="185"/>
       <c r="AB71" s="185"/>
       <c r="AC71" s="185"/>
+      <c r="AD71" s="185"/>
       <c r="AE71" s="185"/>
       <c r="AF71" s="185"/>
     </row>
@@ -17305,6 +17314,7 @@
       <c r="AA72" s="185"/>
       <c r="AB72" s="185"/>
       <c r="AC72" s="185"/>
+      <c r="AD72" s="185"/>
       <c r="AE72" s="185"/>
       <c r="AF72" s="185"/>
     </row>
@@ -17313,7 +17323,7 @@
       <c r="B73" s="4"/>
       <c r="C73" s="186"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="185"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -17353,7 +17363,7 @@
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
+      <c r="K74" s="185"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
@@ -17381,7 +17391,7 @@
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="185"/>
+      <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
@@ -17415,7 +17425,7 @@
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
+      <c r="E76" s="185"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -17585,7 +17595,7 @@
       <c r="B81" s="4"/>
       <c r="C81" s="186"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="185"/>
+      <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
@@ -17653,7 +17663,7 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
+      <c r="E83" s="185"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -17721,7 +17731,7 @@
       <c r="B85" s="4"/>
       <c r="C85" s="186"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
+      <c r="E85" s="185"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -17789,7 +17799,7 @@
       <c r="B87" s="4"/>
       <c r="C87" s="186"/>
       <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
+      <c r="E87" s="185"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
@@ -17848,6 +17858,7 @@
       <c r="AA88" s="185"/>
       <c r="AB88" s="185"/>
       <c r="AC88" s="185"/>
+      <c r="AD88" s="185"/>
       <c r="AE88" s="185"/>
       <c r="AF88" s="185"/>
     </row>
@@ -17856,7 +17867,7 @@
       <c r="B89" s="4"/>
       <c r="C89" s="186"/>
       <c r="D89" s="4"/>
-      <c r="E89" s="185"/>
+      <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
@@ -17886,22 +17897,22 @@
       <c r="AF89" s="185"/>
     </row>
     <row r="90">
-      <c r="A90" s="185"/>
-      <c r="B90" s="185"/>
-      <c r="C90" s="187"/>
-      <c r="D90" s="185"/>
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="186"/>
+      <c r="D90" s="4"/>
       <c r="E90" s="185"/>
-      <c r="F90" s="185"/>
-      <c r="G90" s="185"/>
-      <c r="H90" s="185"/>
-      <c r="I90" s="185"/>
-      <c r="J90" s="185"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
       <c r="K90" s="185"/>
-      <c r="L90" s="185"/>
-      <c r="M90" s="185"/>
-      <c r="N90" s="185"/>
-      <c r="O90" s="185"/>
-      <c r="P90" s="185"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
       <c r="Q90" s="185"/>
       <c r="R90" s="185"/>
       <c r="S90" s="185"/>
@@ -18302,6 +18313,7 @@
       <c r="O102" s="185"/>
       <c r="P102" s="185"/>
       <c r="Q102" s="185"/>
+      <c r="R102" s="185"/>
       <c r="S102" s="185"/>
       <c r="T102" s="185"/>
       <c r="U102" s="185"/>
@@ -18310,6 +18322,7 @@
       <c r="X102" s="185"/>
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
+      <c r="AA102" s="185"/>
       <c r="AB102" s="185"/>
       <c r="AC102" s="185"/>
       <c r="AE102" s="185"/>
@@ -18379,6 +18392,7 @@
       <c r="AA104" s="185"/>
       <c r="AB104" s="185"/>
       <c r="AC104" s="185"/>
+      <c r="AD104" s="185"/>
       <c r="AE104" s="185"/>
       <c r="AF104" s="185"/>
     </row>
@@ -18480,6 +18494,7 @@
       <c r="AA107" s="185"/>
       <c r="AB107" s="185"/>
       <c r="AC107" s="185"/>
+      <c r="AD107" s="185"/>
       <c r="AE107" s="185"/>
       <c r="AF107" s="185"/>
     </row>
@@ -18547,6 +18562,7 @@
       <c r="AA109" s="185"/>
       <c r="AB109" s="185"/>
       <c r="AC109" s="185"/>
+      <c r="AD109" s="185"/>
       <c r="AE109" s="185"/>
       <c r="AF109" s="185"/>
     </row>
@@ -18568,6 +18584,7 @@
       <c r="O110" s="185"/>
       <c r="P110" s="185"/>
       <c r="Q110" s="185"/>
+      <c r="R110" s="185"/>
       <c r="S110" s="185"/>
       <c r="T110" s="185"/>
       <c r="U110" s="185"/>
@@ -18576,6 +18593,7 @@
       <c r="X110" s="185"/>
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
+      <c r="AA110" s="185"/>
       <c r="AB110" s="185"/>
       <c r="AC110" s="185"/>
       <c r="AE110" s="185"/>
@@ -18889,6 +18907,7 @@
       <c r="O120" s="185"/>
       <c r="P120" s="185"/>
       <c r="Q120" s="185"/>
+      <c r="R120" s="185"/>
       <c r="S120" s="185"/>
       <c r="T120" s="185"/>
       <c r="U120" s="185"/>
@@ -18897,6 +18916,7 @@
       <c r="X120" s="185"/>
       <c r="Y120" s="185"/>
       <c r="Z120" s="185"/>
+      <c r="AA120" s="185"/>
       <c r="AB120" s="185"/>
       <c r="AC120" s="185"/>
       <c r="AE120" s="185"/>
@@ -18949,9 +18969,11 @@
       <c r="K122" s="185"/>
       <c r="L122" s="185"/>
       <c r="M122" s="185"/>
+      <c r="N122" s="185"/>
       <c r="O122" s="185"/>
       <c r="P122" s="185"/>
       <c r="Q122" s="185"/>
+      <c r="R122" s="185"/>
       <c r="S122" s="185"/>
       <c r="T122" s="185"/>
       <c r="U122" s="185"/>
@@ -18960,6 +18982,7 @@
       <c r="X122" s="185"/>
       <c r="Y122" s="185"/>
       <c r="Z122" s="185"/>
+      <c r="AA122" s="185"/>
       <c r="AB122" s="185"/>
       <c r="AC122" s="185"/>
       <c r="AE122" s="185"/>
@@ -19201,10 +19224,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -20095,14 +20118,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stepanenko Solomiia")</f>
-        <v>Stepanenko Solomiia</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
-      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -20120,8 +20137,8 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.332)</f>
-        <v>286.332</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W18" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20155,14 +20172,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rothová Anastasia")</f>
-        <v>Rothová Anastasia</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -20180,8 +20191,8 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),341.19)</f>
-        <v>341.19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W19" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20770,14 +20781,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Raboch Tomáš")</f>
-        <v>Raboch Tomáš</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -20795,8 +20800,8 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W29" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20838,7 +20843,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="F30" s="2"/>
+      <c r="F30" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -21571,8 +21579,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="D42" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prošek Václav")</f>
+        <v>Prošek Václav</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -21590,8 +21604,8 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W42" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26030,8 +26044,8 @@
       <c r="T125" s="2"/>
       <c r="U125" s="2"/>
       <c r="V125" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W125" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26184,7 +26198,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F128" s="2"/>
+      <c r="F128" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
@@ -26290,8 +26307,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
+      <c r="D130" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kumar Jatinder")</f>
+        <v>Kumar Jatinder</v>
+      </c>
+      <c r="E130" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -26309,8 +26332,8 @@
       <c r="T130" s="2"/>
       <c r="U130" s="2"/>
       <c r="V130" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W130" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26341,8 +26364,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="D131" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stehlíková Magdaléna")</f>
+        <v>Stehlíková Magdaléna</v>
+      </c>
+      <c r="E131" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -26359,7 +26388,10 @@
       <c r="S131" s="2"/>
       <c r="T131" s="2"/>
       <c r="U131" s="2"/>
-      <c r="V131" s="2"/>
+      <c r="V131" s="190">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
+      </c>
       <c r="W131" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -26389,8 +26421,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
+      <c r="D132" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dragoun Alfréd")</f>
+        <v>Dragoun Alfréd</v>
+      </c>
+      <c r="E132" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -26408,8 +26446,8 @@
       <c r="T132" s="2"/>
       <c r="U132" s="2"/>
       <c r="V132" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W132" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -61021,7 +61059,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -61053,28 +61091,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -61103,22 +61141,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -61140,20 +61178,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -61177,18 +61215,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -61215,15 +61253,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -61250,14 +61288,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -61281,14 +61319,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -61313,17 +61351,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -61348,14 +61386,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61568,7 +61606,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61893,7 +61931,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -62014,7 +62052,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62133,7 +62171,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62167,7 +62205,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62259,7 +62297,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62438,7 +62476,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62559,7 +62597,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62767,7 +62805,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62888,7 +62926,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63096,7 +63134,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63565,7 +63603,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63599,7 +63637,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63633,7 +63671,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63667,7 +63705,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63760,7 +63798,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -64026,7 +64064,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -64060,7 +64098,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64152,7 +64190,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64215,7 +64253,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64307,7 +64345,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64341,7 +64379,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64375,7 +64413,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64438,7 +64476,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64530,7 +64568,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64593,7 +64631,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64714,7 +64752,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64865,7 +64903,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65250,7 +65288,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>

--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="710">
   <si>
     <t>Datum</t>
   </si>
@@ -1842,136 +1842,136 @@
     <t>Počet hodin</t>
   </si>
   <si>
+    <t>Výdaje</t>
+  </si>
+  <si>
+    <t>Benzín</t>
+  </si>
+  <si>
+    <t>Auta</t>
+  </si>
+  <si>
+    <t>Suroviny</t>
+  </si>
+  <si>
+    <t>Ostatní</t>
+  </si>
+  <si>
+    <t>PHM - soukromé</t>
+  </si>
+  <si>
+    <t>Zavíral</t>
+  </si>
+  <si>
+    <t>Zrušené obj. ks</t>
+  </si>
+  <si>
+    <t>Zrušené obj. $</t>
+  </si>
+  <si>
+    <t>Počet zpožděných našich rozvozů +5 min</t>
+  </si>
+  <si>
+    <t>Průměrný make Time</t>
+  </si>
+  <si>
+    <t>Počet rozvozů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vlastní vůz </t>
+  </si>
+  <si>
+    <t>Vyplatit PHM</t>
+  </si>
+  <si>
+    <t>počet výdajových dokadů</t>
+  </si>
+  <si>
+    <t>Počet nezrušených celkem</t>
+  </si>
+  <si>
+    <t>Počet našich rozvozů</t>
+  </si>
+  <si>
+    <t>Počet pozdě přiřazeným WoltDrive 5+</t>
+  </si>
+  <si>
+    <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
+  </si>
+  <si>
+    <t>% zpožděných našich rozvozů +5 min</t>
+  </si>
+  <si>
+    <t>Počet zpožděných Woltdrivem</t>
+  </si>
+  <si>
+    <t>% doručených včas</t>
+  </si>
+  <si>
+    <t>% zpožděných Woltdrivem</t>
+  </si>
+  <si>
+    <t>Wolt drive</t>
+  </si>
+  <si>
+    <t>Vyber datum    &lt;----------&gt;</t>
+  </si>
+  <si>
+    <t>Celkem hodin Instor</t>
+  </si>
+  <si>
+    <t>Celkem hodin Kurýr</t>
+  </si>
+  <si>
+    <t>Počet dní</t>
+  </si>
+  <si>
+    <t>Yarushynskyi Vladyslav</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>29:00</t>
+  </si>
+  <si>
+    <t>Vychivskyi Volodymyr</t>
+  </si>
+  <si>
+    <t>112:00</t>
+  </si>
+  <si>
+    <t>Šebesta Tomáš</t>
+  </si>
+  <si>
+    <t>95:30</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
     <t>Nováková Adéla</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>Výdaje</t>
+    <t>13:00</t>
   </si>
   <si>
     <t>Putna Jaroslav</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Benzín</t>
-  </si>
-  <si>
-    <t>Auta</t>
-  </si>
-  <si>
-    <t>Suroviny</t>
-  </si>
-  <si>
-    <t>Ostatní</t>
-  </si>
-  <si>
-    <t>PHM - soukromé</t>
-  </si>
-  <si>
-    <t>Zavíral</t>
-  </si>
-  <si>
-    <t>Zrušené obj. ks</t>
-  </si>
-  <si>
-    <t>Zrušené obj. $</t>
-  </si>
-  <si>
-    <t>Počet zpožděných našich rozvozů +5 min</t>
-  </si>
-  <si>
-    <t>Průměrný make Time</t>
-  </si>
-  <si>
-    <t>Počet rozvozů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vlastní vůz </t>
-  </si>
-  <si>
-    <t>Vyplatit PHM</t>
-  </si>
-  <si>
-    <t>počet výdajových dokadů</t>
-  </si>
-  <si>
-    <t>Počet nezrušených celkem</t>
-  </si>
-  <si>
-    <t>Počet našich rozvozů</t>
-  </si>
-  <si>
-    <t>Počet pozdě přiřazeným WoltDrive 5+</t>
-  </si>
-  <si>
-    <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
-  </si>
-  <si>
-    <t>% zpožděných našich rozvozů +5 min</t>
-  </si>
-  <si>
-    <t>Počet zpožděných Woltdrivem</t>
-  </si>
-  <si>
-    <t>% doručených včas</t>
-  </si>
-  <si>
-    <t>% zpožděných Woltdrivem</t>
-  </si>
-  <si>
-    <t>Wolt drive</t>
-  </si>
-  <si>
-    <t>Vyber datum    &lt;----------&gt;</t>
-  </si>
-  <si>
-    <t>0#ERROR!</t>
-  </si>
-  <si>
-    <t>Celkem hodin Instor</t>
-  </si>
-  <si>
-    <t>Celkem hodin Kurýr</t>
-  </si>
-  <si>
-    <t>Počet dní</t>
-  </si>
-  <si>
-    <t>Šebesta Tomáš</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>29:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
+    <t>117:00</t>
   </si>
   <si>
     <t>Fáberová Kateřina</t>
   </si>
   <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
+    <t>16:00</t>
   </si>
   <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>11 min 03 s</t>
+    <t>12 min 35 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13250,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13299,7 +13299,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Čtvrtek</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -13458,9 +13458,7 @@
       <c r="F11" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="G11" s="45" t="s">
-        <v>607</v>
-      </c>
+      <c r="G11" s="45"/>
       <c r="I11" s="20"/>
       <c r="J11" s="46">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
@@ -13477,47 +13475,35 @@
         <f t="array" ref="A12">IF(ISBLANK(B12), 0, IF(ISNUMBER(MATCH(B12, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B12, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B12, HR!B:B, 0)) * (F12 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>607</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>608</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>609</v>
-      </c>
+      <c r="B12" s="50"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="52"/>
       <c r="F12" s="53" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>15:00</v>
+        <v>0:00</v>
       </c>
       <c r="I12" s="20"/>
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="54" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M12" s="18"/>
     </row>
     <row r="13">
       <c r="A13" s="49">
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
-        <v>1751.442</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>611</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>612</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>609</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="52"/>
       <c r="F13" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>07:00</v>
+        <v>0:00</v>
       </c>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
@@ -13525,7 +13511,7 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="22" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="M13" s="37"/>
     </row>
@@ -13547,7 +13533,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="57" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="M14" s="37"/>
     </row>
@@ -13568,7 +13554,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="57" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M15" s="37"/>
     </row>
@@ -13589,7 +13575,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="57" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="M16" s="37"/>
     </row>
@@ -13612,7 +13598,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="59" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="M17" s="60">
         <f>sum(I25:I31)</f>
@@ -13633,7 +13619,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="18"/>
@@ -13653,9 +13639,7 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="45" t="s">
-        <v>607</v>
-      </c>
+      <c r="G19" s="45"/>
       <c r="I19" s="20"/>
       <c r="M19" s="62"/>
     </row>
@@ -13704,16 +13688,16 @@
       <c r="H22" s="27"/>
       <c r="I22" s="18"/>
       <c r="J22" s="70" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="K22" s="70" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L22" s="71" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="M22" s="71" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23">
@@ -13757,25 +13741,25 @@
         <v>606</v>
       </c>
       <c r="G24" s="75" t="s">
+        <v>618</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>619</v>
+      </c>
+      <c r="I24" s="76" t="s">
+        <v>620</v>
+      </c>
+      <c r="J24" s="77" t="s">
+        <v>621</v>
+      </c>
+      <c r="K24" s="78" t="s">
+        <v>622</v>
+      </c>
+      <c r="L24" s="77" t="s">
         <v>623</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="M24" s="78" t="s">
         <v>624</v>
-      </c>
-      <c r="I24" s="76" t="s">
-        <v>625</v>
-      </c>
-      <c r="J24" s="77" t="s">
-        <v>626</v>
-      </c>
-      <c r="K24" s="78" t="s">
-        <v>627</v>
-      </c>
-      <c r="L24" s="77" t="s">
-        <v>628</v>
-      </c>
-      <c r="M24" s="78" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="25">
@@ -13874,14 +13858,14 @@
         <v>0</v>
       </c>
       <c r="J27" s="89" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K27" s="90"/>
       <c r="L27" s="77" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="M27" s="78" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -13978,10 +13962,10 @@
       <c r="J30" s="96"/>
       <c r="K30" s="96"/>
       <c r="L30" s="78" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="M30" s="78" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31">
@@ -14019,7 +14003,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="99" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
@@ -14102,9 +14086,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="G11 G19">
-      <formula1>"Nováková Adéla,Putna Jaroslav"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
       <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
     </dataValidation>
@@ -14140,13 +14121,13 @@
         <v>Prosek</v>
       </c>
       <c r="C1" s="107">
-        <v>46188.0</v>
+        <v>46174.0</v>
       </c>
       <c r="D1" s="108" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="E1" s="109">
-        <v>46188.0</v>
+        <v>46203.0</v>
       </c>
       <c r="F1" s="110" t="s">
         <v>586</v>
@@ -14171,18 +14152,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.0</v>
+        <v>0.3180380822647522</v>
       </c>
       <c r="H2" s="20"/>
-      <c r="I2" s="113" t="s">
-        <v>637</v>
+      <c r="I2" s="113">
+        <v>575843.4400000001</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>14580.200000000008</v>
+        <v>238081.89000000007</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14195,7 +14176,7 @@
       <c r="C3" s="26"/>
       <c r="D3" s="118" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pondělí</v>
+        <v>Úterý</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14204,7 +14185,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>1903.0</v>
+        <v>90909.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14224,20 +14205,20 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>7583.0</v>
+        <v>98299.65</v>
       </c>
       <c r="N4" s="116"/>
     </row>
     <row r="5">
       <c r="A5" s="121"/>
       <c r="B5" s="122" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="10"/>
       <c r="F5" s="123" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
@@ -14248,7 +14229,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>3557.0</v>
+        <v>73263.0</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14268,7 +14249,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>927.0</v>
+        <v>4961.0</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14276,14 +14257,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>26</v>
+        <v>336</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14328,7 +14309,7 @@
         <v>602</v>
       </c>
       <c r="C9" s="138" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D9" s="138" t="s">
         <v>606</v>
@@ -14338,67 +14319,75 @@
         <v>602</v>
       </c>
       <c r="G9" s="138" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="H9" s="138" t="s">
         <v>606</v>
       </c>
       <c r="I9" s="140" t="s">
-        <v>623</v>
-      </c>
-      <c r="J9" s="141" t="s">
-        <v>637</v>
+        <v>618</v>
+      </c>
+      <c r="J9" s="141">
+        <v>7.100000000064028</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>3956.0</v>
+        <v>42625.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="143"/>
       <c r="B10" s="144" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C10" s="145">
         <v>1.0</v>
       </c>
       <c r="D10" s="145" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="E10" s="146" t="s">
-        <v>643</v>
-      </c>
-      <c r="F10" s="144"/>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="147"/>
+        <v>637</v>
+      </c>
+      <c r="F10" s="144" t="s">
+        <v>638</v>
+      </c>
+      <c r="G10" s="145">
+        <v>10.0</v>
+      </c>
+      <c r="H10" s="145" t="s">
+        <v>639</v>
+      </c>
+      <c r="I10" s="147">
+        <v>49.0</v>
+      </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
       <c r="L10" s="142" t="s">
         <v>601</v>
       </c>
       <c r="M10" s="120">
-        <v>0.0</v>
+        <v>1245.0</v>
       </c>
       <c r="N10" s="116"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="143"/>
       <c r="B11" s="144" t="s">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="C11" s="145">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E11" s="146" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F11" s="144"/>
       <c r="G11" s="145"/>
@@ -14410,23 +14399,23 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>0.0</v>
+        <v>21256.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
       <c r="B12" s="144" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C12" s="145">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F12" s="144"/>
       <c r="G12" s="145"/>
@@ -14435,18 +14424,24 @@
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="150" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="111"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
-      <c r="B13" s="144"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
+      <c r="B13" s="144" t="s">
+        <v>645</v>
+      </c>
+      <c r="C13" s="145">
+        <v>12.0</v>
+      </c>
+      <c r="D13" s="145" t="s">
+        <v>646</v>
+      </c>
       <c r="E13" s="146" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14455,18 +14450,24 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="142" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="M13" s="120">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
-      <c r="B14" s="144"/>
-      <c r="C14" s="145"/>
-      <c r="D14" s="145"/>
+      <c r="B14" s="144" t="s">
+        <v>647</v>
+      </c>
+      <c r="C14" s="145">
+        <v>2.0</v>
+      </c>
+      <c r="D14" s="145" t="s">
+        <v>648</v>
+      </c>
       <c r="E14" s="146" t="s">
         <v>649</v>
       </c>
@@ -14477,7 +14478,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="151" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="M14" s="120">
         <v>0.0</v>
@@ -14499,10 +14500,10 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="151" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M15" s="120">
-        <v>0.0</v>
+        <v>140.0</v>
       </c>
       <c r="N15" s="116"/>
     </row>
@@ -14519,7 +14520,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="151" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="M16" s="120">
         <v>1165.0</v>
@@ -14539,10 +14540,10 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="153" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="M17" s="154">
-        <v>0.0</v>
+        <v>2205.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14573,16 +14574,16 @@
       <c r="H19" s="145"/>
       <c r="I19" s="147"/>
       <c r="J19" s="157" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="K19" s="158" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L19" s="159" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="M19" s="160" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="N19" s="161"/>
     </row>
@@ -14613,13 +14614,13 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="K21" s="165">
-        <v>0.0</v>
+        <v>5894.6</v>
       </c>
       <c r="L21" s="166">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="M21" s="167" t="s">
         <v>650</v>
@@ -14637,16 +14638,16 @@
       <c r="H22" s="145"/>
       <c r="I22" s="147"/>
       <c r="J22" s="168" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="K22" s="169" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="L22" s="170" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="M22" s="171" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="N22" s="156"/>
     </row>
@@ -14677,16 +14678,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="K24" s="166">
-        <v>89.0</v>
+        <v>1461.0</v>
       </c>
       <c r="L24" s="166">
-        <v>6.0</v>
+        <v>140.0</v>
       </c>
       <c r="M24" s="173">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14701,14 +14702,14 @@
       <c r="H25" s="145"/>
       <c r="I25" s="147"/>
       <c r="J25" s="174" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K25" s="90"/>
       <c r="L25" s="175" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="M25" s="176" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="N25" s="156"/>
     </row>
@@ -14739,14 +14740,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.16666666666666666</v>
+        <v>0.14754623440285208</v>
       </c>
       <c r="M27" s="180">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14762,10 +14763,10 @@
       <c r="I28" s="147"/>
       <c r="J28" s="181"/>
       <c r="L28" s="182" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="M28" s="176" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="N28" s="156"/>
     </row>
@@ -14797,10 +14798,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.8333333333333334</v>
+        <v>0.852453765597148</v>
       </c>
       <c r="M30" s="184">
-        <v>0.16666666666666666</v>
+        <v>0.11956420825906121</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14912,7 +14913,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="186"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="185"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -14946,7 +14947,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="186"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="185"/>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -15014,7 +15015,7 @@
       <c r="B5" s="186"/>
       <c r="C5" s="186"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="185"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -15048,7 +15049,7 @@
       <c r="B6" s="4"/>
       <c r="C6" s="186"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="185"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -15116,7 +15117,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="186"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="185"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -15150,7 +15151,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="186"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="185"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -15184,7 +15185,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="186"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="185"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -15243,6 +15244,7 @@
       <c r="AA11" s="185"/>
       <c r="AB11" s="185"/>
       <c r="AC11" s="185"/>
+      <c r="AD11" s="185"/>
       <c r="AE11" s="185"/>
       <c r="AF11" s="185"/>
     </row>
@@ -15393,7 +15395,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="185"/>
+      <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -15455,13 +15457,13 @@
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="185"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="K18" s="185"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -15489,7 +15491,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="186"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="185"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -15557,7 +15559,7 @@
       <c r="B21" s="4"/>
       <c r="C21" s="186"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="185"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -15625,7 +15627,7 @@
       <c r="B23" s="186"/>
       <c r="C23" s="186"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="185"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -15659,7 +15661,7 @@
       <c r="B24" s="186"/>
       <c r="C24" s="186"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="185"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -15693,7 +15695,7 @@
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="185"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -15760,7 +15762,7 @@
       <c r="B27" s="186"/>
       <c r="C27" s="186"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="185"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -15800,7 +15802,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="185"/>
+      <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
@@ -15828,7 +15830,7 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="185"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -15862,13 +15864,13 @@
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="185"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
+      <c r="K30" s="185"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
@@ -15896,7 +15898,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="186"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="185"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -15964,13 +15966,13 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="185"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="185"/>
+      <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -16134,7 +16136,7 @@
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="185"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -16202,7 +16204,7 @@
       <c r="B40" s="4"/>
       <c r="C40" s="186"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="185"/>
+      <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -16236,7 +16238,7 @@
       <c r="B41" s="4"/>
       <c r="C41" s="186"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="185"/>
+      <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -16270,7 +16272,7 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="185"/>
+      <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -16304,13 +16306,13 @@
       <c r="B43" s="4"/>
       <c r="C43" s="186"/>
       <c r="D43" s="4"/>
-      <c r="E43" s="185"/>
+      <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="185"/>
+      <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
@@ -16344,7 +16346,7 @@
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
+      <c r="K44" s="185"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
@@ -16372,7 +16374,7 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="185"/>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -16440,7 +16442,7 @@
       <c r="B47" s="4"/>
       <c r="C47" s="186"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="185"/>
+      <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -16508,7 +16510,7 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="185"/>
+      <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -16576,7 +16578,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="185"/>
+      <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16610,7 +16612,7 @@
       <c r="B52" s="186"/>
       <c r="C52" s="186"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+      <c r="E52" s="185"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -16644,7 +16646,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
+      <c r="E53" s="185"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16752,7 +16754,7 @@
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-      <c r="K56" s="185"/>
+      <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
@@ -16780,7 +16782,7 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="185"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -17024,7 +17026,7 @@
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
+      <c r="K64" s="185"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
@@ -17120,7 +17122,7 @@
       <c r="B67" s="4"/>
       <c r="C67" s="186"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="185"/>
+      <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -17153,7 +17155,7 @@
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
+      <c r="E68" s="185"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
@@ -17221,7 +17223,7 @@
       <c r="B70" s="4"/>
       <c r="C70" s="186"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="185"/>
+      <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -17255,13 +17257,13 @@
       <c r="B71" s="4"/>
       <c r="C71" s="186"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
+      <c r="E71" s="185"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
+      <c r="K71" s="185"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
@@ -17289,7 +17291,7 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="185"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
@@ -17323,13 +17325,13 @@
       <c r="B73" s="4"/>
       <c r="C73" s="186"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="185"/>
+      <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-      <c r="K73" s="185"/>
+      <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
@@ -17493,7 +17495,7 @@
       <c r="B78" s="4"/>
       <c r="C78" s="186"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
+      <c r="E78" s="185"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -17533,7 +17535,7 @@
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
-      <c r="K79" s="185"/>
+      <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
@@ -17635,7 +17637,7 @@
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
-      <c r="K82" s="185"/>
+      <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
@@ -17697,7 +17699,7 @@
       <c r="B84" s="4"/>
       <c r="C84" s="186"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
+      <c r="E84" s="185"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -17731,7 +17733,7 @@
       <c r="B85" s="4"/>
       <c r="C85" s="186"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="185"/>
+      <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -17765,13 +17767,13 @@
       <c r="B86" s="4"/>
       <c r="C86" s="186"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="185"/>
+      <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
-      <c r="K86" s="185"/>
+      <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
@@ -17799,7 +17801,7 @@
       <c r="B87" s="4"/>
       <c r="C87" s="186"/>
       <c r="D87" s="4"/>
-      <c r="E87" s="185"/>
+      <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
@@ -17833,7 +17835,7 @@
       <c r="B88" s="4"/>
       <c r="C88" s="186"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+      <c r="E88" s="185"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -17873,7 +17875,7 @@
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
-      <c r="K89" s="185"/>
+      <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
@@ -17930,22 +17932,22 @@
       <c r="AF90" s="185"/>
     </row>
     <row r="91">
-      <c r="A91" s="185"/>
-      <c r="B91" s="185"/>
-      <c r="C91" s="185"/>
-      <c r="D91" s="185"/>
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
       <c r="E91" s="185"/>
-      <c r="F91" s="185"/>
-      <c r="G91" s="185"/>
-      <c r="H91" s="185"/>
-      <c r="I91" s="185"/>
-      <c r="J91" s="185"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
       <c r="K91" s="185"/>
-      <c r="L91" s="185"/>
-      <c r="M91" s="185"/>
-      <c r="N91" s="185"/>
-      <c r="O91" s="185"/>
-      <c r="P91" s="185"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
       <c r="Q91" s="185"/>
       <c r="R91" s="185"/>
       <c r="S91" s="185"/>
@@ -17963,22 +17965,22 @@
       <c r="AF91" s="185"/>
     </row>
     <row r="92">
-      <c r="A92" s="185"/>
-      <c r="B92" s="185"/>
-      <c r="C92" s="185"/>
-      <c r="D92" s="185"/>
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
       <c r="E92" s="185"/>
-      <c r="F92" s="185"/>
-      <c r="G92" s="185"/>
-      <c r="H92" s="185"/>
-      <c r="I92" s="185"/>
-      <c r="J92" s="185"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
       <c r="K92" s="185"/>
-      <c r="L92" s="185"/>
-      <c r="M92" s="185"/>
-      <c r="N92" s="185"/>
-      <c r="O92" s="185"/>
-      <c r="P92" s="185"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
       <c r="Q92" s="185"/>
       <c r="R92" s="185"/>
       <c r="S92" s="185"/>
@@ -17996,22 +17998,22 @@
       <c r="AF92" s="185"/>
     </row>
     <row r="93">
-      <c r="A93" s="185"/>
-      <c r="B93" s="185"/>
-      <c r="C93" s="185"/>
-      <c r="D93" s="185"/>
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
       <c r="E93" s="185"/>
-      <c r="F93" s="185"/>
-      <c r="G93" s="185"/>
-      <c r="H93" s="185"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
       <c r="I93" s="185"/>
       <c r="J93" s="185"/>
       <c r="K93" s="185"/>
-      <c r="L93" s="185"/>
-      <c r="M93" s="185"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
       <c r="N93" s="185"/>
-      <c r="O93" s="185"/>
-      <c r="P93" s="185"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
       <c r="Q93" s="185"/>
       <c r="R93" s="185"/>
       <c r="S93" s="185"/>
@@ -18030,22 +18032,22 @@
       <c r="AF93" s="185"/>
     </row>
     <row r="94">
-      <c r="A94" s="185"/>
-      <c r="B94" s="185"/>
-      <c r="C94" s="185"/>
-      <c r="D94" s="185"/>
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
       <c r="E94" s="185"/>
-      <c r="F94" s="185"/>
-      <c r="G94" s="185"/>
-      <c r="H94" s="185"/>
-      <c r="I94" s="185"/>
-      <c r="J94" s="185"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
       <c r="K94" s="185"/>
-      <c r="L94" s="185"/>
-      <c r="M94" s="185"/>
-      <c r="N94" s="185"/>
-      <c r="O94" s="185"/>
-      <c r="P94" s="185"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
       <c r="Q94" s="185"/>
       <c r="R94" s="185"/>
       <c r="S94" s="185"/>
@@ -18063,22 +18065,22 @@
       <c r="AF94" s="185"/>
     </row>
     <row r="95">
-      <c r="A95" s="185"/>
-      <c r="B95" s="185"/>
-      <c r="C95" s="185"/>
-      <c r="D95" s="185"/>
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
       <c r="E95" s="185"/>
-      <c r="F95" s="185"/>
-      <c r="G95" s="185"/>
-      <c r="H95" s="185"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
       <c r="I95" s="185"/>
       <c r="J95" s="185"/>
       <c r="K95" s="185"/>
-      <c r="L95" s="185"/>
-      <c r="M95" s="185"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
       <c r="N95" s="185"/>
-      <c r="O95" s="185"/>
-      <c r="P95" s="185"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
       <c r="Q95" s="185"/>
       <c r="R95" s="185"/>
       <c r="S95" s="185"/>
@@ -18096,22 +18098,22 @@
       <c r="AF95" s="185"/>
     </row>
     <row r="96">
-      <c r="A96" s="185"/>
-      <c r="B96" s="185"/>
-      <c r="C96" s="185"/>
-      <c r="D96" s="185"/>
-      <c r="E96" s="185"/>
-      <c r="F96" s="185"/>
-      <c r="G96" s="185"/>
-      <c r="H96" s="185"/>
-      <c r="I96" s="185"/>
-      <c r="J96" s="185"/>
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
       <c r="K96" s="185"/>
-      <c r="L96" s="185"/>
-      <c r="M96" s="185"/>
-      <c r="N96" s="185"/>
-      <c r="O96" s="185"/>
-      <c r="P96" s="185"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
       <c r="Q96" s="185"/>
       <c r="R96" s="185"/>
       <c r="S96" s="185"/>
@@ -18129,22 +18131,22 @@
       <c r="AF96" s="185"/>
     </row>
     <row r="97">
-      <c r="A97" s="185"/>
-      <c r="B97" s="185"/>
-      <c r="C97" s="185"/>
-      <c r="D97" s="185"/>
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
       <c r="E97" s="185"/>
-      <c r="F97" s="185"/>
-      <c r="G97" s="185"/>
-      <c r="H97" s="185"/>
-      <c r="I97" s="185"/>
-      <c r="J97" s="185"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
       <c r="K97" s="185"/>
-      <c r="L97" s="185"/>
-      <c r="M97" s="185"/>
-      <c r="N97" s="185"/>
-      <c r="O97" s="185"/>
-      <c r="P97" s="185"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
       <c r="Q97" s="185"/>
       <c r="R97" s="185"/>
       <c r="S97" s="185"/>
@@ -18163,22 +18165,22 @@
       <c r="AF97" s="185"/>
     </row>
     <row r="98">
-      <c r="A98" s="185"/>
-      <c r="B98" s="185"/>
-      <c r="C98" s="185"/>
-      <c r="D98" s="185"/>
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
       <c r="E98" s="185"/>
-      <c r="F98" s="185"/>
-      <c r="G98" s="185"/>
-      <c r="H98" s="185"/>
-      <c r="I98" s="185"/>
-      <c r="J98" s="185"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
       <c r="K98" s="185"/>
-      <c r="L98" s="185"/>
-      <c r="M98" s="185"/>
-      <c r="N98" s="185"/>
-      <c r="O98" s="185"/>
-      <c r="P98" s="185"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
       <c r="Q98" s="185"/>
       <c r="R98" s="185"/>
       <c r="S98" s="185"/>

--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="716">
   <si>
     <t>Datum</t>
   </si>
@@ -1842,12 +1842,36 @@
     <t>Počet hodin</t>
   </si>
   <si>
+    <t>Šebesta Tomáš</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>Výdaje</t>
   </si>
   <si>
+    <t>Nováková Adéla</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>Benzín</t>
   </si>
   <si>
+    <t>Fáberová Kateřina</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
     <t>Auta</t>
   </si>
   <si>
@@ -1941,16 +1965,13 @@
     <t>112:00</t>
   </si>
   <si>
-    <t>Šebesta Tomáš</t>
-  </si>
-  <si>
-    <t>95:30</t>
+    <t>123:00</t>
   </si>
   <si>
     <t>23:00</t>
   </si>
   <si>
-    <t>Nováková Adéla</t>
+    <t>104:00</t>
   </si>
   <si>
     <t>13:00</t>
@@ -1959,19 +1980,16 @@
     <t>Putna Jaroslav</t>
   </si>
   <si>
-    <t>117:00</t>
-  </si>
-  <si>
-    <t>Fáberová Kateřina</t>
-  </si>
-  <si>
-    <t>16:00</t>
+    <t>146:30</t>
+  </si>
+  <si>
+    <t>24:00</t>
   </si>
   <si>
     <t>7:00</t>
   </si>
   <si>
-    <t>12 min 35 s</t>
+    <t>12 min 31 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13250,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46191.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13299,7 +13317,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Neděle</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -13458,7 +13476,9 @@
       <c r="F11" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="G11" s="45"/>
+      <c r="G11" s="45" t="s">
+        <v>607</v>
+      </c>
       <c r="I11" s="20"/>
       <c r="J11" s="46">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
@@ -13475,20 +13495,26 @@
         <f t="array" ref="A12">IF(ISBLANK(B12), 0, IF(ISNUMBER(MATCH(B12, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B12, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B12, HR!B:B, 0)) * (F12 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
+      <c r="B12" s="50" t="s">
+        <v>607</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>608</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>609</v>
+      </c>
       <c r="E12" s="52"/>
       <c r="F12" s="53" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>0:00</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I12" s="20"/>
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="54" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M12" s="18"/>
     </row>
@@ -13497,13 +13523,19 @@
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
+      <c r="B13" s="50" t="s">
+        <v>611</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>612</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>613</v>
+      </c>
       <c r="E13" s="52"/>
       <c r="F13" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>07:00</v>
       </c>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
@@ -13511,29 +13543,35 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="22" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="M13" s="37"/>
     </row>
     <row r="14">
       <c r="A14" s="49">
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
+        <v>1501.236</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>615</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>616</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>613</v>
+      </c>
       <c r="E14" s="55"/>
       <c r="F14" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>06:00</v>
       </c>
       <c r="G14" s="56"/>
       <c r="I14" s="20"/>
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="57" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="M14" s="37"/>
     </row>
@@ -13554,7 +13592,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="57" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="M15" s="37"/>
     </row>
@@ -13575,7 +13613,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="57" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="M16" s="37"/>
     </row>
@@ -13598,7 +13636,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="59" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="M17" s="60">
         <f>sum(I25:I31)</f>
@@ -13619,7 +13657,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="18"/>
@@ -13639,7 +13677,9 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="45"/>
+      <c r="G19" s="45" t="s">
+        <v>611</v>
+      </c>
       <c r="I19" s="20"/>
       <c r="M19" s="62"/>
     </row>
@@ -13688,16 +13728,16 @@
       <c r="H22" s="27"/>
       <c r="I22" s="18"/>
       <c r="J22" s="70" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="K22" s="70" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="L22" s="71" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="M22" s="71" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="23">
@@ -13741,25 +13781,25 @@
         <v>606</v>
       </c>
       <c r="G24" s="75" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="H24" s="75" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="J24" s="77" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="K24" s="78" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="L24" s="77" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="M24" s="78" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
     </row>
     <row r="25">
@@ -13858,14 +13898,14 @@
         <v>0</v>
       </c>
       <c r="J27" s="89" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="K27" s="90"/>
       <c r="L27" s="77" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="M27" s="78" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -13962,10 +14002,10 @@
       <c r="J30" s="96"/>
       <c r="K30" s="96"/>
       <c r="L30" s="78" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M30" s="78" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31">
@@ -14003,7 +14043,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="99" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
@@ -14086,11 +14126,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B12:B21">
-      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
       <formula1>"Hanibal Filip,Mikuš Pavel,Šmídová Sabina,Kormash Liubov,Vychivskyi Volodymyr,Hřebík Martin,Reischl Jan,Kulinič Michail,Kačena Stanislav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B12:B21">
+      <formula1>"Nedbal Michal,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G11 G19">
+      <formula1>"Šebesta Tomáš,Nováková Adéla,Fáberová Kateřina"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -14124,7 +14167,7 @@
         <v>46174.0</v>
       </c>
       <c r="D1" s="108" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="E1" s="109">
         <v>46203.0</v>
@@ -14152,18 +14195,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.3180380822647522</v>
+        <v>0.31312068182483815</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>575843.4400000001</v>
+        <v>693189.9400000001</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>238081.89000000007</v>
+        <v>290469.6900000001</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14185,7 +14228,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>90909.0</v>
+        <v>108075.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14205,20 +14248,20 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>98299.65</v>
+        <v>113157.65</v>
       </c>
       <c r="N4" s="116"/>
     </row>
     <row r="5">
       <c r="A5" s="121"/>
       <c r="B5" s="122" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="10"/>
       <c r="F5" s="123" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
@@ -14229,7 +14272,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>73263.0</v>
+        <v>86888.1</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14249,7 +14292,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>4961.0</v>
+        <v>7858.6</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14257,7 +14300,7 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>336</v>
+        <v>409.5</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
@@ -14309,7 +14352,7 @@
         <v>602</v>
       </c>
       <c r="C9" s="138" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="D9" s="138" t="s">
         <v>606</v>
@@ -14319,48 +14362,48 @@
         <v>602</v>
       </c>
       <c r="G9" s="138" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="H9" s="138" t="s">
         <v>606</v>
       </c>
       <c r="I9" s="140" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="J9" s="141">
-        <v>7.100000000064028</v>
+        <v>7.100000000085856</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>42625.0</v>
+        <v>53801.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="143"/>
       <c r="B10" s="144" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C10" s="145">
         <v>1.0</v>
       </c>
       <c r="D10" s="145" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E10" s="146" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="F10" s="144" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="G10" s="145">
         <v>10.0</v>
       </c>
       <c r="H10" s="145" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="I10" s="147">
         <v>49.0</v>
@@ -14378,16 +14421,16 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="143"/>
       <c r="B11" s="144" t="s">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="C11" s="145">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E11" s="146" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F11" s="144"/>
       <c r="G11" s="145"/>
@@ -14399,23 +14442,23 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>21256.0</v>
+        <v>24603.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
       <c r="B12" s="144" t="s">
-        <v>643</v>
+        <v>611</v>
       </c>
       <c r="C12" s="145">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="F12" s="144"/>
       <c r="G12" s="145"/>
@@ -14424,7 +14467,7 @@
       <c r="J12" s="35"/>
       <c r="K12" s="20"/>
       <c r="L12" s="150" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="111"/>
@@ -14432,16 +14475,16 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
       <c r="B13" s="144" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="C13" s="145">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="D13" s="145" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="E13" s="146" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14450,26 +14493,26 @@
       <c r="J13" s="35"/>
       <c r="K13" s="20"/>
       <c r="L13" s="142" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="M13" s="120">
-        <v>1700.0</v>
+        <v>2400.0</v>
       </c>
       <c r="N13" s="116"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
       <c r="B14" s="144" t="s">
-        <v>647</v>
+        <v>615</v>
       </c>
       <c r="C14" s="145">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D14" s="145" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E14" s="146" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14478,7 +14521,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="151" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="M14" s="120">
         <v>0.0</v>
@@ -14491,7 +14534,7 @@
       <c r="C15" s="145"/>
       <c r="D15" s="145"/>
       <c r="E15" s="146" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14500,7 +14543,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="151" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="M15" s="120">
         <v>140.0</v>
@@ -14520,10 +14563,10 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="151" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="M16" s="120">
-        <v>1165.0</v>
+        <v>2354.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
@@ -14540,7 +14583,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="153" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="M17" s="154">
         <v>2205.0</v>
@@ -14574,16 +14617,16 @@
       <c r="H19" s="145"/>
       <c r="I19" s="147"/>
       <c r="J19" s="157" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="K19" s="158" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="L19" s="159" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="M19" s="160" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="N19" s="161"/>
     </row>
@@ -14614,16 +14657,16 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="K21" s="165">
-        <v>5894.6</v>
+        <v>8044.400000000001</v>
       </c>
       <c r="L21" s="166">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="M21" s="167" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="N21" s="156"/>
     </row>
@@ -14638,16 +14681,16 @@
       <c r="H22" s="145"/>
       <c r="I22" s="147"/>
       <c r="J22" s="168" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="K22" s="169" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="L22" s="170" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="M22" s="171" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="N22" s="156"/>
     </row>
@@ -14681,13 +14724,13 @@
         <v>9.0</v>
       </c>
       <c r="K24" s="166">
-        <v>1461.0</v>
+        <v>1783.0</v>
       </c>
       <c r="L24" s="166">
-        <v>140.0</v>
+        <v>175.0</v>
       </c>
       <c r="M24" s="173">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14702,14 +14745,14 @@
       <c r="H25" s="145"/>
       <c r="I25" s="147"/>
       <c r="J25" s="174" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="K25" s="90"/>
       <c r="L25" s="175" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="M25" s="176" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="N25" s="156"/>
     </row>
@@ -14740,14 +14783,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.14754623440285208</v>
+        <v>0.14638171426097124</v>
       </c>
       <c r="M27" s="180">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14763,10 +14806,10 @@
       <c r="I28" s="147"/>
       <c r="J28" s="181"/>
       <c r="L28" s="182" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M28" s="176" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="N28" s="156"/>
     </row>
@@ -14798,10 +14841,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.852453765597148</v>
+        <v>0.8536182857390289</v>
       </c>
       <c r="M30" s="184">
-        <v>0.11956420825906121</v>
+        <v>0.12281790277146315</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -15151,7 +15194,7 @@
       <c r="B9" s="4"/>
       <c r="C9" s="186"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="185"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -15185,7 +15228,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="186"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="185"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -15395,7 +15438,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="K16" s="185"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -15457,13 +15500,13 @@
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="185"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="185"/>
+      <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -15491,7 +15534,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="186"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="185"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -15593,7 +15636,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="185"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -15695,7 +15738,7 @@
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="185"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -15729,7 +15772,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="186"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="185"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -15802,7 +15845,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="185"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
@@ -15830,13 +15873,13 @@
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="185"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="185"/>
+      <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
@@ -15864,7 +15907,7 @@
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="185"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -15898,7 +15941,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="186"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="185"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -15966,13 +16009,13 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="185"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
+      <c r="K33" s="185"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
@@ -16006,7 +16049,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="185"/>
+      <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
@@ -16068,7 +16111,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="186"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="185"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -16102,7 +16145,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="186"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="185"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -16136,7 +16179,7 @@
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="185"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -16170,7 +16213,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="185"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -16210,7 +16253,7 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="185"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -16272,7 +16315,7 @@
       <c r="B42" s="4"/>
       <c r="C42" s="186"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="185"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -16312,7 +16355,7 @@
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="185"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
@@ -16408,7 +16451,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="186"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="185"/>
+      <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -16448,7 +16491,7 @@
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-      <c r="K47" s="185"/>
+      <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -16476,13 +16519,13 @@
       <c r="B48" s="4"/>
       <c r="C48" s="186"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+      <c r="E48" s="185"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
+      <c r="K48" s="185"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -16510,7 +16553,7 @@
       <c r="B49" s="4"/>
       <c r="C49" s="186"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="185"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -16544,7 +16587,7 @@
       <c r="B50" s="4"/>
       <c r="C50" s="186"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="185"/>
+      <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -16578,7 +16621,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="186"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="185"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16646,7 +16689,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="186"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="185"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16720,7 +16763,7 @@
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-      <c r="K55" s="185"/>
+      <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
@@ -16748,13 +16791,13 @@
       <c r="B56" s="4"/>
       <c r="C56" s="186"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
+      <c r="E56" s="185"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
+      <c r="K56" s="185"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
@@ -16782,7 +16825,7 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="185"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -16822,7 +16865,7 @@
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
-      <c r="K58" s="185"/>
+      <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
@@ -16884,7 +16927,7 @@
       <c r="B60" s="4"/>
       <c r="C60" s="186"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="185"/>
+      <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -16986,7 +17029,7 @@
       <c r="B63" s="4"/>
       <c r="C63" s="186"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="185"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -17054,7 +17097,7 @@
       <c r="B65" s="4"/>
       <c r="C65" s="186"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
+      <c r="E65" s="185"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -17122,7 +17165,7 @@
       <c r="B67" s="4"/>
       <c r="C67" s="186"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
+      <c r="E67" s="185"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -17229,7 +17272,7 @@
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
-      <c r="K70" s="185"/>
+      <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
@@ -17257,7 +17300,7 @@
       <c r="B71" s="4"/>
       <c r="C71" s="186"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="185"/>
+      <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -17291,13 +17334,13 @@
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="185"/>
+      <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
-      <c r="K72" s="185"/>
+      <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
@@ -17325,13 +17368,13 @@
       <c r="B73" s="4"/>
       <c r="C73" s="186"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="185"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
+      <c r="K73" s="185"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
@@ -17359,7 +17402,7 @@
       <c r="B74" s="186"/>
       <c r="C74" s="186"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
+      <c r="E74" s="185"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
@@ -17427,7 +17470,7 @@
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="185"/>
+      <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -17495,7 +17538,7 @@
       <c r="B78" s="4"/>
       <c r="C78" s="186"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="185"/>
+      <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -17535,7 +17578,7 @@
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
+      <c r="K79" s="185"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
@@ -17569,7 +17612,7 @@
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
-      <c r="K80" s="185"/>
+      <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
@@ -17637,7 +17680,7 @@
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
+      <c r="K82" s="185"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
@@ -17665,7 +17708,7 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="185"/>
+      <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -17699,7 +17742,7 @@
       <c r="B84" s="4"/>
       <c r="C84" s="186"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="185"/>
+      <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -17773,7 +17816,7 @@
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
+      <c r="K86" s="185"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
@@ -17835,7 +17878,7 @@
       <c r="B88" s="4"/>
       <c r="C88" s="186"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="185"/>
+      <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -17875,7 +17918,7 @@
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
+      <c r="K89" s="185"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
@@ -17903,7 +17946,7 @@
       <c r="B90" s="4"/>
       <c r="C90" s="186"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="185"/>
+      <c r="E90" s="4"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
@@ -17969,7 +18012,7 @@
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="185"/>
+      <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
@@ -18006,12 +18049,12 @@
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
-      <c r="I93" s="185"/>
-      <c r="J93" s="185"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
       <c r="K93" s="185"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
-      <c r="N93" s="185"/>
+      <c r="N93" s="4"/>
       <c r="O93" s="4"/>
       <c r="P93" s="4"/>
       <c r="Q93" s="185"/>
@@ -18036,7 +18079,7 @@
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
-      <c r="E94" s="185"/>
+      <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
@@ -18069,16 +18112,16 @@
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="185"/>
+      <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
-      <c r="I95" s="185"/>
-      <c r="J95" s="185"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
       <c r="K95" s="185"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
-      <c r="N95" s="185"/>
+      <c r="N95" s="4"/>
       <c r="O95" s="4"/>
       <c r="P95" s="4"/>
       <c r="Q95" s="185"/>
@@ -18102,7 +18145,7 @@
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
+      <c r="E96" s="185"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -18135,7 +18178,7 @@
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="185"/>
+      <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -18169,7 +18212,7 @@
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
-      <c r="E98" s="185"/>
+      <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -18198,22 +18241,22 @@
       <c r="AF98" s="185"/>
     </row>
     <row r="99">
-      <c r="A99" s="185"/>
-      <c r="B99" s="185"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="185"/>
-      <c r="E99" s="185"/>
-      <c r="F99" s="185"/>
-      <c r="G99" s="185"/>
-      <c r="H99" s="185"/>
-      <c r="I99" s="185"/>
-      <c r="J99" s="185"/>
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="186"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
       <c r="K99" s="185"/>
-      <c r="L99" s="185"/>
-      <c r="M99" s="185"/>
-      <c r="N99" s="185"/>
-      <c r="O99" s="185"/>
-      <c r="P99" s="185"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
       <c r="Q99" s="185"/>
       <c r="R99" s="185"/>
       <c r="S99" s="185"/>
@@ -18232,22 +18275,22 @@
       <c r="AF99" s="185"/>
     </row>
     <row r="100">
-      <c r="A100" s="185"/>
-      <c r="B100" s="185"/>
-      <c r="C100" s="187"/>
-      <c r="D100" s="185"/>
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="186"/>
+      <c r="D100" s="4"/>
       <c r="E100" s="185"/>
-      <c r="F100" s="185"/>
-      <c r="G100" s="185"/>
-      <c r="H100" s="185"/>
-      <c r="I100" s="185"/>
-      <c r="J100" s="185"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
       <c r="K100" s="185"/>
-      <c r="L100" s="185"/>
-      <c r="M100" s="185"/>
-      <c r="N100" s="185"/>
-      <c r="O100" s="185"/>
-      <c r="P100" s="185"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
       <c r="Q100" s="185"/>
       <c r="R100" s="185"/>
       <c r="S100" s="185"/>
@@ -18265,22 +18308,22 @@
       <c r="AF100" s="185"/>
     </row>
     <row r="101">
-      <c r="A101" s="185"/>
-      <c r="B101" s="185"/>
-      <c r="C101" s="185"/>
-      <c r="D101" s="185"/>
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
       <c r="E101" s="185"/>
-      <c r="F101" s="185"/>
-      <c r="G101" s="185"/>
-      <c r="H101" s="185"/>
-      <c r="I101" s="185"/>
-      <c r="J101" s="185"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
       <c r="K101" s="185"/>
-      <c r="L101" s="185"/>
-      <c r="M101" s="185"/>
-      <c r="N101" s="185"/>
-      <c r="O101" s="185"/>
-      <c r="P101" s="185"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
       <c r="Q101" s="185"/>
       <c r="R101" s="185"/>
       <c r="S101" s="185"/>
@@ -18298,22 +18341,22 @@
       <c r="AF101" s="185"/>
     </row>
     <row r="102">
-      <c r="A102" s="185"/>
-      <c r="B102" s="185"/>
-      <c r="C102" s="187"/>
-      <c r="D102" s="185"/>
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="186"/>
+      <c r="D102" s="4"/>
       <c r="E102" s="185"/>
-      <c r="F102" s="185"/>
-      <c r="G102" s="185"/>
-      <c r="H102" s="185"/>
-      <c r="I102" s="185"/>
-      <c r="J102" s="185"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
       <c r="K102" s="185"/>
-      <c r="L102" s="185"/>
-      <c r="M102" s="185"/>
-      <c r="N102" s="185"/>
-      <c r="O102" s="185"/>
-      <c r="P102" s="185"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
       <c r="Q102" s="185"/>
       <c r="R102" s="185"/>
       <c r="S102" s="185"/>
@@ -18331,22 +18374,22 @@
       <c r="AF102" s="185"/>
     </row>
     <row r="103">
-      <c r="A103" s="185"/>
-      <c r="B103" s="185"/>
-      <c r="C103" s="187"/>
-      <c r="D103" s="185"/>
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="186"/>
+      <c r="D103" s="4"/>
       <c r="E103" s="185"/>
-      <c r="F103" s="185"/>
-      <c r="G103" s="185"/>
-      <c r="H103" s="185"/>
-      <c r="I103" s="185"/>
-      <c r="J103" s="185"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
       <c r="K103" s="185"/>
-      <c r="L103" s="185"/>
-      <c r="M103" s="185"/>
-      <c r="N103" s="185"/>
-      <c r="O103" s="185"/>
-      <c r="P103" s="185"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
       <c r="Q103" s="185"/>
       <c r="R103" s="185"/>
       <c r="S103" s="185"/>
@@ -18365,22 +18408,22 @@
       <c r="AF103" s="185"/>
     </row>
     <row r="104">
-      <c r="A104" s="185"/>
-      <c r="B104" s="185"/>
-      <c r="C104" s="185"/>
-      <c r="D104" s="185"/>
-      <c r="E104" s="185"/>
-      <c r="F104" s="185"/>
-      <c r="G104" s="185"/>
-      <c r="H104" s="185"/>
-      <c r="I104" s="185"/>
-      <c r="J104" s="185"/>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
       <c r="K104" s="185"/>
-      <c r="L104" s="185"/>
-      <c r="M104" s="185"/>
-      <c r="N104" s="185"/>
-      <c r="O104" s="185"/>
-      <c r="P104" s="185"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
       <c r="Q104" s="185"/>
       <c r="R104" s="185"/>
       <c r="S104" s="185"/>
@@ -18399,22 +18442,22 @@
       <c r="AF104" s="185"/>
     </row>
     <row r="105">
-      <c r="A105" s="185"/>
-      <c r="B105" s="185"/>
-      <c r="C105" s="187"/>
-      <c r="D105" s="185"/>
-      <c r="E105" s="185"/>
-      <c r="F105" s="185"/>
-      <c r="G105" s="185"/>
-      <c r="H105" s="185"/>
-      <c r="I105" s="185"/>
-      <c r="J105" s="185"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="186"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
       <c r="K105" s="185"/>
-      <c r="L105" s="185"/>
-      <c r="M105" s="185"/>
-      <c r="N105" s="185"/>
-      <c r="O105" s="185"/>
-      <c r="P105" s="185"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
       <c r="Q105" s="185"/>
       <c r="R105" s="185"/>
       <c r="S105" s="185"/>
@@ -18433,22 +18476,22 @@
       <c r="AF105" s="185"/>
     </row>
     <row r="106">
-      <c r="A106" s="185"/>
-      <c r="B106" s="185"/>
-      <c r="C106" s="185"/>
-      <c r="D106" s="185"/>
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
       <c r="E106" s="185"/>
-      <c r="F106" s="185"/>
-      <c r="G106" s="185"/>
-      <c r="H106" s="185"/>
-      <c r="I106" s="185"/>
-      <c r="J106" s="185"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
       <c r="K106" s="185"/>
-      <c r="L106" s="185"/>
-      <c r="M106" s="185"/>
-      <c r="N106" s="185"/>
-      <c r="O106" s="185"/>
-      <c r="P106" s="185"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
       <c r="Q106" s="185"/>
       <c r="R106" s="185"/>
       <c r="S106" s="185"/>
@@ -18467,22 +18510,22 @@
       <c r="AF106" s="185"/>
     </row>
     <row r="107">
-      <c r="A107" s="185"/>
-      <c r="B107" s="185"/>
-      <c r="C107" s="185"/>
-      <c r="D107" s="185"/>
-      <c r="E107" s="185"/>
-      <c r="F107" s="185"/>
-      <c r="G107" s="185"/>
-      <c r="H107" s="185"/>
-      <c r="I107" s="185"/>
-      <c r="J107" s="185"/>
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
       <c r="K107" s="185"/>
-      <c r="L107" s="185"/>
-      <c r="M107" s="185"/>
-      <c r="N107" s="185"/>
-      <c r="O107" s="185"/>
-      <c r="P107" s="185"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
       <c r="Q107" s="185"/>
       <c r="R107" s="185"/>
       <c r="S107" s="185"/>
@@ -18501,22 +18544,22 @@
       <c r="AF107" s="185"/>
     </row>
     <row r="108">
-      <c r="A108" s="185"/>
-      <c r="B108" s="185"/>
-      <c r="C108" s="187"/>
-      <c r="D108" s="185"/>
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="186"/>
+      <c r="D108" s="4"/>
       <c r="E108" s="185"/>
-      <c r="F108" s="185"/>
-      <c r="G108" s="185"/>
-      <c r="H108" s="185"/>
-      <c r="I108" s="185"/>
-      <c r="J108" s="185"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
       <c r="K108" s="185"/>
-      <c r="L108" s="185"/>
-      <c r="M108" s="185"/>
-      <c r="N108" s="185"/>
-      <c r="O108" s="185"/>
-      <c r="P108" s="185"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
       <c r="Q108" s="185"/>
       <c r="R108" s="185"/>
       <c r="S108" s="185"/>
@@ -18535,22 +18578,22 @@
       <c r="AF108" s="185"/>
     </row>
     <row r="109">
-      <c r="A109" s="185"/>
-      <c r="B109" s="185"/>
-      <c r="C109" s="185"/>
-      <c r="D109" s="185"/>
-      <c r="E109" s="185"/>
-      <c r="F109" s="185"/>
-      <c r="G109" s="185"/>
-      <c r="H109" s="185"/>
-      <c r="I109" s="185"/>
-      <c r="J109" s="185"/>
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
       <c r="K109" s="185"/>
-      <c r="L109" s="185"/>
-      <c r="M109" s="185"/>
-      <c r="N109" s="185"/>
-      <c r="O109" s="185"/>
-      <c r="P109" s="185"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
       <c r="Q109" s="185"/>
       <c r="R109" s="185"/>
       <c r="S109" s="185"/>
@@ -19039,6 +19082,7 @@
       <c r="O124" s="185"/>
       <c r="P124" s="185"/>
       <c r="Q124" s="185"/>
+      <c r="R124" s="185"/>
       <c r="S124" s="185"/>
       <c r="T124" s="185"/>
       <c r="U124" s="185"/>
@@ -19047,10 +19091,42 @@
       <c r="X124" s="185"/>
       <c r="Y124" s="185"/>
       <c r="Z124" s="185"/>
+      <c r="AA124" s="185"/>
       <c r="AB124" s="185"/>
       <c r="AC124" s="185"/>
+      <c r="AD124" s="185"/>
       <c r="AE124" s="185"/>
       <c r="AF124" s="185"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="185"/>
+      <c r="B125" s="185"/>
+      <c r="C125" s="185"/>
+      <c r="D125" s="185"/>
+      <c r="E125" s="185"/>
+      <c r="F125" s="185"/>
+      <c r="G125" s="185"/>
+      <c r="H125" s="185"/>
+      <c r="I125" s="185"/>
+      <c r="J125" s="185"/>
+      <c r="K125" s="185"/>
+      <c r="L125" s="185"/>
+      <c r="M125" s="185"/>
+      <c r="O125" s="185"/>
+      <c r="P125" s="185"/>
+      <c r="Q125" s="185"/>
+      <c r="S125" s="185"/>
+      <c r="T125" s="185"/>
+      <c r="U125" s="185"/>
+      <c r="V125" s="185"/>
+      <c r="W125" s="185"/>
+      <c r="X125" s="185"/>
+      <c r="Y125" s="185"/>
+      <c r="Z125" s="185"/>
+      <c r="AB125" s="185"/>
+      <c r="AC125" s="185"/>
+      <c r="AE125" s="185"/>
+      <c r="AF125" s="185"/>
     </row>
     <row r="128">
       <c r="C128" s="187"/>
@@ -19226,10 +19302,10 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -19481,7 +19557,7 @@
       </c>
       <c r="B8" s="192" t="str">
         <f>IF(OR(E8=Report!$B$1, F8=Report!$B$1, G8=Report!$B$1, H8=Report!$B$1), D8, "")</f>
-        <v>Ahurieva Viktoriia</v>
+        <v/>
       </c>
       <c r="C8" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -19504,8 +19580,8 @@
         <v>Výroba</v>
       </c>
       <c r="H8" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -19943,8 +20019,8 @@
         <v>Malešice</v>
       </c>
       <c r="F15" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -61061,7 +61137,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="194" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -61093,28 +61169,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="I2" s="185"/>
       <c r="J2" s="185"/>
@@ -61143,22 +61219,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C3" s="185"/>
       <c r="D3" s="185"/>
       <c r="E3" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="F3" s="185"/>
       <c r="G3" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="I3" s="185"/>
       <c r="J3" s="185"/>
@@ -61180,20 +61256,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D4" s="185"/>
       <c r="E4" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="G4" s="185"/>
       <c r="H4" s="185"/>
@@ -61217,18 +61293,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E5" s="185"/>
       <c r="F5" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="G5" s="185"/>
       <c r="H5" s="185"/>
@@ -61255,15 +61331,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E6" s="185"/>
       <c r="F6" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
@@ -61290,14 +61366,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="G7" s="185"/>
       <c r="I7" s="185"/>
@@ -61321,14 +61397,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="F8" s="185"/>
       <c r="H8" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="I8" s="185"/>
       <c r="J8" s="185"/>
@@ -61353,17 +61429,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="H9" s="185"/>
       <c r="I9" s="185"/>
@@ -61388,14 +61464,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="F10" s="185"/>
       <c r="G10" s="4" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="I10" s="185"/>
       <c r="J10" s="185"/>
@@ -61608,7 +61684,7 @@
       <c r="Y19" s="185"/>
       <c r="Z19" s="185"/>
       <c r="AA19" s="4" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61933,7 +62009,7 @@
       <c r="Y30" s="185"/>
       <c r="Z30" s="185"/>
       <c r="AA30" s="4" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -62054,7 +62130,7 @@
       <c r="Y34" s="185"/>
       <c r="Z34" s="185"/>
       <c r="AA34" s="4" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62173,7 +62249,7 @@
       <c r="Y38" s="185"/>
       <c r="Z38" s="185"/>
       <c r="AA38" s="4" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62207,7 +62283,7 @@
       <c r="Y39" s="185"/>
       <c r="Z39" s="185"/>
       <c r="AA39" s="4" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62299,7 +62375,7 @@
       <c r="Y42" s="185"/>
       <c r="Z42" s="185"/>
       <c r="AA42" s="4" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62478,7 +62554,7 @@
       <c r="Y48" s="185"/>
       <c r="Z48" s="185"/>
       <c r="AA48" s="4" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62599,7 +62675,7 @@
       <c r="Y52" s="185"/>
       <c r="Z52" s="185"/>
       <c r="AA52" s="4" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62807,7 +62883,7 @@
       <c r="Y59" s="185"/>
       <c r="Z59" s="185"/>
       <c r="AA59" s="4" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62928,7 +63004,7 @@
       <c r="Y63" s="185"/>
       <c r="Z63" s="185"/>
       <c r="AA63" s="4" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63136,7 +63212,7 @@
       <c r="Y70" s="185"/>
       <c r="Z70" s="185"/>
       <c r="AA70" s="4" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63605,7 +63681,7 @@
       <c r="Y86" s="185"/>
       <c r="Z86" s="185"/>
       <c r="AA86" s="4" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63639,7 +63715,7 @@
       <c r="Y87" s="185"/>
       <c r="Z87" s="185"/>
       <c r="AA87" s="4" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63673,7 +63749,7 @@
       <c r="Y88" s="185"/>
       <c r="Z88" s="185"/>
       <c r="AA88" s="4" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63707,7 +63783,7 @@
       <c r="Y89" s="185"/>
       <c r="Z89" s="185"/>
       <c r="AA89" s="4" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63800,7 +63876,7 @@
       <c r="Y92" s="185"/>
       <c r="Z92" s="185"/>
       <c r="AA92" s="4" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -64066,7 +64142,7 @@
       <c r="Y101" s="185"/>
       <c r="Z101" s="185"/>
       <c r="AA101" s="4" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -64100,7 +64176,7 @@
       <c r="Y102" s="185"/>
       <c r="Z102" s="185"/>
       <c r="AA102" s="4" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64192,7 +64268,7 @@
       <c r="Y105" s="185"/>
       <c r="Z105" s="185"/>
       <c r="AA105" s="4" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64255,7 +64331,7 @@
       <c r="Y107" s="185"/>
       <c r="Z107" s="185"/>
       <c r="AA107" s="4" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64347,7 +64423,7 @@
       <c r="Y110" s="185"/>
       <c r="Z110" s="185"/>
       <c r="AA110" s="4" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64381,7 +64457,7 @@
       <c r="Y111" s="185"/>
       <c r="Z111" s="185"/>
       <c r="AA111" s="4" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64415,7 +64491,7 @@
       <c r="Y112" s="185"/>
       <c r="Z112" s="185"/>
       <c r="AA112" s="4" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64478,7 +64554,7 @@
       <c r="Y114" s="185"/>
       <c r="Z114" s="185"/>
       <c r="AA114" s="4" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64570,7 +64646,7 @@
       <c r="Y117" s="185"/>
       <c r="Z117" s="185"/>
       <c r="AA117" s="4" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64633,7 +64709,7 @@
       <c r="Y119" s="185"/>
       <c r="Z119" s="185"/>
       <c r="AA119" s="4" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64754,7 +64830,7 @@
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
       <c r="AA123" s="4" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64905,7 +64981,7 @@
       <c r="Y128" s="185"/>
       <c r="Z128" s="185"/>
       <c r="AA128" s="4" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65290,7 +65366,7 @@
       <c r="Y141" s="185"/>
       <c r="Z141" s="185"/>
       <c r="AA141" s="4" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>

--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -1848,145 +1848,145 @@
     <t>10:00</t>
   </si>
   <si>
-    <t>17</t>
+    <t>01:00</t>
   </si>
   <si>
     <t>Výdaje</t>
   </si>
   <si>
+    <t>Fáberová Kateřina</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Benzín</t>
+  </si>
+  <si>
+    <t>Auta</t>
+  </si>
+  <si>
+    <t>Suroviny</t>
+  </si>
+  <si>
+    <t>Ostatní</t>
+  </si>
+  <si>
+    <t>PHM - soukromé</t>
+  </si>
+  <si>
+    <t>Zavíral</t>
+  </si>
+  <si>
+    <t>Zrušené obj. ks</t>
+  </si>
+  <si>
+    <t>Zrušené obj. $</t>
+  </si>
+  <si>
+    <t>Počet zpožděných našich rozvozů +5 min</t>
+  </si>
+  <si>
+    <t>Průměrný make Time</t>
+  </si>
+  <si>
+    <t>Počet rozvozů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vlastní vůz </t>
+  </si>
+  <si>
+    <t>Vyplatit PHM</t>
+  </si>
+  <si>
+    <t>počet výdajových dokadů</t>
+  </si>
+  <si>
+    <t>Počet nezrušených celkem</t>
+  </si>
+  <si>
+    <t>Počet našich rozvozů</t>
+  </si>
+  <si>
+    <t>Počet pozdě přiřazeným WoltDrive 5+</t>
+  </si>
+  <si>
+    <t>Vychivskyi Volodymyr</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
+  </si>
+  <si>
+    <t>% zpožděných našich rozvozů +5 min</t>
+  </si>
+  <si>
+    <t>Počet zpožděných Woltdrivem</t>
+  </si>
+  <si>
+    <t>% doručených včas</t>
+  </si>
+  <si>
+    <t>% zpožděných Woltdrivem</t>
+  </si>
+  <si>
+    <t>Wolt drive</t>
+  </si>
+  <si>
+    <t>Vyber datum    &lt;----------&gt;</t>
+  </si>
+  <si>
+    <t>Celkem hodin Instor</t>
+  </si>
+  <si>
+    <t>Celkem hodin Kurýr</t>
+  </si>
+  <si>
+    <t>Počet dní</t>
+  </si>
+  <si>
+    <t>Yarushynskyi Vladyslav</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>29:00</t>
+  </si>
+  <si>
+    <t>202:30</t>
+  </si>
+  <si>
+    <t>201:00</t>
+  </si>
+  <si>
     <t>Nováková Adéla</t>
   </si>
   <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>Benzín</t>
-  </si>
-  <si>
-    <t>Fáberová Kateřina</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Auta</t>
-  </si>
-  <si>
-    <t>Suroviny</t>
-  </si>
-  <si>
-    <t>Ostatní</t>
-  </si>
-  <si>
-    <t>PHM - soukromé</t>
-  </si>
-  <si>
-    <t>Zavíral</t>
-  </si>
-  <si>
-    <t>Zrušené obj. ks</t>
-  </si>
-  <si>
-    <t>Zrušené obj. $</t>
-  </si>
-  <si>
-    <t>Počet zpožděných našich rozvozů +5 min</t>
-  </si>
-  <si>
-    <t>Průměrný make Time</t>
-  </si>
-  <si>
-    <t>Počet rozvozů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vlastní vůz </t>
-  </si>
-  <si>
-    <t>Vyplatit PHM</t>
-  </si>
-  <si>
-    <t>počet výdajových dokadů</t>
-  </si>
-  <si>
-    <t>Počet nezrušených celkem</t>
-  </si>
-  <si>
-    <t>Počet našich rozvozů</t>
-  </si>
-  <si>
-    <t>Počet pozdě přiřazeným WoltDrive 5+</t>
-  </si>
-  <si>
-    <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
-  </si>
-  <si>
-    <t>% zpožděných našich rozvozů +5 min</t>
-  </si>
-  <si>
-    <t>Počet zpožděných Woltdrivem</t>
-  </si>
-  <si>
-    <t>% doručených včas</t>
-  </si>
-  <si>
-    <t>% zpožděných Woltdrivem</t>
-  </si>
-  <si>
-    <t>Wolt drive</t>
-  </si>
-  <si>
-    <t>Vyber datum    &lt;----------&gt;</t>
-  </si>
-  <si>
-    <t>Celkem hodin Instor</t>
-  </si>
-  <si>
-    <t>Celkem hodin Kurýr</t>
-  </si>
-  <si>
-    <t>Počet dní</t>
-  </si>
-  <si>
-    <t>Yarushynskyi Vladyslav</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>29:00</t>
-  </si>
-  <si>
-    <t>Vychivskyi Volodymyr</t>
-  </si>
-  <si>
-    <t>112:00</t>
-  </si>
-  <si>
-    <t>123:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>104:00</t>
-  </si>
-  <si>
     <t>13:00</t>
   </si>
   <si>
     <t>Putna Jaroslav</t>
   </si>
   <si>
-    <t>146:30</t>
-  </si>
-  <si>
-    <t>24:00</t>
+    <t>203:30</t>
+  </si>
+  <si>
+    <t>47:00</t>
   </si>
   <si>
     <t>7:00</t>
+  </si>
+  <si>
+    <t>Ahurieva Viktoriia</t>
+  </si>
+  <si>
+    <t>6:00</t>
   </si>
   <si>
     <t>12 min 31 s</t>
@@ -13268,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46194.0</v>
+        <v>46204.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13317,7 +13317,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -13476,9 +13476,7 @@
       <c r="F11" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="G11" s="45" t="s">
-        <v>607</v>
-      </c>
+      <c r="G11" s="45"/>
       <c r="I11" s="20"/>
       <c r="J11" s="46">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
@@ -13508,7 +13506,7 @@
       <c r="F12" s="53" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>#VALUE!</v>
+        <v>15:00</v>
       </c>
       <c r="I12" s="20"/>
       <c r="J12" s="35"/>
@@ -13521,7 +13519,7 @@
     <row r="13">
       <c r="A13" s="49">
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
-        <v>0</v>
+        <v>1501.236</v>
       </c>
       <c r="B13" s="50" t="s">
         <v>611</v>
@@ -13535,7 +13533,7 @@
       <c r="E13" s="52"/>
       <c r="F13" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>07:00</v>
+        <v>06:00</v>
       </c>
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
@@ -13550,28 +13548,22 @@
     <row r="14">
       <c r="A14" s="49">
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
-        <v>1501.236</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>615</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>616</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>613</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="55"/>
       <c r="F14" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>06:00</v>
+        <v>0:00</v>
       </c>
       <c r="G14" s="56"/>
       <c r="I14" s="20"/>
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="57" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M14" s="37"/>
     </row>
@@ -13592,7 +13584,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="57" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="M15" s="37"/>
     </row>
@@ -13613,7 +13605,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="57" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="M16" s="37"/>
     </row>
@@ -13636,7 +13628,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="59" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="M17" s="60">
         <f>sum(I25:I31)</f>
@@ -13657,7 +13649,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="18"/>
@@ -13677,9 +13669,7 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="45" t="s">
-        <v>611</v>
-      </c>
+      <c r="G19" s="45"/>
       <c r="I19" s="20"/>
       <c r="M19" s="62"/>
     </row>
@@ -13728,16 +13718,16 @@
       <c r="H22" s="27"/>
       <c r="I22" s="18"/>
       <c r="J22" s="70" t="s">
+        <v>620</v>
+      </c>
+      <c r="K22" s="70" t="s">
+        <v>621</v>
+      </c>
+      <c r="L22" s="71" t="s">
         <v>622</v>
       </c>
-      <c r="K22" s="70" t="s">
+      <c r="M22" s="71" t="s">
         <v>623</v>
-      </c>
-      <c r="L22" s="71" t="s">
-        <v>624</v>
-      </c>
-      <c r="M22" s="71" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="23">
@@ -13781,40 +13771,46 @@
         <v>606</v>
       </c>
       <c r="G24" s="75" t="s">
+        <v>624</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>625</v>
+      </c>
+      <c r="I24" s="76" t="s">
         <v>626</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="J24" s="77" t="s">
         <v>627</v>
       </c>
-      <c r="I24" s="76" t="s">
+      <c r="K24" s="78" t="s">
         <v>628</v>
       </c>
-      <c r="J24" s="77" t="s">
+      <c r="L24" s="77" t="s">
         <v>629</v>
       </c>
-      <c r="K24" s="78" t="s">
+      <c r="M24" s="78" t="s">
         <v>630</v>
-      </c>
-      <c r="L24" s="77" t="s">
-        <v>631</v>
-      </c>
-      <c r="M24" s="78" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="49">
         <f t="array" ref="A25">IF(ISBLANK(B25), 0, IF(ISNUMBER(MATCH(B25, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B25, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B25, HR!B:B, 0)) * (F25 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
+        <v>3627.987</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>631</v>
+      </c>
+      <c r="C25" s="79" t="s">
+        <v>632</v>
+      </c>
+      <c r="D25" s="79" t="s">
+        <v>609</v>
+      </c>
       <c r="E25" s="79"/>
       <c r="F25" s="80" t="str">
         <f t="shared" ref="F25:F31" si="2">IF(OR(ISBLANK(B25), ISBLANK(D25), D25=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))+1, TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))) - TIMEVALUE(IF(ISBLANK(C25), "00:00", C25)) - TIMEVALUE(IF(ISBLANK(E25), "00:00", E25))), "hh:mm"))
 </f>
-        <v>0:00</v>
+        <v>14:30</v>
       </c>
       <c r="G25" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B25)</f>
@@ -14127,13 +14123,13 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
-      <formula1>"Hanibal Filip,Mikuš Pavel,Šmídová Sabina,Kormash Liubov,Vychivskyi Volodymyr,Hřebík Martin,Reischl Jan,Kulinič Michail,Kačena Stanislav"</formula1>
+      <formula1>"Hanibal Filip,Kormash Liubov,Vychivskyi Volodymyr,Hřebík Martin,Reischl Jan"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
-      <formula1>"Nedbal Michal,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Makula Radek,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
+      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Coufal Jakub,Nováková Adéla,Yarushynskyi Vladyslav,Gorol Patrik,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G11 G19">
-      <formula1>"Šebesta Tomáš,Nováková Adéla,Fáberová Kateřina"</formula1>
+      <formula1>"Šebesta Tomáš,Fáberová Kateřina"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -14195,18 +14191,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="112">
-        <v>0.31312068182483815</v>
+        <v>0.3125156426126</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="113">
-        <v>693189.9400000001</v>
+        <v>1094445.3499999999</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="114" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="115">
-        <v>290469.6900000001</v>
+        <v>474655.6900000001</v>
       </c>
       <c r="N2" s="116"/>
     </row>
@@ -14228,7 +14224,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="120">
-        <v>108075.0</v>
+        <v>161058.0</v>
       </c>
       <c r="N3" s="116"/>
     </row>
@@ -14248,7 +14244,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="120">
-        <v>113157.65</v>
+        <v>177588.06</v>
       </c>
       <c r="N4" s="116"/>
     </row>
@@ -14272,7 +14268,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="120">
-        <v>86888.1</v>
+        <v>131132.1</v>
       </c>
       <c r="N5" s="116"/>
     </row>
@@ -14292,7 +14288,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="120">
-        <v>7858.6</v>
+        <v>13968.6</v>
       </c>
       <c r="N6" s="116"/>
     </row>
@@ -14300,14 +14296,14 @@
       <c r="A7" s="125"/>
       <c r="B7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>409.5</v>
+        <v>670.5</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="127">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>112</v>
+        <v>202.5</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14368,17 +14364,17 @@
         <v>606</v>
       </c>
       <c r="I9" s="140" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="J9" s="141">
-        <v>7.100000000085856</v>
+        <v>6.100000000176806</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="142" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="120">
-        <v>53801.0</v>
+        <v>81037.0</v>
       </c>
       <c r="N9" s="116"/>
     </row>
@@ -14397,16 +14393,16 @@
         <v>645</v>
       </c>
       <c r="F10" s="144" t="s">
+        <v>631</v>
+      </c>
+      <c r="G10" s="145">
+        <v>17.0</v>
+      </c>
+      <c r="H10" s="145" t="s">
         <v>646</v>
       </c>
-      <c r="G10" s="145">
-        <v>10.0</v>
-      </c>
-      <c r="H10" s="145" t="s">
-        <v>647</v>
-      </c>
       <c r="I10" s="147">
-        <v>49.0</v>
+        <v>95.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14414,7 +14410,7 @@
         <v>601</v>
       </c>
       <c r="M10" s="120">
-        <v>1245.0</v>
+        <v>1545.0</v>
       </c>
       <c r="N10" s="116"/>
     </row>
@@ -14424,13 +14420,13 @@
         <v>607</v>
       </c>
       <c r="C11" s="145">
-        <v>14.0</v>
+        <v>24.0</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E11" s="146" t="s">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="F11" s="144"/>
       <c r="G11" s="145"/>
@@ -14442,23 +14438,23 @@
         <v>596</v>
       </c>
       <c r="M11" s="149">
-        <v>24603.0</v>
+        <v>43573.0</v>
       </c>
       <c r="N11" s="116"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="143"/>
       <c r="B12" s="144" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="C12" s="145">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="D12" s="145" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E12" s="146" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F12" s="144"/>
       <c r="G12" s="145"/>
@@ -14475,16 +14471,16 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="143"/>
       <c r="B13" s="144" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C13" s="145">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="D13" s="145" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E13" s="146" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F13" s="144"/>
       <c r="G13" s="145"/>
@@ -14503,16 +14499,16 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="143"/>
       <c r="B14" s="144" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C14" s="145">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="D14" s="145" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E14" s="146" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F14" s="144"/>
       <c r="G14" s="145"/>
@@ -14521,7 +14517,7 @@
       <c r="J14" s="35"/>
       <c r="K14" s="20"/>
       <c r="L14" s="151" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M14" s="120">
         <v>0.0</v>
@@ -14530,11 +14526,17 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="143"/>
-      <c r="B15" s="144"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
+      <c r="B15" s="144" t="s">
+        <v>654</v>
+      </c>
+      <c r="C15" s="145">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="145" t="s">
+        <v>655</v>
+      </c>
       <c r="E15" s="146" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F15" s="144"/>
       <c r="G15" s="145"/>
@@ -14543,7 +14545,7 @@
       <c r="J15" s="35"/>
       <c r="K15" s="20"/>
       <c r="L15" s="151" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="M15" s="120">
         <v>140.0</v>
@@ -14563,10 +14565,10 @@
       <c r="J16" s="35"/>
       <c r="K16" s="20"/>
       <c r="L16" s="151" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="M16" s="120">
-        <v>2354.0</v>
+        <v>3079.0</v>
       </c>
       <c r="N16" s="116"/>
     </row>
@@ -14583,10 +14585,10 @@
       <c r="J17" s="17"/>
       <c r="K17" s="18"/>
       <c r="L17" s="153" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="M17" s="154">
-        <v>2205.0</v>
+        <v>4275.0</v>
       </c>
       <c r="N17" s="116"/>
     </row>
@@ -14617,16 +14619,16 @@
       <c r="H19" s="145"/>
       <c r="I19" s="147"/>
       <c r="J19" s="157" t="s">
+        <v>620</v>
+      </c>
+      <c r="K19" s="158" t="s">
+        <v>621</v>
+      </c>
+      <c r="L19" s="159" t="s">
         <v>622</v>
       </c>
-      <c r="K19" s="158" t="s">
+      <c r="M19" s="160" t="s">
         <v>623</v>
-      </c>
-      <c r="L19" s="159" t="s">
-        <v>624</v>
-      </c>
-      <c r="M19" s="160" t="s">
-        <v>625</v>
       </c>
       <c r="N19" s="161"/>
     </row>
@@ -14657,13 +14659,13 @@
       <c r="H21" s="145"/>
       <c r="I21" s="147"/>
       <c r="J21" s="164">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="K21" s="165">
-        <v>8044.400000000001</v>
+        <v>8788.900000000001</v>
       </c>
       <c r="L21" s="166">
-        <v>29.0</v>
+        <v>39.0</v>
       </c>
       <c r="M21" s="167" t="s">
         <v>656</v>
@@ -14681,16 +14683,16 @@
       <c r="H22" s="145"/>
       <c r="I22" s="147"/>
       <c r="J22" s="168" t="s">
+        <v>627</v>
+      </c>
+      <c r="K22" s="169" t="s">
+        <v>628</v>
+      </c>
+      <c r="L22" s="170" t="s">
         <v>629</v>
       </c>
-      <c r="K22" s="169" t="s">
+      <c r="M22" s="171" t="s">
         <v>630</v>
-      </c>
-      <c r="L22" s="170" t="s">
-        <v>631</v>
-      </c>
-      <c r="M22" s="171" t="s">
-        <v>632</v>
       </c>
       <c r="N22" s="156"/>
     </row>
@@ -14721,16 +14723,16 @@
       <c r="H24" s="145"/>
       <c r="I24" s="147"/>
       <c r="J24" s="172">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
       <c r="K24" s="166">
-        <v>1783.0</v>
+        <v>2823.0</v>
       </c>
       <c r="L24" s="166">
-        <v>175.0</v>
+        <v>265.0</v>
       </c>
       <c r="M24" s="173">
-        <v>34.0</v>
+        <v>42.0</v>
       </c>
       <c r="N24" s="156"/>
     </row>
@@ -14783,14 +14785,14 @@
       <c r="H27" s="145"/>
       <c r="I27" s="147"/>
       <c r="J27" s="178">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="K27" s="94"/>
       <c r="L27" s="179">
-        <v>0.14638171426097124</v>
+        <v>0.13493064125417067</v>
       </c>
       <c r="M27" s="180">
-        <v>24.0</v>
+        <v>33.0</v>
       </c>
       <c r="N27" s="156"/>
     </row>
@@ -14841,10 +14843,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="183">
-        <v>0.8536182857390289</v>
+        <v>0.8650693587458294</v>
       </c>
       <c r="M30" s="184">
-        <v>0.12281790277146315</v>
+        <v>0.11445133842192666</v>
       </c>
       <c r="N30" s="156"/>
     </row>
@@ -14956,7 +14958,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="186"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="185"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -15024,7 +15026,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="186"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="185"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -15228,7 +15230,7 @@
       <c r="B10" s="4"/>
       <c r="C10" s="186"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="185"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -15330,7 +15332,7 @@
       <c r="B13" s="4"/>
       <c r="C13" s="186"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="185"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -15506,7 +15508,7 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="K18" s="185"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -15534,7 +15536,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="186"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="185"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -15568,7 +15570,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="186"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="E20" s="185"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -15670,7 +15672,7 @@
       <c r="B23" s="186"/>
       <c r="C23" s="186"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="185"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -15738,7 +15740,7 @@
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="185"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -15797,6 +15799,7 @@
       <c r="AA26" s="185"/>
       <c r="AB26" s="185"/>
       <c r="AC26" s="185"/>
+      <c r="AD26" s="185"/>
       <c r="AE26" s="185"/>
       <c r="AF26" s="185"/>
     </row>
@@ -15805,7 +15808,7 @@
       <c r="B27" s="186"/>
       <c r="C27" s="186"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="185"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -15839,7 +15842,7 @@
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="185"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -15879,7 +15882,7 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
+      <c r="K29" s="185"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
@@ -15907,7 +15910,7 @@
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="185"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -16009,7 +16012,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="186"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="185"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -16049,7 +16052,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
+      <c r="K34" s="185"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
@@ -16145,7 +16148,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="186"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="185"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -16179,7 +16182,7 @@
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="185"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -16213,7 +16216,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="186"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="185"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -16247,13 +16250,13 @@
       <c r="B40" s="4"/>
       <c r="C40" s="186"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="185"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
+      <c r="K40" s="185"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -16383,7 +16386,7 @@
       <c r="B44" s="4"/>
       <c r="C44" s="186"/>
       <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="185"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -16417,7 +16420,7 @@
       <c r="B45" s="4"/>
       <c r="C45" s="186"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="185"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -16485,13 +16488,13 @@
       <c r="B47" s="4"/>
       <c r="C47" s="186"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
+      <c r="E47" s="185"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
+      <c r="K47" s="185"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -16593,7 +16596,7 @@
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
-      <c r="K50" s="185"/>
+      <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
@@ -16655,7 +16658,7 @@
       <c r="B52" s="186"/>
       <c r="C52" s="186"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="185"/>
+      <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -16763,7 +16766,7 @@
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
+      <c r="K55" s="185"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
@@ -16791,7 +16794,7 @@
       <c r="B56" s="4"/>
       <c r="C56" s="186"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="185"/>
+      <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -16825,7 +16828,7 @@
       <c r="B57" s="4"/>
       <c r="C57" s="186"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="185"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -16865,7 +16868,7 @@
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
+      <c r="K58" s="185"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
@@ -16927,7 +16930,7 @@
       <c r="B60" s="4"/>
       <c r="C60" s="186"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="185"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -16995,7 +16998,7 @@
       <c r="B62" s="4"/>
       <c r="C62" s="186"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="185"/>
+      <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -17029,7 +17032,7 @@
       <c r="B63" s="4"/>
       <c r="C63" s="186"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="185"/>
+      <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -17063,7 +17066,7 @@
       <c r="B64" s="4"/>
       <c r="C64" s="186"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="185"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -17097,7 +17100,7 @@
       <c r="B65" s="4"/>
       <c r="C65" s="186"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="185"/>
+      <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -17194,22 +17197,22 @@
       <c r="AF67" s="185"/>
     </row>
     <row r="68">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
+      <c r="A68" s="185"/>
+      <c r="B68" s="185"/>
+      <c r="C68" s="187"/>
+      <c r="D68" s="185"/>
       <c r="E68" s="185"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
+      <c r="F68" s="185"/>
+      <c r="G68" s="185"/>
+      <c r="H68" s="185"/>
+      <c r="I68" s="185"/>
+      <c r="J68" s="185"/>
       <c r="K68" s="185"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
+      <c r="L68" s="185"/>
+      <c r="M68" s="185"/>
+      <c r="N68" s="185"/>
+      <c r="O68" s="185"/>
+      <c r="P68" s="185"/>
       <c r="Q68" s="185"/>
       <c r="R68" s="185"/>
       <c r="S68" s="185"/>
@@ -17228,22 +17231,22 @@
       <c r="AF68" s="185"/>
     </row>
     <row r="69">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
+      <c r="A69" s="185"/>
+      <c r="B69" s="185"/>
+      <c r="C69" s="185"/>
+      <c r="D69" s="185"/>
+      <c r="E69" s="185"/>
+      <c r="F69" s="185"/>
+      <c r="G69" s="185"/>
+      <c r="H69" s="185"/>
+      <c r="I69" s="185"/>
+      <c r="J69" s="185"/>
       <c r="K69" s="185"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
+      <c r="L69" s="185"/>
+      <c r="M69" s="185"/>
+      <c r="N69" s="185"/>
+      <c r="O69" s="185"/>
+      <c r="P69" s="185"/>
       <c r="Q69" s="185"/>
       <c r="R69" s="185"/>
       <c r="S69" s="185"/>
@@ -17262,22 +17265,22 @@
       <c r="AF69" s="185"/>
     </row>
     <row r="70">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="186"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
+      <c r="A70" s="185"/>
+      <c r="B70" s="185"/>
+      <c r="C70" s="187"/>
+      <c r="D70" s="185"/>
+      <c r="E70" s="185"/>
+      <c r="F70" s="185"/>
+      <c r="G70" s="185"/>
+      <c r="H70" s="185"/>
+      <c r="I70" s="185"/>
+      <c r="J70" s="185"/>
+      <c r="K70" s="185"/>
+      <c r="L70" s="185"/>
+      <c r="M70" s="185"/>
+      <c r="N70" s="185"/>
+      <c r="O70" s="185"/>
+      <c r="P70" s="185"/>
       <c r="Q70" s="185"/>
       <c r="R70" s="185"/>
       <c r="S70" s="185"/>
@@ -17296,22 +17299,22 @@
       <c r="AF70" s="185"/>
     </row>
     <row r="71">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="186"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
+      <c r="A71" s="185"/>
+      <c r="B71" s="185"/>
+      <c r="C71" s="187"/>
+      <c r="D71" s="185"/>
+      <c r="E71" s="185"/>
+      <c r="F71" s="185"/>
+      <c r="G71" s="185"/>
+      <c r="H71" s="185"/>
+      <c r="I71" s="185"/>
+      <c r="J71" s="185"/>
       <c r="K71" s="185"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
+      <c r="L71" s="185"/>
+      <c r="M71" s="185"/>
+      <c r="N71" s="185"/>
+      <c r="O71" s="185"/>
+      <c r="P71" s="185"/>
       <c r="Q71" s="185"/>
       <c r="R71" s="185"/>
       <c r="S71" s="185"/>
@@ -17330,22 +17333,22 @@
       <c r="AF71" s="185"/>
     </row>
     <row r="72">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
+      <c r="A72" s="185"/>
+      <c r="B72" s="185"/>
+      <c r="C72" s="185"/>
+      <c r="D72" s="185"/>
+      <c r="E72" s="185"/>
+      <c r="F72" s="185"/>
+      <c r="G72" s="185"/>
+      <c r="H72" s="185"/>
+      <c r="I72" s="185"/>
+      <c r="J72" s="185"/>
+      <c r="K72" s="185"/>
+      <c r="L72" s="185"/>
+      <c r="M72" s="185"/>
+      <c r="N72" s="185"/>
+      <c r="O72" s="185"/>
+      <c r="P72" s="185"/>
       <c r="Q72" s="185"/>
       <c r="R72" s="185"/>
       <c r="S72" s="185"/>
@@ -17364,22 +17367,22 @@
       <c r="AF72" s="185"/>
     </row>
     <row r="73">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="186"/>
-      <c r="D73" s="4"/>
+      <c r="A73" s="185"/>
+      <c r="B73" s="185"/>
+      <c r="C73" s="187"/>
+      <c r="D73" s="185"/>
       <c r="E73" s="185"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
+      <c r="F73" s="185"/>
+      <c r="G73" s="185"/>
+      <c r="H73" s="185"/>
+      <c r="I73" s="185"/>
+      <c r="J73" s="185"/>
       <c r="K73" s="185"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
+      <c r="L73" s="185"/>
+      <c r="M73" s="185"/>
+      <c r="N73" s="185"/>
+      <c r="O73" s="185"/>
+      <c r="P73" s="185"/>
       <c r="Q73" s="185"/>
       <c r="R73" s="185"/>
       <c r="S73" s="185"/>
@@ -17398,22 +17401,22 @@
       <c r="AF73" s="185"/>
     </row>
     <row r="74">
-      <c r="A74" s="4"/>
-      <c r="B74" s="186"/>
-      <c r="C74" s="186"/>
-      <c r="D74" s="4"/>
+      <c r="A74" s="185"/>
+      <c r="B74" s="187"/>
+      <c r="C74" s="187"/>
+      <c r="D74" s="185"/>
       <c r="E74" s="185"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
+      <c r="F74" s="185"/>
+      <c r="G74" s="185"/>
+      <c r="H74" s="185"/>
+      <c r="I74" s="185"/>
+      <c r="J74" s="185"/>
       <c r="K74" s="185"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
+      <c r="L74" s="185"/>
+      <c r="M74" s="185"/>
+      <c r="N74" s="185"/>
+      <c r="O74" s="185"/>
+      <c r="P74" s="185"/>
       <c r="Q74" s="185"/>
       <c r="R74" s="185"/>
       <c r="S74" s="185"/>
@@ -17432,22 +17435,22 @@
       <c r="AF74" s="185"/>
     </row>
     <row r="75">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
+      <c r="A75" s="185"/>
+      <c r="B75" s="185"/>
+      <c r="C75" s="185"/>
+      <c r="D75" s="185"/>
+      <c r="E75" s="185"/>
+      <c r="F75" s="185"/>
+      <c r="G75" s="185"/>
+      <c r="H75" s="185"/>
+      <c r="I75" s="185"/>
+      <c r="J75" s="185"/>
       <c r="K75" s="185"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
+      <c r="L75" s="185"/>
+      <c r="M75" s="185"/>
+      <c r="N75" s="185"/>
+      <c r="O75" s="185"/>
+      <c r="P75" s="185"/>
       <c r="Q75" s="185"/>
       <c r="R75" s="185"/>
       <c r="S75" s="185"/>
@@ -17466,22 +17469,22 @@
       <c r="AF75" s="185"/>
     </row>
     <row r="76">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
+      <c r="A76" s="185"/>
+      <c r="B76" s="185"/>
+      <c r="C76" s="185"/>
+      <c r="D76" s="185"/>
+      <c r="E76" s="185"/>
+      <c r="F76" s="185"/>
+      <c r="G76" s="185"/>
+      <c r="H76" s="185"/>
+      <c r="I76" s="185"/>
+      <c r="J76" s="185"/>
       <c r="K76" s="185"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
+      <c r="L76" s="185"/>
+      <c r="M76" s="185"/>
+      <c r="N76" s="185"/>
+      <c r="O76" s="185"/>
+      <c r="P76" s="185"/>
       <c r="Q76" s="185"/>
       <c r="R76" s="185"/>
       <c r="S76" s="185"/>
@@ -17500,22 +17503,22 @@
       <c r="AF76" s="185"/>
     </row>
     <row r="77">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
+      <c r="A77" s="185"/>
+      <c r="B77" s="185"/>
+      <c r="C77" s="185"/>
+      <c r="D77" s="185"/>
+      <c r="E77" s="185"/>
+      <c r="F77" s="185"/>
+      <c r="G77" s="185"/>
+      <c r="H77" s="185"/>
+      <c r="I77" s="185"/>
+      <c r="J77" s="185"/>
       <c r="K77" s="185"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
+      <c r="L77" s="185"/>
+      <c r="M77" s="185"/>
+      <c r="N77" s="185"/>
+      <c r="O77" s="185"/>
+      <c r="P77" s="185"/>
       <c r="Q77" s="185"/>
       <c r="R77" s="185"/>
       <c r="S77" s="185"/>
@@ -17534,22 +17537,22 @@
       <c r="AF77" s="185"/>
     </row>
     <row r="78">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="186"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
+      <c r="A78" s="185"/>
+      <c r="B78" s="185"/>
+      <c r="C78" s="187"/>
+      <c r="D78" s="185"/>
+      <c r="E78" s="185"/>
+      <c r="F78" s="185"/>
+      <c r="G78" s="185"/>
+      <c r="H78" s="185"/>
+      <c r="I78" s="185"/>
+      <c r="J78" s="185"/>
       <c r="K78" s="185"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
+      <c r="L78" s="185"/>
+      <c r="M78" s="185"/>
+      <c r="N78" s="185"/>
+      <c r="O78" s="185"/>
+      <c r="P78" s="185"/>
       <c r="Q78" s="185"/>
       <c r="R78" s="185"/>
       <c r="S78" s="185"/>
@@ -17568,22 +17571,22 @@
       <c r="AF78" s="185"/>
     </row>
     <row r="79">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="186"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
+      <c r="A79" s="185"/>
+      <c r="B79" s="185"/>
+      <c r="C79" s="187"/>
+      <c r="D79" s="185"/>
+      <c r="E79" s="185"/>
+      <c r="F79" s="185"/>
+      <c r="G79" s="185"/>
+      <c r="H79" s="185"/>
+      <c r="I79" s="185"/>
+      <c r="J79" s="185"/>
       <c r="K79" s="185"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
+      <c r="L79" s="185"/>
+      <c r="M79" s="185"/>
+      <c r="N79" s="185"/>
+      <c r="O79" s="185"/>
+      <c r="P79" s="185"/>
       <c r="Q79" s="185"/>
       <c r="R79" s="185"/>
       <c r="S79" s="185"/>
@@ -17602,22 +17605,22 @@
       <c r="AF79" s="185"/>
     </row>
     <row r="80">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="186"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
+      <c r="A80" s="185"/>
+      <c r="B80" s="185"/>
+      <c r="C80" s="187"/>
+      <c r="D80" s="185"/>
+      <c r="E80" s="185"/>
+      <c r="F80" s="185"/>
+      <c r="G80" s="185"/>
+      <c r="H80" s="185"/>
+      <c r="I80" s="185"/>
+      <c r="J80" s="185"/>
+      <c r="K80" s="185"/>
+      <c r="L80" s="185"/>
+      <c r="M80" s="185"/>
+      <c r="N80" s="185"/>
+      <c r="O80" s="185"/>
+      <c r="P80" s="185"/>
       <c r="Q80" s="185"/>
       <c r="R80" s="185"/>
       <c r="S80" s="185"/>
@@ -17636,22 +17639,22 @@
       <c r="AF80" s="185"/>
     </row>
     <row r="81">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="186"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
+      <c r="A81" s="185"/>
+      <c r="B81" s="185"/>
+      <c r="C81" s="187"/>
+      <c r="D81" s="185"/>
+      <c r="E81" s="185"/>
+      <c r="F81" s="185"/>
+      <c r="G81" s="185"/>
+      <c r="H81" s="185"/>
+      <c r="I81" s="185"/>
+      <c r="J81" s="185"/>
       <c r="K81" s="185"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
+      <c r="L81" s="185"/>
+      <c r="M81" s="185"/>
+      <c r="N81" s="185"/>
+      <c r="O81" s="185"/>
+      <c r="P81" s="185"/>
       <c r="Q81" s="185"/>
       <c r="R81" s="185"/>
       <c r="S81" s="185"/>
@@ -17670,22 +17673,22 @@
       <c r="AF81" s="185"/>
     </row>
     <row r="82">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
+      <c r="A82" s="185"/>
+      <c r="B82" s="185"/>
+      <c r="C82" s="185"/>
+      <c r="D82" s="185"/>
+      <c r="E82" s="185"/>
+      <c r="F82" s="185"/>
+      <c r="G82" s="185"/>
+      <c r="H82" s="185"/>
+      <c r="I82" s="185"/>
+      <c r="J82" s="185"/>
       <c r="K82" s="185"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
+      <c r="L82" s="185"/>
+      <c r="M82" s="185"/>
+      <c r="N82" s="185"/>
+      <c r="O82" s="185"/>
+      <c r="P82" s="185"/>
       <c r="Q82" s="185"/>
       <c r="R82" s="185"/>
       <c r="S82" s="185"/>
@@ -17704,22 +17707,22 @@
       <c r="AF82" s="185"/>
     </row>
     <row r="83">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
+      <c r="A83" s="185"/>
+      <c r="B83" s="185"/>
+      <c r="C83" s="185"/>
+      <c r="D83" s="185"/>
+      <c r="E83" s="185"/>
+      <c r="F83" s="185"/>
+      <c r="G83" s="185"/>
+      <c r="H83" s="185"/>
+      <c r="I83" s="185"/>
+      <c r="J83" s="185"/>
       <c r="K83" s="185"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
+      <c r="L83" s="185"/>
+      <c r="M83" s="185"/>
+      <c r="N83" s="185"/>
+      <c r="O83" s="185"/>
+      <c r="P83" s="185"/>
       <c r="Q83" s="185"/>
       <c r="R83" s="185"/>
       <c r="S83" s="185"/>
@@ -17738,22 +17741,22 @@
       <c r="AF83" s="185"/>
     </row>
     <row r="84">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="186"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
+      <c r="A84" s="185"/>
+      <c r="B84" s="185"/>
+      <c r="C84" s="187"/>
+      <c r="D84" s="185"/>
+      <c r="E84" s="185"/>
+      <c r="F84" s="185"/>
+      <c r="G84" s="185"/>
+      <c r="H84" s="185"/>
+      <c r="I84" s="185"/>
+      <c r="J84" s="185"/>
       <c r="K84" s="185"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
+      <c r="L84" s="185"/>
+      <c r="M84" s="185"/>
+      <c r="N84" s="185"/>
+      <c r="O84" s="185"/>
+      <c r="P84" s="185"/>
       <c r="Q84" s="185"/>
       <c r="R84" s="185"/>
       <c r="S84" s="185"/>
@@ -17772,22 +17775,22 @@
       <c r="AF84" s="185"/>
     </row>
     <row r="85">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="186"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
+      <c r="A85" s="185"/>
+      <c r="B85" s="185"/>
+      <c r="C85" s="187"/>
+      <c r="D85" s="185"/>
+      <c r="E85" s="185"/>
+      <c r="F85" s="185"/>
+      <c r="G85" s="185"/>
+      <c r="H85" s="185"/>
+      <c r="I85" s="185"/>
+      <c r="J85" s="185"/>
       <c r="K85" s="185"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
+      <c r="L85" s="185"/>
+      <c r="M85" s="185"/>
+      <c r="N85" s="185"/>
+      <c r="O85" s="185"/>
+      <c r="P85" s="185"/>
       <c r="Q85" s="185"/>
       <c r="R85" s="185"/>
       <c r="S85" s="185"/>
@@ -17806,22 +17809,22 @@
       <c r="AF85" s="185"/>
     </row>
     <row r="86">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="186"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
+      <c r="A86" s="185"/>
+      <c r="B86" s="185"/>
+      <c r="C86" s="187"/>
+      <c r="D86" s="185"/>
+      <c r="E86" s="185"/>
+      <c r="F86" s="185"/>
+      <c r="G86" s="185"/>
+      <c r="H86" s="185"/>
+      <c r="I86" s="185"/>
+      <c r="J86" s="185"/>
       <c r="K86" s="185"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
+      <c r="L86" s="185"/>
+      <c r="M86" s="185"/>
+      <c r="N86" s="185"/>
+      <c r="O86" s="185"/>
+      <c r="P86" s="185"/>
       <c r="Q86" s="185"/>
       <c r="R86" s="185"/>
       <c r="S86" s="185"/>
@@ -17840,22 +17843,22 @@
       <c r="AF86" s="185"/>
     </row>
     <row r="87">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="186"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
+      <c r="A87" s="185"/>
+      <c r="B87" s="185"/>
+      <c r="C87" s="187"/>
+      <c r="D87" s="185"/>
+      <c r="E87" s="185"/>
+      <c r="F87" s="185"/>
+      <c r="G87" s="185"/>
+      <c r="H87" s="185"/>
+      <c r="I87" s="185"/>
+      <c r="J87" s="185"/>
       <c r="K87" s="185"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
+      <c r="L87" s="185"/>
+      <c r="M87" s="185"/>
+      <c r="N87" s="185"/>
+      <c r="O87" s="185"/>
+      <c r="P87" s="185"/>
       <c r="Q87" s="185"/>
       <c r="R87" s="185"/>
       <c r="S87" s="185"/>
@@ -17874,22 +17877,22 @@
       <c r="AF87" s="185"/>
     </row>
     <row r="88">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="186"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
+      <c r="A88" s="185"/>
+      <c r="B88" s="185"/>
+      <c r="C88" s="187"/>
+      <c r="D88" s="185"/>
+      <c r="E88" s="185"/>
+      <c r="F88" s="185"/>
+      <c r="G88" s="185"/>
+      <c r="H88" s="185"/>
+      <c r="I88" s="185"/>
+      <c r="J88" s="185"/>
       <c r="K88" s="185"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
+      <c r="L88" s="185"/>
+      <c r="M88" s="185"/>
+      <c r="N88" s="185"/>
+      <c r="O88" s="185"/>
+      <c r="P88" s="185"/>
       <c r="Q88" s="185"/>
       <c r="R88" s="185"/>
       <c r="S88" s="185"/>
@@ -17908,22 +17911,22 @@
       <c r="AF88" s="185"/>
     </row>
     <row r="89">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="186"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
+      <c r="A89" s="185"/>
+      <c r="B89" s="185"/>
+      <c r="C89" s="187"/>
+      <c r="D89" s="185"/>
+      <c r="E89" s="185"/>
+      <c r="F89" s="185"/>
+      <c r="G89" s="185"/>
+      <c r="H89" s="185"/>
+      <c r="I89" s="185"/>
+      <c r="J89" s="185"/>
       <c r="K89" s="185"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
+      <c r="L89" s="185"/>
+      <c r="M89" s="185"/>
+      <c r="N89" s="185"/>
+      <c r="O89" s="185"/>
+      <c r="P89" s="185"/>
       <c r="Q89" s="185"/>
       <c r="R89" s="185"/>
       <c r="S89" s="185"/>
@@ -17942,22 +17945,22 @@
       <c r="AF89" s="185"/>
     </row>
     <row r="90">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="186"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
+      <c r="A90" s="185"/>
+      <c r="B90" s="185"/>
+      <c r="C90" s="187"/>
+      <c r="D90" s="185"/>
+      <c r="E90" s="185"/>
+      <c r="F90" s="185"/>
+      <c r="G90" s="185"/>
+      <c r="H90" s="185"/>
+      <c r="I90" s="185"/>
+      <c r="J90" s="185"/>
       <c r="K90" s="185"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
+      <c r="L90" s="185"/>
+      <c r="M90" s="185"/>
+      <c r="N90" s="185"/>
+      <c r="O90" s="185"/>
+      <c r="P90" s="185"/>
       <c r="Q90" s="185"/>
       <c r="R90" s="185"/>
       <c r="S90" s="185"/>
@@ -17971,26 +17974,27 @@
       <c r="AA90" s="185"/>
       <c r="AB90" s="185"/>
       <c r="AC90" s="185"/>
+      <c r="AD90" s="185"/>
       <c r="AE90" s="185"/>
       <c r="AF90" s="185"/>
     </row>
     <row r="91">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
+      <c r="A91" s="185"/>
+      <c r="B91" s="185"/>
+      <c r="C91" s="185"/>
+      <c r="D91" s="185"/>
       <c r="E91" s="185"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
+      <c r="F91" s="185"/>
+      <c r="G91" s="185"/>
+      <c r="H91" s="185"/>
+      <c r="I91" s="185"/>
+      <c r="J91" s="185"/>
       <c r="K91" s="185"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
+      <c r="L91" s="185"/>
+      <c r="M91" s="185"/>
+      <c r="N91" s="185"/>
+      <c r="O91" s="185"/>
+      <c r="P91" s="185"/>
       <c r="Q91" s="185"/>
       <c r="R91" s="185"/>
       <c r="S91" s="185"/>
@@ -18008,22 +18012,22 @@
       <c r="AF91" s="185"/>
     </row>
     <row r="92">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
+      <c r="A92" s="185"/>
+      <c r="B92" s="185"/>
+      <c r="C92" s="185"/>
+      <c r="D92" s="185"/>
+      <c r="E92" s="185"/>
+      <c r="F92" s="185"/>
+      <c r="G92" s="185"/>
+      <c r="H92" s="185"/>
+      <c r="I92" s="185"/>
+      <c r="J92" s="185"/>
       <c r="K92" s="185"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
+      <c r="L92" s="185"/>
+      <c r="M92" s="185"/>
+      <c r="N92" s="185"/>
+      <c r="O92" s="185"/>
+      <c r="P92" s="185"/>
       <c r="Q92" s="185"/>
       <c r="R92" s="185"/>
       <c r="S92" s="185"/>
@@ -18041,22 +18045,22 @@
       <c r="AF92" s="185"/>
     </row>
     <row r="93">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
+      <c r="A93" s="185"/>
+      <c r="B93" s="185"/>
+      <c r="C93" s="185"/>
+      <c r="D93" s="185"/>
       <c r="E93" s="185"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
+      <c r="F93" s="185"/>
+      <c r="G93" s="185"/>
+      <c r="H93" s="185"/>
+      <c r="I93" s="185"/>
+      <c r="J93" s="185"/>
       <c r="K93" s="185"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
+      <c r="L93" s="185"/>
+      <c r="M93" s="185"/>
+      <c r="N93" s="185"/>
+      <c r="O93" s="185"/>
+      <c r="P93" s="185"/>
       <c r="Q93" s="185"/>
       <c r="R93" s="185"/>
       <c r="S93" s="185"/>
@@ -18075,22 +18079,22 @@
       <c r="AF93" s="185"/>
     </row>
     <row r="94">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
+      <c r="A94" s="185"/>
+      <c r="B94" s="185"/>
+      <c r="C94" s="185"/>
+      <c r="D94" s="185"/>
+      <c r="E94" s="185"/>
+      <c r="F94" s="185"/>
+      <c r="G94" s="185"/>
+      <c r="H94" s="185"/>
+      <c r="I94" s="185"/>
+      <c r="J94" s="185"/>
       <c r="K94" s="185"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
+      <c r="L94" s="185"/>
+      <c r="M94" s="185"/>
+      <c r="N94" s="185"/>
+      <c r="O94" s="185"/>
+      <c r="P94" s="185"/>
       <c r="Q94" s="185"/>
       <c r="R94" s="185"/>
       <c r="S94" s="185"/>
@@ -18108,22 +18112,22 @@
       <c r="AF94" s="185"/>
     </row>
     <row r="95">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
+      <c r="A95" s="185"/>
+      <c r="B95" s="185"/>
+      <c r="C95" s="185"/>
+      <c r="D95" s="185"/>
+      <c r="E95" s="185"/>
+      <c r="F95" s="185"/>
+      <c r="G95" s="185"/>
+      <c r="H95" s="185"/>
+      <c r="I95" s="185"/>
+      <c r="J95" s="185"/>
       <c r="K95" s="185"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
+      <c r="L95" s="185"/>
+      <c r="M95" s="185"/>
+      <c r="N95" s="185"/>
+      <c r="O95" s="185"/>
+      <c r="P95" s="185"/>
       <c r="Q95" s="185"/>
       <c r="R95" s="185"/>
       <c r="S95" s="185"/>
@@ -18141,22 +18145,22 @@
       <c r="AF95" s="185"/>
     </row>
     <row r="96">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
+      <c r="A96" s="185"/>
+      <c r="B96" s="185"/>
+      <c r="C96" s="185"/>
+      <c r="D96" s="185"/>
       <c r="E96" s="185"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
+      <c r="F96" s="185"/>
+      <c r="G96" s="185"/>
+      <c r="H96" s="185"/>
+      <c r="I96" s="185"/>
+      <c r="J96" s="185"/>
       <c r="K96" s="185"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
+      <c r="L96" s="185"/>
+      <c r="M96" s="185"/>
+      <c r="N96" s="185"/>
+      <c r="O96" s="185"/>
+      <c r="P96" s="185"/>
       <c r="Q96" s="185"/>
       <c r="R96" s="185"/>
       <c r="S96" s="185"/>
@@ -18174,22 +18178,22 @@
       <c r="AF96" s="185"/>
     </row>
     <row r="97">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
+      <c r="A97" s="185"/>
+      <c r="B97" s="185"/>
+      <c r="C97" s="185"/>
+      <c r="D97" s="185"/>
+      <c r="E97" s="185"/>
+      <c r="F97" s="185"/>
+      <c r="G97" s="185"/>
+      <c r="H97" s="185"/>
+      <c r="I97" s="185"/>
+      <c r="J97" s="185"/>
       <c r="K97" s="185"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
+      <c r="L97" s="185"/>
+      <c r="M97" s="185"/>
+      <c r="N97" s="185"/>
+      <c r="O97" s="185"/>
+      <c r="P97" s="185"/>
       <c r="Q97" s="185"/>
       <c r="R97" s="185"/>
       <c r="S97" s="185"/>
@@ -18208,22 +18212,22 @@
       <c r="AF97" s="185"/>
     </row>
     <row r="98">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
+      <c r="A98" s="185"/>
+      <c r="B98" s="185"/>
+      <c r="C98" s="185"/>
+      <c r="D98" s="185"/>
+      <c r="E98" s="185"/>
+      <c r="F98" s="185"/>
+      <c r="G98" s="185"/>
+      <c r="H98" s="185"/>
+      <c r="I98" s="185"/>
+      <c r="J98" s="185"/>
       <c r="K98" s="185"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
+      <c r="L98" s="185"/>
+      <c r="M98" s="185"/>
+      <c r="N98" s="185"/>
+      <c r="O98" s="185"/>
+      <c r="P98" s="185"/>
       <c r="Q98" s="185"/>
       <c r="R98" s="185"/>
       <c r="S98" s="185"/>
@@ -18241,22 +18245,22 @@
       <c r="AF98" s="185"/>
     </row>
     <row r="99">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="186"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
+      <c r="A99" s="185"/>
+      <c r="B99" s="185"/>
+      <c r="C99" s="187"/>
+      <c r="D99" s="185"/>
+      <c r="E99" s="185"/>
+      <c r="F99" s="185"/>
+      <c r="G99" s="185"/>
+      <c r="H99" s="185"/>
+      <c r="I99" s="185"/>
+      <c r="J99" s="185"/>
       <c r="K99" s="185"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
+      <c r="L99" s="185"/>
+      <c r="M99" s="185"/>
+      <c r="N99" s="185"/>
+      <c r="O99" s="185"/>
+      <c r="P99" s="185"/>
       <c r="Q99" s="185"/>
       <c r="R99" s="185"/>
       <c r="S99" s="185"/>
@@ -18275,22 +18279,22 @@
       <c r="AF99" s="185"/>
     </row>
     <row r="100">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="186"/>
-      <c r="D100" s="4"/>
+      <c r="A100" s="185"/>
+      <c r="B100" s="185"/>
+      <c r="C100" s="187"/>
+      <c r="D100" s="185"/>
       <c r="E100" s="185"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
+      <c r="F100" s="185"/>
+      <c r="G100" s="185"/>
+      <c r="H100" s="185"/>
+      <c r="I100" s="185"/>
+      <c r="J100" s="185"/>
       <c r="K100" s="185"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
+      <c r="L100" s="185"/>
+      <c r="M100" s="185"/>
+      <c r="N100" s="185"/>
+      <c r="O100" s="185"/>
+      <c r="P100" s="185"/>
       <c r="Q100" s="185"/>
       <c r="R100" s="185"/>
       <c r="S100" s="185"/>
@@ -18308,22 +18312,22 @@
       <c r="AF100" s="185"/>
     </row>
     <row r="101">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
+      <c r="A101" s="185"/>
+      <c r="B101" s="185"/>
+      <c r="C101" s="185"/>
+      <c r="D101" s="185"/>
       <c r="E101" s="185"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
+      <c r="F101" s="185"/>
+      <c r="G101" s="185"/>
+      <c r="H101" s="185"/>
+      <c r="I101" s="185"/>
+      <c r="J101" s="185"/>
       <c r="K101" s="185"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
+      <c r="L101" s="185"/>
+      <c r="M101" s="185"/>
+      <c r="N101" s="185"/>
+      <c r="O101" s="185"/>
+      <c r="P101" s="185"/>
       <c r="Q101" s="185"/>
       <c r="R101" s="185"/>
       <c r="S101" s="185"/>
@@ -18341,22 +18345,22 @@
       <c r="AF101" s="185"/>
     </row>
     <row r="102">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="186"/>
-      <c r="D102" s="4"/>
+      <c r="A102" s="185"/>
+      <c r="B102" s="185"/>
+      <c r="C102" s="187"/>
+      <c r="D102" s="185"/>
       <c r="E102" s="185"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
+      <c r="F102" s="185"/>
+      <c r="G102" s="185"/>
+      <c r="H102" s="185"/>
+      <c r="I102" s="185"/>
+      <c r="J102" s="185"/>
       <c r="K102" s="185"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
+      <c r="L102" s="185"/>
+      <c r="M102" s="185"/>
+      <c r="N102" s="185"/>
+      <c r="O102" s="185"/>
+      <c r="P102" s="185"/>
       <c r="Q102" s="185"/>
       <c r="R102" s="185"/>
       <c r="S102" s="185"/>
@@ -18374,22 +18378,22 @@
       <c r="AF102" s="185"/>
     </row>
     <row r="103">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="186"/>
-      <c r="D103" s="4"/>
+      <c r="A103" s="185"/>
+      <c r="B103" s="185"/>
+      <c r="C103" s="187"/>
+      <c r="D103" s="185"/>
       <c r="E103" s="185"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
+      <c r="F103" s="185"/>
+      <c r="G103" s="185"/>
+      <c r="H103" s="185"/>
+      <c r="I103" s="185"/>
+      <c r="J103" s="185"/>
       <c r="K103" s="185"/>
-      <c r="L103" s="4"/>
-      <c r="M103" s="4"/>
-      <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
+      <c r="L103" s="185"/>
+      <c r="M103" s="185"/>
+      <c r="N103" s="185"/>
+      <c r="O103" s="185"/>
+      <c r="P103" s="185"/>
       <c r="Q103" s="185"/>
       <c r="R103" s="185"/>
       <c r="S103" s="185"/>
@@ -18408,22 +18412,22 @@
       <c r="AF103" s="185"/>
     </row>
     <row r="104">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
+      <c r="A104" s="185"/>
+      <c r="B104" s="185"/>
+      <c r="C104" s="185"/>
+      <c r="D104" s="185"/>
+      <c r="E104" s="185"/>
+      <c r="F104" s="185"/>
+      <c r="G104" s="185"/>
+      <c r="H104" s="185"/>
+      <c r="I104" s="185"/>
+      <c r="J104" s="185"/>
       <c r="K104" s="185"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
+      <c r="L104" s="185"/>
+      <c r="M104" s="185"/>
+      <c r="N104" s="185"/>
+      <c r="O104" s="185"/>
+      <c r="P104" s="185"/>
       <c r="Q104" s="185"/>
       <c r="R104" s="185"/>
       <c r="S104" s="185"/>
@@ -18442,22 +18446,22 @@
       <c r="AF104" s="185"/>
     </row>
     <row r="105">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="186"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
+      <c r="A105" s="185"/>
+      <c r="B105" s="185"/>
+      <c r="C105" s="187"/>
+      <c r="D105" s="185"/>
+      <c r="E105" s="185"/>
+      <c r="F105" s="185"/>
+      <c r="G105" s="185"/>
+      <c r="H105" s="185"/>
+      <c r="I105" s="185"/>
+      <c r="J105" s="185"/>
       <c r="K105" s="185"/>
-      <c r="L105" s="4"/>
-      <c r="M105" s="4"/>
-      <c r="N105" s="4"/>
-      <c r="O105" s="4"/>
-      <c r="P105" s="4"/>
+      <c r="L105" s="185"/>
+      <c r="M105" s="185"/>
+      <c r="N105" s="185"/>
+      <c r="O105" s="185"/>
+      <c r="P105" s="185"/>
       <c r="Q105" s="185"/>
       <c r="R105" s="185"/>
       <c r="S105" s="185"/>
@@ -18476,22 +18480,22 @@
       <c r="AF105" s="185"/>
     </row>
     <row r="106">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
+      <c r="A106" s="185"/>
+      <c r="B106" s="185"/>
+      <c r="C106" s="185"/>
+      <c r="D106" s="185"/>
       <c r="E106" s="185"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
+      <c r="F106" s="185"/>
+      <c r="G106" s="185"/>
+      <c r="H106" s="185"/>
+      <c r="I106" s="185"/>
+      <c r="J106" s="185"/>
       <c r="K106" s="185"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
+      <c r="L106" s="185"/>
+      <c r="M106" s="185"/>
+      <c r="N106" s="185"/>
+      <c r="O106" s="185"/>
+      <c r="P106" s="185"/>
       <c r="Q106" s="185"/>
       <c r="R106" s="185"/>
       <c r="S106" s="185"/>
@@ -18510,22 +18514,22 @@
       <c r="AF106" s="185"/>
     </row>
     <row r="107">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
+      <c r="A107" s="185"/>
+      <c r="B107" s="185"/>
+      <c r="C107" s="185"/>
+      <c r="D107" s="185"/>
+      <c r="E107" s="185"/>
+      <c r="F107" s="185"/>
+      <c r="G107" s="185"/>
+      <c r="H107" s="185"/>
+      <c r="I107" s="185"/>
+      <c r="J107" s="185"/>
       <c r="K107" s="185"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
+      <c r="L107" s="185"/>
+      <c r="M107" s="185"/>
+      <c r="N107" s="185"/>
+      <c r="O107" s="185"/>
+      <c r="P107" s="185"/>
       <c r="Q107" s="185"/>
       <c r="R107" s="185"/>
       <c r="S107" s="185"/>
@@ -18544,22 +18548,22 @@
       <c r="AF107" s="185"/>
     </row>
     <row r="108">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="186"/>
-      <c r="D108" s="4"/>
+      <c r="A108" s="185"/>
+      <c r="B108" s="185"/>
+      <c r="C108" s="187"/>
+      <c r="D108" s="185"/>
       <c r="E108" s="185"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
+      <c r="F108" s="185"/>
+      <c r="G108" s="185"/>
+      <c r="H108" s="185"/>
+      <c r="I108" s="185"/>
+      <c r="J108" s="185"/>
       <c r="K108" s="185"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
+      <c r="L108" s="185"/>
+      <c r="M108" s="185"/>
+      <c r="N108" s="185"/>
+      <c r="O108" s="185"/>
+      <c r="P108" s="185"/>
       <c r="Q108" s="185"/>
       <c r="R108" s="185"/>
       <c r="S108" s="185"/>
@@ -18578,22 +18582,22 @@
       <c r="AF108" s="185"/>
     </row>
     <row r="109">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
+      <c r="A109" s="185"/>
+      <c r="B109" s="185"/>
+      <c r="C109" s="185"/>
+      <c r="D109" s="185"/>
+      <c r="E109" s="185"/>
+      <c r="F109" s="185"/>
+      <c r="G109" s="185"/>
+      <c r="H109" s="185"/>
+      <c r="I109" s="185"/>
+      <c r="J109" s="185"/>
       <c r="K109" s="185"/>
-      <c r="L109" s="4"/>
-      <c r="M109" s="4"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
+      <c r="L109" s="185"/>
+      <c r="M109" s="185"/>
+      <c r="N109" s="185"/>
+      <c r="O109" s="185"/>
+      <c r="P109" s="185"/>
       <c r="Q109" s="185"/>
       <c r="R109" s="185"/>
       <c r="S109" s="185"/>
@@ -18703,6 +18707,7 @@
       <c r="Z112" s="185"/>
       <c r="AB112" s="185"/>
       <c r="AC112" s="185"/>
+      <c r="AD112" s="185"/>
       <c r="AE112" s="185"/>
       <c r="AF112" s="185"/>
     </row>
@@ -18865,6 +18870,7 @@
       <c r="AA117" s="185"/>
       <c r="AB117" s="185"/>
       <c r="AC117" s="185"/>
+      <c r="AD117" s="185"/>
       <c r="AE117" s="185"/>
       <c r="AF117" s="185"/>
     </row>
@@ -18931,6 +18937,7 @@
       <c r="AA119" s="185"/>
       <c r="AB119" s="185"/>
       <c r="AC119" s="185"/>
+      <c r="AD119" s="185"/>
       <c r="AE119" s="185"/>
       <c r="AF119" s="185"/>
     </row>
@@ -19051,6 +19058,7 @@
       <c r="O123" s="185"/>
       <c r="P123" s="185"/>
       <c r="Q123" s="185"/>
+      <c r="R123" s="185"/>
       <c r="S123" s="185"/>
       <c r="T123" s="185"/>
       <c r="U123" s="185"/>
@@ -19059,6 +19067,7 @@
       <c r="X123" s="185"/>
       <c r="Y123" s="185"/>
       <c r="Z123" s="185"/>
+      <c r="AA123" s="185"/>
       <c r="AB123" s="185"/>
       <c r="AC123" s="185"/>
       <c r="AE123" s="185"/>
@@ -19200,8 +19209,8 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="189">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),31.0)</f>
+        <v>31</v>
       </c>
       <c r="W1" s="190" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"dní")</f>
@@ -19406,8 +19415,8 @@
         <v>432.3078</v>
       </c>
       <c r="W5" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
@@ -19472,8 +19481,8 @@
         <v>432.3078</v>
       </c>
       <c r="W6" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
@@ -19532,8 +19541,8 @@
         <v>341.19</v>
       </c>
       <c r="W7" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
@@ -19557,7 +19566,7 @@
       </c>
       <c r="B8" s="192" t="str">
         <f>IF(OR(E8=Report!$B$1, F8=Report!$B$1, G8=Report!$B$1, H8=Report!$B$1), D8, "")</f>
-        <v/>
+        <v>Ahurieva Viktoriia</v>
       </c>
       <c r="C8" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -19580,8 +19589,8 @@
         <v>Výroba</v>
       </c>
       <c r="H8" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -19601,8 +19610,8 @@
         <v>432.3078</v>
       </c>
       <c r="W8" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
@@ -19664,8 +19673,8 @@
         <v>341.19</v>
       </c>
       <c r="W9" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
@@ -19733,8 +19742,8 @@
         <v>432.3078</v>
       </c>
       <c r="W10" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
@@ -19913,8 +19922,8 @@
         <v>341.19</v>
       </c>
       <c r="W13" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
@@ -20042,8 +20051,8 @@
         <v>341.19</v>
       </c>
       <c r="W15" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
@@ -20105,8 +20114,8 @@
         <v>341.19</v>
       </c>
       <c r="W16" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
@@ -20196,8 +20205,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="D18" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pánková Vendula")</f>
+        <v>Pánková Vendula</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -20215,8 +20230,8 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
+        <v>267.6</v>
       </c>
       <c r="W18" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20247,14 +20262,29 @@
         <v/>
       </c>
       <c r="C19" s="2" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Erik")</f>
+        <v>Hegedüs Erik</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="G19" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="H19" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -20269,12 +20299,12 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),432.3078)</f>
+        <v>432.3078</v>
       </c>
       <c r="W19" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
@@ -20301,16 +20331,16 @@
         <v/>
       </c>
       <c r="C20" s="2" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pánková Vendula")</f>
-        <v>Pánková Vendula</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav ml.")</f>
+        <v>Roth Stanislav ml.</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -20329,12 +20359,12 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
-        <v>267.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),432.3078)</f>
+        <v>432.3078</v>
       </c>
       <c r="W20" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
@@ -20361,29 +20391,23 @@
         <v/>
       </c>
       <c r="C21" s="2" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Erik")</f>
-        <v>Hegedüs Erik</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubník Martin")</f>
+        <v>Bubník Martin</v>
       </c>
       <c r="E21" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
       <c r="F21" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="G21" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="H21" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -20398,12 +20422,12 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),432.3078)</f>
-        <v>432.3078</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
+        <v>267.6</v>
       </c>
       <c r="W21" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
@@ -20430,16 +20454,16 @@
         <v/>
       </c>
       <c r="C22" s="2" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav ml.")</f>
-        <v>Roth Stanislav ml.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Berdar Vasyl")</f>
+        <v>Berdar Vasyl</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -20458,12 +20482,12 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),432.3078)</f>
-        <v>432.3078</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.332)</f>
+        <v>286.332</v>
       </c>
       <c r="W22" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
@@ -20487,23 +20511,32 @@
       </c>
       <c r="B23" s="192" t="str">
         <f>IF(OR(E23=Report!$B$1, F23=Report!$B$1, G23=Report!$B$1, H23=Report!$B$1), D23, "")</f>
-        <v>Makula Radek</v>
+        <v>Yarushynskyi Vladyslav</v>
       </c>
       <c r="C23" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D23" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Makula Radek")</f>
-        <v>Makula Radek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yarushynskyi Vladyslav")</f>
+        <v>Yarushynskyi Vladyslav</v>
       </c>
       <c r="E23" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="G23" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
+      <c r="H23" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
         <v>Prosek</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -20518,8 +20551,8 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
+        <v>267.6</v>
       </c>
       <c r="W23" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20554,12 +20587,12 @@
         <v>0</v>
       </c>
       <c r="D24" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubník Martin")</f>
-        <v>Bubník Martin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Židek Petr")</f>
+        <v>Židek Petr</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F24" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
@@ -20581,8 +20614,8 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
-        <v>267.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W24" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20610,22 +20643,28 @@
       </c>
       <c r="B25" s="192" t="str">
         <f>IF(OR(E25=Report!$B$1, F25=Report!$B$1, G25=Report!$B$1, H25=Report!$B$1), D25, "")</f>
-        <v/>
+        <v>Gorol Patrik</v>
       </c>
       <c r="C25" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D25" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mirga Simon")</f>
-        <v>Mirga Simon</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gorol Patrik")</f>
+        <v>Gorol Patrik</v>
       </c>
       <c r="E25" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="F25" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="G25" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -20676,8 +20715,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="D26" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Gergö")</f>
+        <v>Hegedüs Gergö</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -20695,8 +20740,8 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W26" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20731,8 +20776,8 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Berdar Vasyl")</f>
-        <v>Berdar Vasyl</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Barvínková Eliška")</f>
+        <v>Barvínková Eliška</v>
       </c>
       <c r="E27" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -20755,8 +20800,8 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),286.332)</f>
-        <v>286.332</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W27" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20784,32 +20829,26 @@
       </c>
       <c r="B28" s="192" t="str">
         <f>IF(OR(E28=Report!$B$1, F28=Report!$B$1, G28=Report!$B$1, H28=Report!$B$1), D28, "")</f>
-        <v>Yarushynskyi Vladyslav</v>
+        <v/>
       </c>
       <c r="C28" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yarushynskyi Vladyslav")</f>
-        <v>Yarushynskyi Vladyslav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kursheva Diana")</f>
+        <v>Kursheva Diana</v>
       </c>
       <c r="E28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
       </c>
       <c r="F28" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="G28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
-      <c r="H28" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -20824,8 +20863,8 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
-        <v>267.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W28" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20859,8 +20898,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="D29" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kubík Martin")</f>
+        <v>Kubík Martin</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -20878,8 +20923,8 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W29" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -20907,23 +20952,23 @@
       </c>
       <c r="B30" s="192" t="str">
         <f>IF(OR(E30=Report!$B$1, F30=Report!$B$1, G30=Report!$B$1, H30=Report!$B$1), D30, "")</f>
-        <v/>
+        <v>Putna Jaroslav</v>
       </c>
       <c r="C30" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D30" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Židek Petr")</f>
-        <v>Židek Petr</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Putna Jaroslav")</f>
+        <v>Putna Jaroslav</v>
       </c>
       <c r="E30" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F30" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -20970,29 +21015,32 @@
       </c>
       <c r="B31" s="192" t="str">
         <f>IF(OR(E31=Report!$B$1, F31=Report!$B$1, G31=Report!$B$1, H31=Report!$B$1), D31, "")</f>
-        <v>Gorol Patrik</v>
+        <v>Kopic Jakub</v>
       </c>
       <c r="C31" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D31" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gorol Patrik")</f>
-        <v>Gorol Patrik</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kopic Jakub")</f>
+        <v>Kopic Jakub</v>
       </c>
       <c r="E31" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
       <c r="F31" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
+      <c r="G31" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="G31" s="2" t="str">
+      <c r="H31" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
         <v>Prosek</v>
       </c>
-      <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -21007,8 +21055,8 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W31" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21036,19 +21084,19 @@
       </c>
       <c r="B32" s="192" t="str">
         <f>IF(OR(E32=Report!$B$1, F32=Report!$B$1, G32=Report!$B$1, H32=Report!$B$1), D32, "")</f>
-        <v/>
+        <v>Fáberová Kateřina</v>
       </c>
       <c r="C32" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D32" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kratochvíl Kryštof")</f>
-        <v>Kratochvíl Kryštof</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fáberová Kateřina")</f>
+        <v>Fáberová Kateřina</v>
       </c>
       <c r="E32" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -21067,8 +21115,8 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),267.6)</f>
-        <v>267.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W32" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21103,12 +21151,12 @@
         <v>0</v>
       </c>
       <c r="D33" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Gergö")</f>
-        <v>Hegedüs Gergö</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubnová Adéla")</f>
+        <v>Chlubnová Adéla</v>
       </c>
       <c r="E33" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -21127,8 +21175,8 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W33" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21163,8 +21211,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Barvínková Eliška")</f>
-        <v>Barvínková Eliška</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prošek Václav")</f>
+        <v>Prošek Václav</v>
       </c>
       <c r="E34" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -21187,8 +21235,8 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W34" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21223,17 +21271,14 @@
         <v>0</v>
       </c>
       <c r="D35" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kursheva Diana")</f>
-        <v>Kursheva Diana</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Millington Emmanuel")</f>
+        <v>Millington Emmanuel</v>
       </c>
       <c r="E35" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
-      </c>
-      <c r="F35" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -21286,12 +21331,12 @@
         <v>0</v>
       </c>
       <c r="D36" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tůma Vladimír")</f>
-        <v>Tůma Vladimír</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kašpárek Jan")</f>
+        <v>Kašpárek Jan</v>
       </c>
       <c r="E36" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -21346,12 +21391,12 @@
         <v>0</v>
       </c>
       <c r="D37" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kubík Martin")</f>
-        <v>Kubík Martin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Koteliuk Maryna")</f>
+        <v>Koteliuk Maryna</v>
       </c>
       <c r="E37" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -21399,24 +21444,21 @@
       </c>
       <c r="B38" s="192" t="str">
         <f>IF(OR(E38=Report!$B$1, F38=Report!$B$1, G38=Report!$B$1, H38=Report!$B$1), D38, "")</f>
-        <v>Putna Jaroslav</v>
+        <v/>
       </c>
       <c r="C38" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D38" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Putna Jaroslav")</f>
-        <v>Putna Jaroslav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Remač Jiří")</f>
+        <v>Remač Jiří</v>
       </c>
       <c r="E38" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
-      <c r="F38" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -21462,32 +21504,17 @@
       </c>
       <c r="B39" s="192" t="str">
         <f>IF(OR(E39=Report!$B$1, F39=Report!$B$1, G39=Report!$B$1, H39=Report!$B$1), D39, "")</f>
-        <v>Kopic Jakub</v>
+        <v/>
       </c>
       <c r="C39" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kopic Jakub")</f>
-        <v>Kopic Jakub</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
-      <c r="F39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
-      <c r="G39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="H39" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -21502,8 +21529,8 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W39" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21531,20 +21558,14 @@
       </c>
       <c r="B40" s="192" t="str">
         <f>IF(OR(E40=Report!$B$1, F40=Report!$B$1, G40=Report!$B$1, H40=Report!$B$1), D40, "")</f>
-        <v>Fáberová Kateřina</v>
+        <v/>
       </c>
       <c r="C40" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fáberová Kateřina")</f>
-        <v>Fáberová Kateřina</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -21562,8 +21583,8 @@
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W40" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21597,14 +21618,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubnová Adéla")</f>
-        <v>Chlubnová Adéla</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -21622,8 +21637,8 @@
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W41" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -21657,14 +21672,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prošek Václav")</f>
-        <v>Prošek Václav</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -21682,8 +21691,8 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W42" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -23871,19 +23880,19 @@
       <c r="A86" s="2"/>
       <c r="B86" s="192" t="str">
         <f>IF(OR(E86=Report!$B$1, F86=Report!$B$1, G86=Report!$B$1, H86=Report!$B$1), D86, "")</f>
-        <v>Mikuš Pavel</v>
+        <v/>
       </c>
       <c r="C86" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D86" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mikuš Pavel")</f>
-        <v>Mikuš Pavel</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hyský Aleš")</f>
+        <v>Hyský Aleš</v>
       </c>
       <c r="E86" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -23902,8 +23911,8 @@
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W86" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -23935,16 +23944,25 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hyský Aleš")</f>
-        <v>Hyský Aleš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lažek Jaroslav")</f>
+        <v>Lažek Jaroslav</v>
       </c>
       <c r="E87" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F87" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
+      <c r="G87" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="H87" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
+      </c>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -23959,8 +23977,8 @@
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
       <c r="V87" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
+        <v>170</v>
       </c>
       <c r="W87" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -23985,19 +24003,19 @@
       <c r="A88" s="2"/>
       <c r="B88" s="192" t="str">
         <f>IF(OR(E88=Report!$B$1, F88=Report!$B$1, G88=Report!$B$1, H88=Report!$B$1), D88, "")</f>
-        <v>Šmídová Sabina</v>
+        <v>Kormash Liubov</v>
       </c>
       <c r="C88" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D88" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Šmídová Sabina")</f>
-        <v>Šmídová Sabina</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kormash Liubov")</f>
+        <v>Kormash Liubov</v>
       </c>
       <c r="E88" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F88" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
@@ -24019,8 +24037,8 @@
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
       <c r="V88" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),160.0)</f>
+        <v>160</v>
       </c>
       <c r="W88" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24052,25 +24070,22 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lažek Jaroslav")</f>
-        <v>Lažek Jaroslav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubna Tomáš")</f>
+        <v>Chlubna Tomáš</v>
       </c>
       <c r="E89" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="F89" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F89" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
       <c r="G89" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
-      <c r="H89" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
         <v>Výroba</v>
       </c>
+      <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
@@ -24085,8 +24100,8 @@
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
       <c r="V89" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
-        <v>170</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W89" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24111,25 +24126,28 @@
       <c r="A90" s="2"/>
       <c r="B90" s="192" t="str">
         <f>IF(OR(E90=Report!$B$1, F90=Report!$B$1, G90=Report!$B$1, H90=Report!$B$1), D90, "")</f>
-        <v>Kormash Liubov</v>
+        <v>Vychivskyi Volodymyr</v>
       </c>
       <c r="C90" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D90" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kormash Liubov")</f>
-        <v>Kormash Liubov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vychivskyi Volodymyr")</f>
+        <v>Vychivskyi Volodymyr</v>
       </c>
       <c r="E90" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
       </c>
       <c r="F90" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
         <v>Prosek</v>
       </c>
-      <c r="G90" s="2"/>
+      <c r="G90" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
@@ -24145,8 +24163,8 @@
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
       <c r="V90" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),160.0)</f>
-        <v>160</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W90" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24171,17 +24189,32 @@
       <c r="A91" s="2"/>
       <c r="B91" s="192" t="str">
         <f>IF(OR(E91=Report!$B$1, F91=Report!$B$1, G91=Report!$B$1, H91=Report!$B$1), D91, "")</f>
-        <v/>
+        <v>Hřebík Martin</v>
       </c>
       <c r="C91" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
+      <c r="D91" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hřebík Martin")</f>
+        <v>Hřebík Martin</v>
+      </c>
+      <c r="E91" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
+      </c>
+      <c r="F91" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="G91" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
+      <c r="H91" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
@@ -24196,12 +24229,12 @@
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
       <c r="V91" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.68199999999996)</f>
+        <v>386.682</v>
       </c>
       <c r="W91" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2494.722580645161)</f>
+        <v>2494.722581</v>
       </c>
       <c r="X91" s="2"/>
       <c r="Y91" s="2"/>
@@ -24228,8 +24261,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="D92" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Eszenyiová Patrícia")</f>
+        <v>Eszenyiová Patrícia</v>
+      </c>
+      <c r="E92" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -24247,8 +24286,8 @@
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W92" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24273,29 +24312,32 @@
       <c r="A93" s="2"/>
       <c r="B93" s="192" t="str">
         <f>IF(OR(E93=Report!$B$1, F93=Report!$B$1, G93=Report!$B$1, H93=Report!$B$1), D93, "")</f>
-        <v/>
+        <v>Reischl Jan</v>
       </c>
       <c r="C93" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D93" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubna Tomáš")</f>
-        <v>Chlubna Tomáš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Reischl Jan")</f>
+        <v>Reischl Jan</v>
       </c>
       <c r="E93" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="F93" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="F93" s="2" t="str">
+      <c r="G93" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="G93" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
-      </c>
-      <c r="H93" s="2"/>
+      <c r="H93" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -24310,8 +24352,8 @@
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
       <c r="V93" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W93" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24336,28 +24378,22 @@
       <c r="A94" s="2"/>
       <c r="B94" s="192" t="str">
         <f>IF(OR(E94=Report!$B$1, F94=Report!$B$1, G94=Report!$B$1, H94=Report!$B$1), D94, "")</f>
-        <v>Vychivskyi Volodymyr</v>
+        <v/>
       </c>
       <c r="C94" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D94" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vychivskyi Volodymyr")</f>
-        <v>Vychivskyi Volodymyr</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mikešová Adéla")</f>
+        <v>Mikešová Adéla</v>
       </c>
       <c r="E94" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
-      <c r="F94" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
-      <c r="G94" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
@@ -24373,8 +24409,8 @@
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
       <c r="V94" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W94" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24405,8 +24441,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="D95" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chyský David")</f>
+        <v>Chyský David</v>
+      </c>
+      <c r="E95" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -24424,8 +24466,8 @@
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
       <c r="V95" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W95" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24450,32 +24492,26 @@
       <c r="A96" s="2"/>
       <c r="B96" s="192" t="str">
         <f>IF(OR(E96=Report!$B$1, F96=Report!$B$1, G96=Report!$B$1, H96=Report!$B$1), D96, "")</f>
-        <v>Hřebík Martin</v>
+        <v/>
       </c>
       <c r="C96" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D96" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hřebík Martin")</f>
-        <v>Hřebík Martin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kalina Filip")</f>
+        <v>Kalina Filip</v>
       </c>
       <c r="E96" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
       </c>
       <c r="F96" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="G96" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
-      <c r="H96" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -24490,12 +24526,12 @@
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
       <c r="V96" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.68199999999996)</f>
-        <v>386.682</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W96" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2577.8799999999997)</f>
-        <v>2577.88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X96" s="2"/>
       <c r="Y96" s="2"/>
@@ -24523,12 +24559,12 @@
         <v>0</v>
       </c>
       <c r="D97" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Eszenyiová Patrícia")</f>
-        <v>Eszenyiová Patrícia</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kaločai Rudolf")</f>
+        <v>Kaločai Rudolf</v>
       </c>
       <c r="E97" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -24547,8 +24583,8 @@
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
       <c r="V97" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="W97" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24573,32 +24609,26 @@
       <c r="A98" s="2"/>
       <c r="B98" s="192" t="str">
         <f>IF(OR(E98=Report!$B$1, F98=Report!$B$1, G98=Report!$B$1, H98=Report!$B$1), D98, "")</f>
-        <v>Reischl Jan</v>
+        <v/>
       </c>
       <c r="C98" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D98" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Reischl Jan")</f>
-        <v>Reischl Jan</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dušek Sam")</f>
+        <v>Dušek Sam</v>
       </c>
       <c r="E98" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F98" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="F98" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="G98" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="H98" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
@@ -24613,8 +24643,8 @@
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
       <c r="V98" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W98" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24646,12 +24676,12 @@
         <v>0</v>
       </c>
       <c r="D99" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mikešová Adéla")</f>
-        <v>Mikešová Adéla</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Banga Adam")</f>
+        <v>Banga Adam</v>
       </c>
       <c r="E99" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -24670,8 +24700,8 @@
       <c r="T99" s="2"/>
       <c r="U99" s="2"/>
       <c r="V99" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W99" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24703,12 +24733,12 @@
         <v>0</v>
       </c>
       <c r="D100" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pražák Aleš")</f>
-        <v>Pražák Aleš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Anna")</f>
+        <v>Vopatová Anna</v>
       </c>
       <c r="E100" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -24727,8 +24757,8 @@
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
       <c r="V100" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W100" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24760,12 +24790,12 @@
         <v>0</v>
       </c>
       <c r="D101" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chyský David")</f>
-        <v>Chyský David</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Šárka")</f>
+        <v>Vopatová Šárka</v>
       </c>
       <c r="E101" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -24784,8 +24814,8 @@
       <c r="T101" s="2"/>
       <c r="U101" s="2"/>
       <c r="V101" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W101" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24816,8 +24846,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+      <c r="D102" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Richterová Monika")</f>
+        <v>Richterová Monika</v>
+      </c>
+      <c r="E102" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -24835,8 +24871,8 @@
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
       <c r="V102" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W102" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24867,9 +24903,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
+      <c r="D103" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Serin David")</f>
+        <v>Serin David</v>
+      </c>
+      <c r="E103" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F103" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
@@ -24886,8 +24931,8 @@
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
       <c r="V103" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W103" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -24912,19 +24957,19 @@
       <c r="A104" s="2"/>
       <c r="B104" s="192" t="str">
         <f>IF(OR(E104=Report!$B$1, F104=Report!$B$1, G104=Report!$B$1, H104=Report!$B$1), D104, "")</f>
-        <v>Kulinič Michail</v>
+        <v/>
       </c>
       <c r="C104" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D104" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kulinič Michail")</f>
-        <v>Kulinič Michail</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fabera Tomáš")</f>
+        <v>Fabera Tomáš</v>
       </c>
       <c r="E104" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -24976,17 +25021,14 @@
         <v>0</v>
       </c>
       <c r="D105" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kalina Filip")</f>
-        <v>Kalina Filip</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hendrych Rostislav")</f>
+        <v>Hendrych Rostislav</v>
       </c>
       <c r="E105" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="F105" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
+      <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
@@ -25003,8 +25045,8 @@
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
       <c r="V105" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W105" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25035,8 +25077,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
+      <c r="D106" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Světlík František")</f>
+        <v>Světlík František</v>
+      </c>
+      <c r="E106" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -25054,8 +25102,8 @@
       <c r="T106" s="2"/>
       <c r="U106" s="2"/>
       <c r="V106" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W106" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25087,8 +25135,8 @@
         <v>0</v>
       </c>
       <c r="D107" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kaločai Rudolf")</f>
-        <v>Kaločai Rudolf</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ženíšek Lukáš")</f>
+        <v>Ženíšek Lukáš</v>
       </c>
       <c r="E107" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
@@ -25111,8 +25159,8 @@
       <c r="T107" s="2"/>
       <c r="U107" s="2"/>
       <c r="V107" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W107" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25144,17 +25192,14 @@
         <v>0</v>
       </c>
       <c r="D108" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dušek Sam")</f>
-        <v>Dušek Sam</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav st.")</f>
+        <v>Roth Stanislav st.</v>
       </c>
       <c r="E108" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F108" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
+      <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
@@ -25171,12 +25216,12 @@
       <c r="T108" s="2"/>
       <c r="U108" s="2"/>
       <c r="V108" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49506.0)</f>
+        <v>49506</v>
       </c>
       <c r="W108" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1596.967741935484)</f>
+        <v>1596.967742</v>
       </c>
       <c r="X108" s="2"/>
       <c r="Y108" s="2"/>
@@ -25197,19 +25242,19 @@
       <c r="A109" s="2"/>
       <c r="B109" s="192" t="str">
         <f>IF(OR(E109=Report!$B$1, F109=Report!$B$1, G109=Report!$B$1, H109=Report!$B$1), D109, "")</f>
-        <v>Kačena Stanislav</v>
+        <v/>
       </c>
       <c r="C109" s="2" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D109" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kačena Stanislav")</f>
-        <v>Kačena Stanislav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vaníková Anna")</f>
+        <v>Vaníková Anna</v>
       </c>
       <c r="E109" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -25228,8 +25273,8 @@
       <c r="T109" s="2"/>
       <c r="U109" s="2"/>
       <c r="V109" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W109" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25261,8 +25306,8 @@
         <v>0</v>
       </c>
       <c r="D110" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cieslar Marek")</f>
-        <v>Cieslar Marek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Břicháč Pavel")</f>
+        <v>Břicháč Pavel</v>
       </c>
       <c r="E110" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -25285,8 +25330,8 @@
       <c r="T110" s="2"/>
       <c r="U110" s="2"/>
       <c r="V110" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W110" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25318,8 +25363,8 @@
         <v>0</v>
       </c>
       <c r="D111" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Banga Adam")</f>
-        <v>Banga Adam</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čerešňák Michal")</f>
+        <v>Čerešňák Michal</v>
       </c>
       <c r="E111" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
@@ -25342,8 +25387,8 @@
       <c r="T111" s="2"/>
       <c r="U111" s="2"/>
       <c r="V111" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
+        <v>170</v>
       </c>
       <c r="W111" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25375,14 +25420,17 @@
         <v>0</v>
       </c>
       <c r="D112" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Anna")</f>
-        <v>Vopatová Anna</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Weindling Josef")</f>
+        <v>Weindling Josef</v>
       </c>
       <c r="E112" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
-      <c r="F112" s="2"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F112" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -25399,8 +25447,8 @@
       <c r="T112" s="2"/>
       <c r="U112" s="2"/>
       <c r="V112" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W112" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25432,12 +25480,12 @@
         <v>0</v>
       </c>
       <c r="D113" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Šárka")</f>
-        <v>Vopatová Šárka</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fux Vojtěch")</f>
+        <v>Fux Vojtěch</v>
       </c>
       <c r="E113" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -25456,8 +25504,8 @@
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
       <c r="V113" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),200.0)</f>
+        <v>200</v>
       </c>
       <c r="W113" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25489,12 +25537,12 @@
         <v>0</v>
       </c>
       <c r="D114" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Richterová Monika")</f>
-        <v>Richterová Monika</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kumar Jatinder")</f>
+        <v>Kumar Jatinder</v>
       </c>
       <c r="E114" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -25513,8 +25561,8 @@
       <c r="T114" s="2"/>
       <c r="U114" s="2"/>
       <c r="V114" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
+        <v>231.474</v>
       </c>
       <c r="W114" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25546,17 +25594,14 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Serin David")</f>
-        <v>Serin David</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stehlíková Magdaléna")</f>
+        <v>Stehlíková Magdaléna</v>
       </c>
       <c r="E115" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F115" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
+      <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
@@ -25573,8 +25618,8 @@
       <c r="T115" s="2"/>
       <c r="U115" s="2"/>
       <c r="V115" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
+        <v>214.08</v>
       </c>
       <c r="W115" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25606,14 +25651,17 @@
         <v>0</v>
       </c>
       <c r="D116" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fabera Tomáš")</f>
-        <v>Fabera Tomáš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dragoun Alfréd")</f>
+        <v>Dragoun Alfréd</v>
       </c>
       <c r="E116" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="F116" s="2"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
+      <c r="F116" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -25630,8 +25678,8 @@
       <c r="T116" s="2"/>
       <c r="U116" s="2"/>
       <c r="V116" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W116" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25662,14 +25710,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D117" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hendrych Rostislav")</f>
-        <v>Hendrych Rostislav</v>
-      </c>
-      <c r="E117" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -25687,8 +25729,8 @@
       <c r="T117" s="2"/>
       <c r="U117" s="2"/>
       <c r="V117" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W117" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25770,14 +25812,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D119" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Světlík František")</f>
-        <v>Světlík František</v>
-      </c>
-      <c r="E119" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -25795,8 +25831,8 @@
       <c r="T119" s="2"/>
       <c r="U119" s="2"/>
       <c r="V119" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W119" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25827,14 +25863,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D120" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ženíšek Lukáš")</f>
-        <v>Ženíšek Lukáš</v>
-      </c>
-      <c r="E120" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -25852,8 +25882,8 @@
       <c r="T120" s="2"/>
       <c r="U120" s="2"/>
       <c r="V120" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W120" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25885,10 +25915,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="2"/>
-      <c r="E121" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -25906,8 +25933,8 @@
       <c r="T121" s="2"/>
       <c r="U121" s="2"/>
       <c r="V121" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W121" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -25938,14 +25965,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D122" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav st.")</f>
-        <v>Roth Stanislav st.</v>
-      </c>
-      <c r="E122" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -25963,12 +25984,12 @@
       <c r="T122" s="2"/>
       <c r="U122" s="2"/>
       <c r="V122" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49506.0)</f>
-        <v>49506</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W122" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1650.2)</f>
-        <v>1650.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X122" s="2"/>
       <c r="Y122" s="2"/>
@@ -26097,14 +26118,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D125" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vaníková Anna")</f>
-        <v>Vaníková Anna</v>
-      </c>
-      <c r="E125" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -26122,8 +26137,8 @@
       <c r="T125" s="2"/>
       <c r="U125" s="2"/>
       <c r="V125" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W125" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26154,14 +26169,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D126" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Břicháč Pavel")</f>
-        <v>Břicháč Pavel</v>
-      </c>
-      <c r="E126" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -26179,8 +26188,8 @@
       <c r="T126" s="2"/>
       <c r="U126" s="2"/>
       <c r="V126" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W126" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26211,14 +26220,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D127" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čerešňák Michal")</f>
-        <v>Čerešňák Michal</v>
-      </c>
-      <c r="E127" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -26236,8 +26239,8 @@
       <c r="T127" s="2"/>
       <c r="U127" s="2"/>
       <c r="V127" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
-        <v>170</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W127" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26268,18 +26271,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D128" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Weindling Josef")</f>
-        <v>Weindling Josef</v>
-      </c>
-      <c r="E128" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F128" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
@@ -26296,8 +26290,8 @@
       <c r="T128" s="2"/>
       <c r="U128" s="2"/>
       <c r="V128" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W128" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26328,14 +26322,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D129" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fux Vojtěch")</f>
-        <v>Fux Vojtěch</v>
-      </c>
-      <c r="E129" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -26353,8 +26341,8 @@
       <c r="T129" s="2"/>
       <c r="U129" s="2"/>
       <c r="V129" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),200.0)</f>
-        <v>200</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W129" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26385,13 +26373,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D130" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kumar Jatinder")</f>
-        <v>Kumar Jatinder</v>
-      </c>
+      <c r="D130" s="2"/>
       <c r="E130" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -26442,14 +26427,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D131" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stehlíková Magdaléna")</f>
-        <v>Stehlíková Magdaléna</v>
-      </c>
-      <c r="E131" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -26467,8 +26446,8 @@
       <c r="T131" s="2"/>
       <c r="U131" s="2"/>
       <c r="V131" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),214.08)</f>
-        <v>214.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W131" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -26499,14 +26478,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D132" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dragoun Alfréd")</f>
-        <v>Dragoun Alfréd</v>
-      </c>
-      <c r="E132" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -26524,8 +26497,8 @@
       <c r="T132" s="2"/>
       <c r="U132" s="2"/>
       <c r="V132" s="190">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W132" s="190">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>

--- a/google_data/Pobočky/Prosek/Report Prosek.xlsx
+++ b/google_data/Pobočky/Prosek/Report Prosek.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="705">
   <si>
     <t>Datum</t>
   </si>
@@ -1926,10 +1926,10 @@
     <t>Počet dní</t>
   </si>
   <si>
-    <t>Yarushynskyi Vladyslav</t>
-  </si>
-  <si>
-    <t>12:00</t>
+    <t>Šebesta Tomáš</t>
+  </si>
+  <si>
+    <t>22:00</t>
   </si>
   <si>
     <t>29:00</t>
@@ -1938,13 +1938,13 @@
     <t>Vychivskyi Volodymyr</t>
   </si>
   <si>
-    <t>202:30</t>
-  </si>
-  <si>
-    <t>Šebesta Tomáš</t>
-  </si>
-  <si>
-    <t>201:00</t>
+    <t>26:30</t>
+  </si>
+  <si>
+    <t>Fáberová Kateřina</t>
+  </si>
+  <si>
+    <t>7:00</t>
   </si>
   <si>
     <t>23:00</t>
@@ -1956,28 +1956,7 @@
     <t>13:00</t>
   </si>
   <si>
-    <t>Putna Jaroslav</t>
-  </si>
-  <si>
-    <t>203:30</t>
-  </si>
-  <si>
-    <t>Fáberová Kateřina</t>
-  </si>
-  <si>
-    <t>47:00</t>
-  </si>
-  <si>
-    <t>7:00</t>
-  </si>
-  <si>
-    <t>Ahurieva Viktoriia</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t>12 min 31 s</t>
+    <t>11 min 04 s</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -13253,7 +13232,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="9">
-        <v>46205.0</v>
+        <v>46207.0</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="11" t="s">
@@ -13302,7 +13281,7 @@
       <c r="A3" s="24"/>
       <c r="B3" s="25" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Sobota</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -14124,13 +14103,13 @@
         <v>Prosek</v>
       </c>
       <c r="C1" s="106">
-        <v>46174.0</v>
+        <v>46204.0</v>
       </c>
       <c r="D1" s="107" t="s">
         <v>631</v>
       </c>
       <c r="E1" s="108">
-        <v>46203.0</v>
+        <v>46234.0</v>
       </c>
       <c r="F1" s="109" t="s">
         <v>586</v>
@@ -14155,18 +14134,18 @@
       <c r="D2" s="16"/>
       <c r="E2" s="18"/>
       <c r="F2" s="111">
-        <v>0.3125156426126</v>
+        <v>0.28180847808358267</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="112">
-        <v>1094445.3499999999</v>
+        <v>75991.6</v>
       </c>
       <c r="K2" s="20"/>
       <c r="L2" s="113" t="s">
         <v>589</v>
       </c>
       <c r="M2" s="114">
-        <v>474655.6900000001</v>
+        <v>35786.60000000002</v>
       </c>
       <c r="N2" s="115"/>
     </row>
@@ -14174,12 +14153,12 @@
       <c r="A3" s="116"/>
       <c r="B3" s="117" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pondělí</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="117" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Pátek</v>
       </c>
       <c r="E3" s="10"/>
       <c r="H3" s="20"/>
@@ -14188,7 +14167,7 @@
         <v>590</v>
       </c>
       <c r="M3" s="119">
-        <v>161058.0</v>
+        <v>8516.0</v>
       </c>
       <c r="N3" s="115"/>
     </row>
@@ -14208,7 +14187,7 @@
         <v>591</v>
       </c>
       <c r="M4" s="119">
-        <v>177588.06</v>
+        <v>12333.0</v>
       </c>
       <c r="N4" s="115"/>
     </row>
@@ -14232,7 +14211,7 @@
         <v>593</v>
       </c>
       <c r="M5" s="119">
-        <v>131132.1</v>
+        <v>8397.0</v>
       </c>
       <c r="N5" s="115"/>
     </row>
@@ -14252,7 +14231,7 @@
         <v>594</v>
       </c>
       <c r="M6" s="119">
-        <v>13968.6</v>
+        <v>309.0</v>
       </c>
       <c r="N6" s="115"/>
     </row>
@@ -14260,14 +14239,14 @@
       <c r="A7" s="124"/>
       <c r="B7" s="125">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(D10:D30, FIND(":", D10:D30) - 1) * 60, 0) + IFERROR(MID(D10:D30, FIND(":", D10:D30) + 1, LEN(D10:D30) - FIND(":", D10:D30)), 0))), "[h]:mm")/60</f>
-        <v>670.5</v>
+        <v>42</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="18"/>
       <c r="F7" s="126">
         <f>TEXT(SUMPRODUCT((IFERROR(LEFT(H10:H30, FIND(":", H10:H30) - 1) * 60, 0) + IFERROR(MID(H10:H30, FIND(":", H10:H30) + 1, LEN(H10:H30) - FIND(":", H10:H30)), 0))), "[h]:mm")/60</f>
-        <v>202.5</v>
+        <v>26.5</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -14331,14 +14310,14 @@
         <v>618</v>
       </c>
       <c r="J9" s="140">
-        <v>6.100000000176806</v>
+        <v>7.275957614183426E-12</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="141" t="s">
         <v>597</v>
       </c>
       <c r="M9" s="119">
-        <v>81037.0</v>
+        <v>6854.0</v>
       </c>
       <c r="N9" s="115"/>
     </row>
@@ -14348,7 +14327,7 @@
         <v>635</v>
       </c>
       <c r="C10" s="144">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D10" s="144" t="s">
         <v>636</v>
@@ -14360,13 +14339,13 @@
         <v>638</v>
       </c>
       <c r="G10" s="144">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="H10" s="144" t="s">
         <v>639</v>
       </c>
       <c r="I10" s="146">
-        <v>95.0</v>
+        <v>10.0</v>
       </c>
       <c r="J10" s="35"/>
       <c r="K10" s="20"/>
@@ -14374,7 +14353,7 @@
         <v>601</v>
       </c>
       <c r="M10" s="119">
-        <v>1545.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="115"/>
     </row>
@@ -14384,7 +14363,7 @@
         <v>640</v>
       </c>
       <c r="C11" s="144">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="144" t="s">
         <v>641</v>
@@ -14402,7 +14381,7 @@
         <v>596</v>
       </c>
       <c r="M11" s="148">
-        <v>43573.0</v>
+        <v>2556.0</v>
       </c>
       <c r="N11" s="115"/>
     </row>
@@ -14412,10 +14391,10 @@
         <v>643</v>
       </c>
       <c r="C12" s="144">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="144" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E12" s="145" t="s">
         <v>644</v>
@@ -14434,15 +14413,9 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="142"/>
-      <c r="B13" s="143" t="s">
-        <v>645</v>
-      </c>
-      <c r="C13" s="144">
-        <v>21.0</v>
-      </c>
-      <c r="D13" s="144" t="s">
-        <v>646</v>
-      </c>
+      <c r="B13" s="143"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
       <c r="E13" s="145" t="s">
         <v>644</v>
       </c>
@@ -14456,23 +14429,17 @@
         <v>608</v>
       </c>
       <c r="M13" s="119">
-        <v>2400.0</v>
+        <v>700.0</v>
       </c>
       <c r="N13" s="115"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="142"/>
-      <c r="B14" s="143" t="s">
-        <v>647</v>
-      </c>
-      <c r="C14" s="144">
-        <v>6.0</v>
-      </c>
-      <c r="D14" s="144" t="s">
-        <v>648</v>
-      </c>
+      <c r="B14" s="143"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
       <c r="E14" s="145" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F14" s="143"/>
       <c r="G14" s="144"/>
@@ -14490,17 +14457,11 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="142"/>
-      <c r="B15" s="143" t="s">
-        <v>650</v>
-      </c>
-      <c r="C15" s="144">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="144" t="s">
-        <v>651</v>
-      </c>
+      <c r="B15" s="143"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
       <c r="E15" s="145" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F15" s="143"/>
       <c r="G15" s="144"/>
@@ -14532,7 +14493,7 @@
         <v>611</v>
       </c>
       <c r="M16" s="119">
-        <v>3079.0</v>
+        <v>0.0</v>
       </c>
       <c r="N16" s="115"/>
     </row>
@@ -14552,7 +14513,7 @@
         <v>612</v>
       </c>
       <c r="M17" s="153">
-        <v>4275.0</v>
+        <v>400.0</v>
       </c>
       <c r="N17" s="115"/>
     </row>
@@ -14623,16 +14584,16 @@
       <c r="H21" s="144"/>
       <c r="I21" s="146"/>
       <c r="J21" s="163">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="K21" s="164">
-        <v>8788.900000000001</v>
+        <v>0.0</v>
       </c>
       <c r="L21" s="165">
-        <v>39.0</v>
+        <v>1.0</v>
       </c>
       <c r="M21" s="166" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="N21" s="155"/>
     </row>
@@ -14687,16 +14648,16 @@
       <c r="H24" s="144"/>
       <c r="I24" s="146"/>
       <c r="J24" s="171">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="K24" s="165">
-        <v>2823.0</v>
+        <v>200.0</v>
       </c>
       <c r="L24" s="165">
-        <v>265.0</v>
+        <v>13.0</v>
       </c>
       <c r="M24" s="172">
-        <v>42.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="155"/>
     </row>
@@ -14749,14 +14710,14 @@
       <c r="H27" s="144"/>
       <c r="I27" s="146"/>
       <c r="J27" s="177">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" s="93"/>
       <c r="L27" s="178">
-        <v>0.13493064125417067</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M27" s="179">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="155"/>
     </row>
@@ -14807,10 +14768,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="27"/>
       <c r="L30" s="182">
-        <v>0.8650693587458294</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="M30" s="183">
-        <v>0.11445133842192666</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="N30" s="155"/>
     </row>
@@ -14922,7 +14883,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="185"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="184"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -14962,7 +14923,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="184"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -14990,7 +14951,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="185"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="184"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -15024,7 +14985,7 @@
       <c r="B5" s="185"/>
       <c r="C5" s="185"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="184"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -15058,7 +15019,7 @@
       <c r="B6" s="4"/>
       <c r="C6" s="185"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="184"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -15364,13 +15325,13 @@
       <c r="B15" s="4"/>
       <c r="C15" s="185"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="184"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="K15" s="184"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -15398,13 +15359,13 @@
       <c r="B16" s="4"/>
       <c r="C16" s="185"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="184"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="K16" s="184"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -15432,7 +15393,7 @@
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="184"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -15574,7 +15535,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="184"/>
+      <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
@@ -15670,7 +15631,7 @@
       <c r="B24" s="185"/>
       <c r="C24" s="185"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="184"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -15778,7 +15739,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+      <c r="K27" s="184"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -15942,7 +15903,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="185"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="184"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -16112,7 +16073,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="185"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="184"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -16146,7 +16107,7 @@
       <c r="B38" s="185"/>
       <c r="C38" s="185"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="184"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -16254,7 +16215,7 @@
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-      <c r="K41" s="184"/>
+      <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
@@ -16316,7 +16277,7 @@
       <c r="B43" s="4"/>
       <c r="C43" s="185"/>
       <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="184"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -16350,7 +16311,7 @@
       <c r="B44" s="4"/>
       <c r="C44" s="185"/>
       <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="184"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -16588,7 +16549,7 @@
       <c r="B51" s="4"/>
       <c r="C51" s="185"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="184"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -16656,7 +16617,7 @@
       <c r="B53" s="4"/>
       <c r="C53" s="185"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="184"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -16758,7 +16719,7 @@
       <c r="B56" s="4"/>
       <c r="C56" s="185"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="184"/>
+      <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -16792,13 +16753,13 @@
       <c r="B57" s="4"/>
       <c r="C57" s="185"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="184"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
+      <c r="K57" s="184"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
@@ -16826,7 +16787,7 @@
       <c r="B58" s="4"/>
       <c r="C58" s="185"/>
       <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
+      <c r="E58" s="184"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -16968,7 +16929,7 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-      <c r="K62" s="184"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
@@ -16996,7 +16957,7 @@
       <c r="B63" s="4"/>
       <c r="C63" s="185"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="184"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -17030,7 +16991,7 @@
       <c r="B64" s="4"/>
       <c r="C64" s="185"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="184"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -17098,7 +17059,7 @@
       <c r="B66" s="4"/>
       <c r="C66" s="185"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
+      <c r="E66" s="184"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -17165,13 +17126,13 @@
       <c r="B68" s="4"/>
       <c r="C68" s="185"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
+      <c r="E68" s="184"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
+      <c r="K68" s="184"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
@@ -17199,7 +17160,7 @@
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="184"/>
+      <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
@@ -17233,7 +17194,7 @@
       <c r="B70" s="4"/>
       <c r="C70" s="185"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="184"/>
+      <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -17267,7 +17228,7 @@
       <c r="B71" s="4"/>
       <c r="C71" s="185"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="184"/>
+      <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -17403,7 +17364,7 @@
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="184"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
@@ -17471,7 +17432,7 @@
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="184"/>
+      <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -17511,7 +17472,7 @@
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
-      <c r="K78" s="184"/>
+      <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
@@ -17573,7 +17534,7 @@
       <c r="B80" s="4"/>
       <c r="C80" s="185"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
+      <c r="E80" s="184"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
@@ -17641,7 +17602,7 @@
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
+      <c r="E82" s="184"/>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -17709,7 +17670,7 @@
       <c r="B84" s="4"/>
       <c r="C84" s="185"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
+      <c r="E84" s="184"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -17749,7 +17710,7 @@
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
-      <c r="K85" s="184"/>
+      <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
@@ -17777,7 +17738,7 @@
       <c r="B86" s="4"/>
       <c r="C86" s="185"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="184"/>
+      <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
@@ -17845,7 +17806,7 @@
       <c r="B88" s="4"/>
       <c r="C88" s="185"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+      <c r="E88" s="184"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -17879,7 +17840,7 @@
       <c r="B89" s="4"/>
       <c r="C89" s="185"/>
       <c r="D89" s="4"/>
-      <c r="E89" s="184"/>
+      <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
@@ -17913,7 +17874,7 @@
       <c r="B90" s="4"/>
       <c r="C90" s="185"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
+      <c r="E90" s="184"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
@@ -18013,7 +17974,7 @@
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
-      <c r="E93" s="184"/>
+      <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -18144,9 +18105,9 @@
     <row r="97">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
+      <c r="C97" s="185"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
+      <c r="E97" s="184"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -18213,7 +18174,7 @@
       <c r="B99" s="4"/>
       <c r="C99" s="185"/>
       <c r="D99" s="4"/>
-      <c r="E99" s="184"/>
+      <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -18247,7 +18208,7 @@
       <c r="B100" s="4"/>
       <c r="C100" s="185"/>
       <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
+      <c r="E100" s="184"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -18280,7 +18241,7 @@
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
+      <c r="E101" s="184"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -18313,7 +18274,7 @@
       <c r="B102" s="4"/>
       <c r="C102" s="185"/>
       <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
+      <c r="E102" s="184"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
@@ -18342,22 +18303,22 @@
       <c r="AF102" s="184"/>
     </row>
     <row r="103">
-      <c r="A103" s="184"/>
-      <c r="B103" s="184"/>
-      <c r="C103" s="186"/>
-      <c r="D103" s="184"/>
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="185"/>
+      <c r="D103" s="4"/>
       <c r="E103" s="184"/>
-      <c r="F103" s="184"/>
-      <c r="G103" s="184"/>
-      <c r="H103" s="184"/>
-      <c r="I103" s="184"/>
-      <c r="J103" s="184"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
       <c r="K103" s="184"/>
-      <c r="L103" s="184"/>
-      <c r="M103" s="184"/>
-      <c r="N103" s="184"/>
-      <c r="O103" s="184"/>
-      <c r="P103" s="184"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
       <c r="Q103" s="184"/>
       <c r="R103" s="184"/>
       <c r="S103" s="184"/>
@@ -18376,22 +18337,22 @@
       <c r="AF103" s="184"/>
     </row>
     <row r="104">
-      <c r="A104" s="184"/>
-      <c r="B104" s="184"/>
-      <c r="C104" s="184"/>
-      <c r="D104" s="184"/>
-      <c r="E104" s="184"/>
-      <c r="F104" s="184"/>
-      <c r="G104" s="184"/>
-      <c r="H104" s="184"/>
-      <c r="I104" s="184"/>
-      <c r="J104" s="184"/>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
       <c r="K104" s="184"/>
-      <c r="L104" s="184"/>
-      <c r="M104" s="184"/>
-      <c r="N104" s="184"/>
-      <c r="O104" s="184"/>
-      <c r="P104" s="184"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
       <c r="Q104" s="184"/>
       <c r="R104" s="184"/>
       <c r="S104" s="184"/>
@@ -18410,22 +18371,22 @@
       <c r="AF104" s="184"/>
     </row>
     <row r="105">
-      <c r="A105" s="184"/>
-      <c r="B105" s="184"/>
-      <c r="C105" s="186"/>
-      <c r="D105" s="184"/>
-      <c r="E105" s="184"/>
-      <c r="F105" s="184"/>
-      <c r="G105" s="184"/>
-      <c r="H105" s="184"/>
-      <c r="I105" s="184"/>
-      <c r="J105" s="184"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="185"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
       <c r="K105" s="184"/>
-      <c r="L105" s="184"/>
-      <c r="M105" s="184"/>
-      <c r="N105" s="184"/>
-      <c r="O105" s="184"/>
-      <c r="P105" s="184"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
       <c r="Q105" s="184"/>
       <c r="R105" s="184"/>
       <c r="S105" s="184"/>
@@ -18444,22 +18405,22 @@
       <c r="AF105" s="184"/>
     </row>
     <row r="106">
-      <c r="A106" s="184"/>
-      <c r="B106" s="184"/>
-      <c r="C106" s="184"/>
-      <c r="D106" s="184"/>
-      <c r="E106" s="184"/>
-      <c r="F106" s="184"/>
-      <c r="G106" s="184"/>
-      <c r="H106" s="184"/>
-      <c r="I106" s="184"/>
-      <c r="J106" s="184"/>
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
       <c r="K106" s="184"/>
-      <c r="L106" s="184"/>
-      <c r="M106" s="184"/>
-      <c r="N106" s="184"/>
-      <c r="O106" s="184"/>
-      <c r="P106" s="184"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
       <c r="Q106" s="184"/>
       <c r="R106" s="184"/>
       <c r="S106" s="184"/>
@@ -18478,22 +18439,22 @@
       <c r="AF106" s="184"/>
     </row>
     <row r="107">
-      <c r="A107" s="184"/>
-      <c r="B107" s="184"/>
-      <c r="C107" s="184"/>
-      <c r="D107" s="184"/>
-      <c r="E107" s="184"/>
-      <c r="F107" s="184"/>
-      <c r="G107" s="184"/>
-      <c r="H107" s="184"/>
-      <c r="I107" s="184"/>
-      <c r="J107" s="184"/>
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
       <c r="K107" s="184"/>
-      <c r="L107" s="184"/>
-      <c r="M107" s="184"/>
-      <c r="N107" s="184"/>
-      <c r="O107" s="184"/>
-      <c r="P107" s="184"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
       <c r="Q107" s="184"/>
       <c r="R107" s="184"/>
       <c r="S107" s="184"/>
@@ -18512,22 +18473,22 @@
       <c r="AF107" s="184"/>
     </row>
     <row r="108">
-      <c r="A108" s="184"/>
-      <c r="B108" s="184"/>
-      <c r="C108" s="186"/>
-      <c r="D108" s="184"/>
-      <c r="E108" s="184"/>
-      <c r="F108" s="184"/>
-      <c r="G108" s="184"/>
-      <c r="H108" s="184"/>
-      <c r="I108" s="184"/>
-      <c r="J108" s="184"/>
-      <c r="K108" s="184"/>
-      <c r="L108" s="184"/>
-      <c r="M108" s="184"/>
-      <c r="N108" s="184"/>
-      <c r="O108" s="184"/>
-      <c r="P108" s="184"/>
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="185"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
       <c r="Q108" s="184"/>
       <c r="R108" s="184"/>
       <c r="S108" s="184"/>
@@ -18546,22 +18507,22 @@
       <c r="AF108" s="184"/>
     </row>
     <row r="109">
-      <c r="A109" s="184"/>
-      <c r="B109" s="184"/>
-      <c r="C109" s="184"/>
-      <c r="D109" s="184"/>
-      <c r="E109" s="184"/>
-      <c r="F109" s="184"/>
-      <c r="G109" s="184"/>
-      <c r="H109" s="184"/>
-      <c r="I109" s="184"/>
-      <c r="J109" s="184"/>
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
       <c r="K109" s="184"/>
-      <c r="L109" s="184"/>
-      <c r="M109" s="184"/>
-      <c r="N109" s="184"/>
-      <c r="O109" s="184"/>
-      <c r="P109" s="184"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
       <c r="Q109" s="184"/>
       <c r="R109" s="184"/>
       <c r="S109" s="184"/>
@@ -18580,22 +18541,22 @@
       <c r="AF109" s="184"/>
     </row>
     <row r="110">
-      <c r="A110" s="184"/>
-      <c r="B110" s="184"/>
-      <c r="C110" s="186"/>
-      <c r="D110" s="184"/>
-      <c r="E110" s="184"/>
-      <c r="F110" s="184"/>
-      <c r="G110" s="184"/>
-      <c r="H110" s="184"/>
-      <c r="I110" s="184"/>
-      <c r="J110" s="184"/>
-      <c r="K110" s="184"/>
-      <c r="L110" s="184"/>
-      <c r="M110" s="184"/>
-      <c r="N110" s="184"/>
-      <c r="O110" s="184"/>
-      <c r="P110" s="184"/>
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="185"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
       <c r="Q110" s="184"/>
       <c r="R110" s="184"/>
       <c r="S110" s="184"/>
@@ -18613,22 +18574,22 @@
       <c r="AF110" s="184"/>
     </row>
     <row r="111">
-      <c r="A111" s="184"/>
-      <c r="B111" s="184"/>
-      <c r="C111" s="184"/>
-      <c r="D111" s="184"/>
-      <c r="E111" s="184"/>
-      <c r="F111" s="184"/>
-      <c r="G111" s="184"/>
-      <c r="H111" s="184"/>
-      <c r="I111" s="184"/>
-      <c r="J111" s="184"/>
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
       <c r="K111" s="184"/>
-      <c r="L111" s="184"/>
-      <c r="M111" s="184"/>
-      <c r="N111" s="184"/>
-      <c r="O111" s="184"/>
-      <c r="P111" s="184"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
       <c r="Q111" s="184"/>
       <c r="S111" s="184"/>
       <c r="T111" s="184"/>
@@ -18644,22 +18605,22 @@
       <c r="AF111" s="184"/>
     </row>
     <row r="112">
-      <c r="A112" s="184"/>
-      <c r="B112" s="184"/>
-      <c r="C112" s="184"/>
-      <c r="D112" s="184"/>
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
       <c r="E112" s="184"/>
-      <c r="F112" s="184"/>
-      <c r="G112" s="184"/>
-      <c r="H112" s="184"/>
-      <c r="I112" s="184"/>
-      <c r="J112" s="184"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
       <c r="K112" s="184"/>
-      <c r="L112" s="184"/>
-      <c r="M112" s="184"/>
-      <c r="N112" s="184"/>
-      <c r="O112" s="184"/>
-      <c r="P112" s="184"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
       <c r="Q112" s="184"/>
       <c r="S112" s="184"/>
       <c r="T112" s="184"/>
@@ -18676,23 +18637,24 @@
       <c r="AF112" s="184"/>
     </row>
     <row r="113">
-      <c r="A113" s="184"/>
-      <c r="B113" s="184"/>
-      <c r="C113" s="186"/>
-      <c r="D113" s="184"/>
-      <c r="E113" s="184"/>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="184"/>
-      <c r="L113" s="184"/>
-      <c r="M113" s="184"/>
-      <c r="N113" s="184"/>
-      <c r="O113" s="184"/>
-      <c r="P113" s="184"/>
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="185"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
       <c r="Q113" s="184"/>
+      <c r="R113" s="184"/>
       <c r="S113" s="184"/>
       <c r="T113" s="184"/>
       <c r="U113" s="184"/>
@@ -18701,28 +18663,29 @@
       <c r="X113" s="184"/>
       <c r="Y113" s="184"/>
       <c r="Z113" s="184"/>
+      <c r="AA113" s="184"/>
       <c r="AB113" s="184"/>
       <c r="AC113" s="184"/>
       <c r="AE113" s="184"/>
       <c r="AF113" s="184"/>
     </row>
     <row r="114">
-      <c r="A114" s="184"/>
-      <c r="B114" s="184"/>
-      <c r="C114" s="184"/>
-      <c r="D114" s="184"/>
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
       <c r="E114" s="184"/>
-      <c r="F114" s="184"/>
-      <c r="G114" s="184"/>
-      <c r="H114" s="184"/>
-      <c r="I114" s="184"/>
-      <c r="J114" s="184"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
       <c r="K114" s="184"/>
-      <c r="L114" s="184"/>
-      <c r="M114" s="184"/>
-      <c r="N114" s="184"/>
-      <c r="O114" s="184"/>
-      <c r="P114" s="184"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
       <c r="Q114" s="184"/>
       <c r="R114" s="184"/>
       <c r="S114" s="184"/>
@@ -18741,22 +18704,22 @@
       <c r="AF114" s="184"/>
     </row>
     <row r="115">
-      <c r="A115" s="184"/>
-      <c r="B115" s="184"/>
-      <c r="C115" s="184"/>
-      <c r="D115" s="184"/>
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
       <c r="E115" s="184"/>
-      <c r="F115" s="184"/>
-      <c r="G115" s="184"/>
-      <c r="H115" s="184"/>
-      <c r="I115" s="184"/>
-      <c r="J115" s="184"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
       <c r="K115" s="184"/>
-      <c r="L115" s="184"/>
-      <c r="M115" s="184"/>
-      <c r="N115" s="184"/>
-      <c r="O115" s="184"/>
-      <c r="P115" s="184"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
       <c r="Q115" s="184"/>
       <c r="S115" s="184"/>
       <c r="T115" s="184"/>
@@ -18772,22 +18735,22 @@
       <c r="AF115" s="184"/>
     </row>
     <row r="116">
-      <c r="A116" s="184"/>
-      <c r="B116" s="184"/>
-      <c r="C116" s="184"/>
-      <c r="D116" s="184"/>
-      <c r="E116" s="184"/>
-      <c r="F116" s="184"/>
-      <c r="G116" s="184"/>
-      <c r="H116" s="184"/>
-      <c r="I116" s="184"/>
-      <c r="J116" s="184"/>
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
       <c r="K116" s="184"/>
-      <c r="L116" s="184"/>
-      <c r="M116" s="184"/>
-      <c r="N116" s="184"/>
-      <c r="O116" s="184"/>
-      <c r="P116" s="184"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
       <c r="Q116" s="184"/>
       <c r="R116" s="184"/>
       <c r="S116" s="184"/>
@@ -18805,22 +18768,22 @@
       <c r="AF116" s="184"/>
     </row>
     <row r="117">
-      <c r="A117" s="184"/>
-      <c r="B117" s="184"/>
-      <c r="C117" s="184"/>
-      <c r="D117" s="184"/>
-      <c r="E117" s="184"/>
-      <c r="F117" s="184"/>
-      <c r="G117" s="184"/>
-      <c r="H117" s="184"/>
-      <c r="I117" s="184"/>
-      <c r="J117" s="184"/>
-      <c r="K117" s="184"/>
-      <c r="L117" s="184"/>
-      <c r="M117" s="184"/>
-      <c r="N117" s="184"/>
-      <c r="O117" s="184"/>
-      <c r="P117" s="184"/>
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
       <c r="Q117" s="184"/>
       <c r="R117" s="184"/>
       <c r="S117" s="184"/>
@@ -18839,22 +18802,22 @@
       <c r="AF117" s="184"/>
     </row>
     <row r="118">
-      <c r="A118" s="184"/>
-      <c r="B118" s="184"/>
-      <c r="C118" s="184"/>
-      <c r="D118" s="184"/>
-      <c r="E118" s="184"/>
-      <c r="F118" s="184"/>
-      <c r="G118" s="184"/>
-      <c r="H118" s="184"/>
-      <c r="I118" s="184"/>
-      <c r="J118" s="184"/>
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
       <c r="K118" s="184"/>
-      <c r="L118" s="184"/>
-      <c r="M118" s="184"/>
-      <c r="N118" s="184"/>
-      <c r="O118" s="184"/>
-      <c r="P118" s="184"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
       <c r="Q118" s="184"/>
       <c r="R118" s="184"/>
       <c r="S118" s="184"/>
@@ -18872,22 +18835,22 @@
       <c r="AF118" s="184"/>
     </row>
     <row r="119">
-      <c r="A119" s="184"/>
-      <c r="B119" s="184"/>
-      <c r="C119" s="184"/>
-      <c r="D119" s="184"/>
-      <c r="E119" s="184"/>
-      <c r="F119" s="184"/>
-      <c r="G119" s="184"/>
-      <c r="H119" s="184"/>
-      <c r="I119" s="184"/>
-      <c r="J119" s="184"/>
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
       <c r="K119" s="184"/>
-      <c r="L119" s="184"/>
-      <c r="M119" s="184"/>
-      <c r="N119" s="184"/>
-      <c r="O119" s="184"/>
-      <c r="P119" s="184"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4"/>
       <c r="Q119" s="184"/>
       <c r="R119" s="184"/>
       <c r="S119" s="184"/>
@@ -18906,22 +18869,22 @@
       <c r="AF119" s="184"/>
     </row>
     <row r="120">
-      <c r="A120" s="184"/>
-      <c r="B120" s="184"/>
-      <c r="C120" s="184"/>
-      <c r="D120" s="184"/>
-      <c r="E120" s="184"/>
-      <c r="F120" s="184"/>
-      <c r="G120" s="184"/>
-      <c r="H120" s="184"/>
-      <c r="I120" s="184"/>
-      <c r="J120" s="184"/>
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
       <c r="K120" s="184"/>
-      <c r="L120" s="184"/>
-      <c r="M120" s="184"/>
-      <c r="N120" s="184"/>
-      <c r="O120" s="184"/>
-      <c r="P120" s="184"/>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4"/>
       <c r="Q120" s="184"/>
       <c r="R120" s="184"/>
       <c r="S120" s="184"/>
@@ -18939,22 +18902,22 @@
       <c r="AF120" s="184"/>
     </row>
     <row r="121">
-      <c r="A121" s="184"/>
-      <c r="B121" s="184"/>
-      <c r="C121" s="186"/>
-      <c r="D121" s="184"/>
-      <c r="E121" s="184"/>
-      <c r="F121" s="184"/>
-      <c r="G121" s="184"/>
-      <c r="H121" s="184"/>
-      <c r="I121" s="184"/>
-      <c r="J121" s="184"/>
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="185"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
       <c r="K121" s="184"/>
-      <c r="L121" s="184"/>
-      <c r="M121" s="184"/>
-      <c r="N121" s="184"/>
-      <c r="O121" s="184"/>
-      <c r="P121" s="184"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
       <c r="Q121" s="184"/>
       <c r="R121" s="184"/>
       <c r="S121" s="184"/>
@@ -19275,10 +19238,10 @@
     </row>
     <row r="4">
       <c r="A4" s="190" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="B4" s="190" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -61074,7 +61037,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="193" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -61106,28 +61069,28 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>656</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>663</v>
       </c>
       <c r="I2" s="184"/>
       <c r="J2" s="184"/>
@@ -61156,22 +61119,22 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C3" s="184"/>
       <c r="D3" s="184"/>
       <c r="E3" s="4" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="F3" s="184"/>
       <c r="G3" s="4" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="I3" s="184"/>
       <c r="J3" s="184"/>
@@ -61193,20 +61156,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="D4" s="184"/>
       <c r="E4" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="G4" s="184"/>
       <c r="H4" s="184"/>
@@ -61230,18 +61193,18 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="B5" s="184"/>
       <c r="C5" s="4" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="E5" s="184"/>
       <c r="F5" s="4" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="G5" s="184"/>
       <c r="H5" s="184"/>
@@ -61268,15 +61231,15 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C6" s="184"/>
       <c r="D6" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="E6" s="184"/>
       <c r="F6" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G6" s="184"/>
       <c r="H6" s="184"/>
@@ -61303,14 +61266,14 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C7" s="184"/>
       <c r="D7" s="4" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="G7" s="184"/>
       <c r="I7" s="184"/>
@@ -61334,14 +61297,14 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="F8" s="184"/>
       <c r="H8" s="4" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="I8" s="184"/>
       <c r="J8" s="184"/>
@@ -61366,17 +61329,17 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="D9" s="184"/>
       <c r="E9" s="4" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="H9" s="184"/>
       <c r="I9" s="184"/>
@@ -61401,14 +61364,14 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="F10" s="184"/>
       <c r="G10" s="4" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="I10" s="184"/>
       <c r="J10" s="184"/>
@@ -61621,7 +61584,7 @@
       <c r="Y19" s="184"/>
       <c r="Z19" s="184"/>
       <c r="AA19" s="4" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="AB19" s="4">
         <v>-11.0</v>
@@ -61946,7 +61909,7 @@
       <c r="Y30" s="184"/>
       <c r="Z30" s="184"/>
       <c r="AA30" s="4" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="AB30" s="4">
         <v>-8.0</v>
@@ -62067,7 +62030,7 @@
       <c r="Y34" s="184"/>
       <c r="Z34" s="184"/>
       <c r="AA34" s="4" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="AB34" s="4">
         <v>0.0</v>
@@ -62186,7 +62149,7 @@
       <c r="Y38" s="184"/>
       <c r="Z38" s="184"/>
       <c r="AA38" s="4" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="AB38" s="4">
         <v>-12.0</v>
@@ -62220,7 +62183,7 @@
       <c r="Y39" s="184"/>
       <c r="Z39" s="184"/>
       <c r="AA39" s="4" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="AB39" s="4">
         <v>0.0</v>
@@ -62312,7 +62275,7 @@
       <c r="Y42" s="184"/>
       <c r="Z42" s="184"/>
       <c r="AA42" s="4" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="AB42" s="4">
         <v>6.0</v>
@@ -62491,7 +62454,7 @@
       <c r="Y48" s="184"/>
       <c r="Z48" s="184"/>
       <c r="AA48" s="4" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="AB48" s="4">
         <v>-13.0</v>
@@ -62612,7 +62575,7 @@
       <c r="Y52" s="184"/>
       <c r="Z52" s="184"/>
       <c r="AA52" s="4" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="AB52" s="4">
         <v>5.0</v>
@@ -62820,7 +62783,7 @@
       <c r="Y59" s="184"/>
       <c r="Z59" s="184"/>
       <c r="AA59" s="4" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="AB59" s="4">
         <v>-9.0</v>
@@ -62941,7 +62904,7 @@
       <c r="Y63" s="184"/>
       <c r="Z63" s="184"/>
       <c r="AA63" s="4" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="AB63" s="4">
         <v>-19.0</v>
@@ -63149,7 +63112,7 @@
       <c r="Y70" s="184"/>
       <c r="Z70" s="184"/>
       <c r="AA70" s="4" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="AB70" s="4">
         <v>-14.0</v>
@@ -63618,7 +63581,7 @@
       <c r="Y86" s="184"/>
       <c r="Z86" s="184"/>
       <c r="AA86" s="4" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="AB86" s="4">
         <v>-21.0</v>
@@ -63652,7 +63615,7 @@
       <c r="Y87" s="184"/>
       <c r="Z87" s="184"/>
       <c r="AA87" s="4" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="AB87" s="4">
         <v>-7.0</v>
@@ -63686,7 +63649,7 @@
       <c r="Y88" s="184"/>
       <c r="Z88" s="184"/>
       <c r="AA88" s="4" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="AB88" s="4">
         <v>-10.0</v>
@@ -63720,7 +63683,7 @@
       <c r="Y89" s="184"/>
       <c r="Z89" s="184"/>
       <c r="AA89" s="4" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="AB89" s="4">
         <v>-6.0</v>
@@ -63813,7 +63776,7 @@
       <c r="Y92" s="184"/>
       <c r="Z92" s="184"/>
       <c r="AA92" s="4" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="AB92" s="4">
         <v>-17.0</v>
@@ -64079,7 +64042,7 @@
       <c r="Y101" s="184"/>
       <c r="Z101" s="184"/>
       <c r="AA101" s="4" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="AB101" s="4">
         <v>-6.0</v>
@@ -64113,7 +64076,7 @@
       <c r="Y102" s="184"/>
       <c r="Z102" s="184"/>
       <c r="AA102" s="4" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="AB102" s="4">
         <v>1.0</v>
@@ -64205,7 +64168,7 @@
       <c r="Y105" s="184"/>
       <c r="Z105" s="184"/>
       <c r="AA105" s="4" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="AB105" s="4">
         <v>-2.0</v>
@@ -64268,7 +64231,7 @@
       <c r="Y107" s="184"/>
       <c r="Z107" s="184"/>
       <c r="AA107" s="4" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="AB107" s="4">
         <v>-12.0</v>
@@ -64360,7 +64323,7 @@
       <c r="Y110" s="184"/>
       <c r="Z110" s="184"/>
       <c r="AA110" s="4" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="AB110" s="4">
         <v>-14.0</v>
@@ -64394,7 +64357,7 @@
       <c r="Y111" s="184"/>
       <c r="Z111" s="184"/>
       <c r="AA111" s="4" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AB111" s="4">
         <v>-6.0</v>
@@ -64428,7 +64391,7 @@
       <c r="Y112" s="184"/>
       <c r="Z112" s="184"/>
       <c r="AA112" s="4" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AB112" s="4">
         <v>-11.0</v>
@@ -64491,7 +64454,7 @@
       <c r="Y114" s="184"/>
       <c r="Z114" s="184"/>
       <c r="AA114" s="4" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="AB114" s="4">
         <v>-1.0</v>
@@ -64583,7 +64546,7 @@
       <c r="Y117" s="184"/>
       <c r="Z117" s="184"/>
       <c r="AA117" s="4" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AB117" s="4">
         <v>12.0</v>
@@ -64646,7 +64609,7 @@
       <c r="Y119" s="184"/>
       <c r="Z119" s="184"/>
       <c r="AA119" s="4" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AB119" s="4">
         <v>-17.0</v>
@@ -64767,7 +64730,7 @@
       <c r="Y123" s="184"/>
       <c r="Z123" s="184"/>
       <c r="AA123" s="4" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="AB123" s="4">
         <v>-15.0</v>
@@ -64918,7 +64881,7 @@
       <c r="Y128" s="184"/>
       <c r="Z128" s="184"/>
       <c r="AA128" s="4" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="AB128" s="4">
         <v>-11.0</v>
@@ -65303,7 +65266,7 @@
       <c r="Y141" s="184"/>
       <c r="Z141" s="184"/>
       <c r="AA141" s="4" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="AB141" s="4">
         <v>-10.0</v>
